--- a/server/trades.xlsx
+++ b/server/trades.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,9 +446,56 @@
         <v>Missed Profits</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>1-Jun</v>
+      </c>
+      <c r="D2" t="str">
+        <v>BankniftyPE</v>
+      </c>
+      <c r="E2">
+        <v>120</v>
+      </c>
+      <c r="F2">
+        <v>522.8</v>
+      </c>
+      <c r="G2">
+        <v>496.85</v>
+      </c>
+      <c r="H2">
+        <v>-25.949999999999932</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3263.999999999992</v>
+      </c>
+      <c r="K2">
+        <v>150</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2">
+        <v>-3263.999999999992</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/trades.xlsx
+++ b/server/trades.xlsx
@@ -466,16 +466,16 @@
         <v>522.8</v>
       </c>
       <c r="G2">
-        <v>496.85</v>
+        <v>496.83</v>
       </c>
       <c r="H2">
-        <v>-25.949999999999932</v>
+        <v>-25.96999999999997</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>3263.999999999992</v>
+        <v>3266.3999999999965</v>
       </c>
       <c r="K2">
         <v>150</v>
@@ -487,7 +487,7 @@
         <v/>
       </c>
       <c r="N2">
-        <v>-3263.999999999992</v>
+        <v>-3266.3999999999965</v>
       </c>
       <c r="O2">
         <v>0</v>

--- a/server/trades.xlsx
+++ b/server/trades.xlsx
@@ -466,16 +466,16 @@
         <v>522.8</v>
       </c>
       <c r="G2">
-        <v>496.83</v>
+        <v>496.85</v>
       </c>
       <c r="H2">
-        <v>-25.96999999999997</v>
+        <v>-25.949999999999932</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>3266.3999999999965</v>
+        <v>3263.999999999992</v>
       </c>
       <c r="K2">
         <v>150</v>
@@ -487,7 +487,7 @@
         <v/>
       </c>
       <c r="N2">
-        <v>-3266.3999999999965</v>
+        <v>-3263.999999999992</v>
       </c>
       <c r="O2">
         <v>0</v>

--- a/server/trades.xlsx
+++ b/server/trades.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,56 +446,9 @@
         <v>Missed Profits</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
-      <c r="C2" t="str">
-        <v>1-Jun</v>
-      </c>
-      <c r="D2" t="str">
-        <v>BankniftyPE</v>
-      </c>
-      <c r="E2">
-        <v>120</v>
-      </c>
-      <c r="F2">
-        <v>522.8</v>
-      </c>
-      <c r="G2">
-        <v>496.85</v>
-      </c>
-      <c r="H2">
-        <v>-25.949999999999932</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>3263.999999999992</v>
-      </c>
-      <c r="K2">
-        <v>150</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2">
-        <v>-3263.999999999992</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/trades.xlsx
+++ b/server/trades.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,9 +446,56 @@
         <v>Missed Profits</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v>01-06-2026</v>
+      </c>
+      <c r="D2" t="str">
+        <v>BankniftyPE</v>
+      </c>
+      <c r="E2">
+        <v>120</v>
+      </c>
+      <c r="F2">
+        <v>522.8</v>
+      </c>
+      <c r="G2">
+        <v>496.85</v>
+      </c>
+      <c r="H2">
+        <v>-25.949999999999932</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>3243.999999999992</v>
+      </c>
+      <c r="K2">
+        <v>130</v>
+      </c>
+      <c r="L2" t="str">
+        <v>YES</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2">
+        <v>-3243.999999999992</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/trades.xlsx
+++ b/server/trades.xlsx
@@ -454,40 +454,40 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>01-06-2026</v>
+        <v>14-10-2025</v>
       </c>
       <c r="D2" t="str">
         <v>BankniftyPE</v>
       </c>
       <c r="E2">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="F2">
-        <v>522.8</v>
+        <v>413</v>
       </c>
       <c r="G2">
-        <v>496.85</v>
+        <v>449</v>
       </c>
       <c r="H2">
-        <v>-25.949999999999932</v>
+        <v>36</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1265</v>
       </c>
       <c r="J2">
-        <v>3243.999999999992</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>130</v>
+        <v>-27</v>
       </c>
       <c r="L2" t="str">
-        <v>YES</v>
+        <v>Yes</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>Target Hit</v>
       </c>
       <c r="N2">
-        <v>-3243.999999999992</v>
+        <v>1238</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -501,28 +501,28 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>14-10-2025</v>
+        <v>15-10-2025</v>
       </c>
       <c r="D3" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E3">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F3">
-        <v>413</v>
+        <v>193</v>
       </c>
       <c r="G3">
-        <v>449</v>
+        <v>163</v>
       </c>
       <c r="H3">
-        <v>36</v>
+        <v>-30</v>
       </c>
       <c r="I3">
-        <v>1265</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>-2254</v>
       </c>
       <c r="K3">
         <v>-27</v>
@@ -531,10 +531,10 @@
         <v>Yes</v>
       </c>
       <c r="M3" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N3">
-        <v>1238</v>
+        <v>-2281</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -557,19 +557,19 @@
         <v>75</v>
       </c>
       <c r="F4">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="G4">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="H4">
-        <v>-30</v>
+        <v>27</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2006</v>
       </c>
       <c r="J4">
-        <v>-2254</v>
+        <v>0</v>
       </c>
       <c r="K4">
         <v>-27</v>
@@ -578,10 +578,10 @@
         <v>Yes</v>
       </c>
       <c r="M4" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N4">
-        <v>-2281</v>
+        <v>1979</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -598,22 +598,22 @@
         <v>15-10-2025</v>
       </c>
       <c r="D5" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E5">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F5">
-        <v>202</v>
+        <v>394</v>
       </c>
       <c r="G5">
-        <v>228</v>
+        <v>426</v>
       </c>
       <c r="H5">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I5">
-        <v>2006</v>
+        <v>1150</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -628,7 +628,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N5">
-        <v>1979</v>
+        <v>1123</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -642,31 +642,31 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>15-10-2025</v>
+        <v>17-10-2025</v>
       </c>
       <c r="D6" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E6">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F6">
-        <v>394</v>
+        <v>528</v>
       </c>
       <c r="G6">
-        <v>426</v>
+        <v>603</v>
       </c>
       <c r="H6">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="I6">
-        <v>1150</v>
+        <v>1511</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="L6" t="str">
         <v>Yes</v>
@@ -675,7 +675,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N6">
-        <v>1123</v>
+        <v>1483</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -692,22 +692,22 @@
         <v>17-10-2025</v>
       </c>
       <c r="D7" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>528</v>
+        <v>418</v>
       </c>
       <c r="G7">
-        <v>603</v>
+        <v>443</v>
       </c>
       <c r="H7">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="I7">
-        <v>1511</v>
+        <v>858</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -722,7 +722,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N7">
-        <v>1483</v>
+        <v>830</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -739,22 +739,22 @@
         <v>17-10-2025</v>
       </c>
       <c r="D8" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F8">
-        <v>418</v>
+        <v>185</v>
       </c>
       <c r="G8">
-        <v>443</v>
+        <v>195</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>858</v>
+        <v>686</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -769,7 +769,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N8">
-        <v>830</v>
+        <v>658</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -786,22 +786,22 @@
         <v>17-10-2025</v>
       </c>
       <c r="D9" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E9">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>185</v>
+        <v>423</v>
       </c>
       <c r="G9">
-        <v>195</v>
+        <v>474</v>
       </c>
       <c r="H9">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="I9">
-        <v>686</v>
+        <v>1766</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -816,7 +816,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N9">
-        <v>658</v>
+        <v>1738</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -830,28 +830,28 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>17-10-2025</v>
+        <v>20-10-2025</v>
       </c>
       <c r="D10" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E10">
         <v>35</v>
       </c>
       <c r="F10">
-        <v>423</v>
+        <v>387</v>
       </c>
       <c r="G10">
-        <v>474</v>
+        <v>358</v>
       </c>
       <c r="H10">
-        <v>50</v>
+        <v>-28</v>
       </c>
       <c r="I10">
-        <v>1766</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>-994</v>
       </c>
       <c r="K10">
         <v>-28</v>
@@ -860,10 +860,10 @@
         <v>Yes</v>
       </c>
       <c r="M10" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N10">
-        <v>1738</v>
+        <v>-1022</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -877,28 +877,28 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>20-10-2025</v>
+        <v>23-10-2025</v>
       </c>
       <c r="D11" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E11">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F11">
-        <v>387</v>
+        <v>507</v>
       </c>
       <c r="G11">
-        <v>358</v>
+        <v>585</v>
       </c>
       <c r="H11">
-        <v>-28</v>
+        <v>78</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1554</v>
       </c>
       <c r="J11">
-        <v>-994</v>
+        <v>0</v>
       </c>
       <c r="K11">
         <v>-28</v>
@@ -907,10 +907,10 @@
         <v>Yes</v>
       </c>
       <c r="M11" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N11">
-        <v>-1022</v>
+        <v>1526</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -933,16 +933,16 @@
         <v>20</v>
       </c>
       <c r="F12">
-        <v>507</v>
+        <v>535</v>
       </c>
       <c r="G12">
-        <v>585</v>
+        <v>537</v>
       </c>
       <c r="H12">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>1554</v>
+        <v>43</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -957,7 +957,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N12">
-        <v>1526</v>
+        <v>15</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -974,22 +974,22 @@
         <v>23-10-2025</v>
       </c>
       <c r="D13" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E13">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F13">
-        <v>535</v>
+        <v>186</v>
       </c>
       <c r="G13">
-        <v>537</v>
+        <v>227</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I13">
-        <v>43</v>
+        <v>3101</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N13">
-        <v>15</v>
+        <v>3073</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1018,25 +1018,25 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>23-10-2025</v>
+        <v>24-10-2025</v>
       </c>
       <c r="D14" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E14">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F14">
-        <v>186</v>
+        <v>380</v>
       </c>
       <c r="G14">
-        <v>227</v>
+        <v>438</v>
       </c>
       <c r="H14">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="I14">
-        <v>3101</v>
+        <v>2039</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1051,7 +1051,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N14">
-        <v>3073</v>
+        <v>2011</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1065,28 +1065,28 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>24-10-2025</v>
+        <v>27-10-2025</v>
       </c>
       <c r="D15" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E15">
         <v>35</v>
       </c>
       <c r="F15">
-        <v>380</v>
+        <v>405</v>
       </c>
       <c r="G15">
-        <v>438</v>
+        <v>344</v>
       </c>
       <c r="H15">
-        <v>58</v>
+        <v>-60</v>
       </c>
       <c r="I15">
-        <v>2039</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>-2107</v>
       </c>
       <c r="K15">
         <v>-28</v>
@@ -1095,10 +1095,10 @@
         <v>Yes</v>
       </c>
       <c r="M15" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N15">
-        <v>2011</v>
+        <v>-2135</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1115,37 +1115,37 @@
         <v>27-10-2025</v>
       </c>
       <c r="D16" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E16">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F16">
+        <v>480</v>
+      </c>
+      <c r="G16">
         <v>405</v>
       </c>
-      <c r="G16">
-        <v>344</v>
-      </c>
       <c r="H16">
-        <v>-60</v>
+        <v>-75</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>-2107</v>
+        <v>-1501</v>
       </c>
       <c r="K16">
         <v>-28</v>
       </c>
       <c r="L16" t="str">
-        <v>Yes</v>
+        <v>yes</v>
       </c>
       <c r="M16" t="str">
         <v>Stop Loss Hit</v>
       </c>
       <c r="N16">
-        <v>-2135</v>
+        <v>-1529</v>
       </c>
       <c r="O16">
         <v>0</v>
@@ -1159,28 +1159,28 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>27-10-2025</v>
+        <v>29-10-2025</v>
       </c>
       <c r="D17" t="str">
-        <v>Sensex CE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F17">
-        <v>480</v>
+        <v>209</v>
       </c>
       <c r="G17">
-        <v>405</v>
+        <v>185</v>
       </c>
       <c r="H17">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>-1501</v>
+        <v>-1849</v>
       </c>
       <c r="K17">
         <v>-28</v>
@@ -1192,7 +1192,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N17">
-        <v>-1529</v>
+        <v>-1877</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -1209,28 +1209,28 @@
         <v>29-10-2025</v>
       </c>
       <c r="D18" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E18">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F18">
-        <v>209</v>
+        <v>414</v>
       </c>
       <c r="G18">
-        <v>185</v>
+        <v>394</v>
       </c>
       <c r="H18">
+        <v>-20</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>-693</v>
+      </c>
+      <c r="K18">
         <v>-25</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>-1849</v>
-      </c>
-      <c r="K18">
-        <v>-28</v>
       </c>
       <c r="L18" t="str">
         <v>yes</v>
@@ -1239,7 +1239,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N18">
-        <v>-1877</v>
+        <v>-718</v>
       </c>
       <c r="O18">
         <v>0</v>
@@ -1253,40 +1253,40 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>29-10-2025</v>
+        <v>30-10-2025</v>
       </c>
       <c r="D19" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E19">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>414</v>
+        <v>474</v>
       </c>
       <c r="G19">
-        <v>394</v>
+        <v>575</v>
       </c>
       <c r="H19">
-        <v>-20</v>
+        <v>101</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>2016</v>
       </c>
       <c r="J19">
-        <v>-693</v>
+        <v>0</v>
       </c>
       <c r="K19">
         <v>-25</v>
       </c>
       <c r="L19" t="str">
-        <v>yes</v>
+        <v>No</v>
       </c>
       <c r="M19" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N19">
-        <v>-718</v>
+        <v>1991</v>
       </c>
       <c r="O19">
         <v>0</v>
@@ -1300,40 +1300,40 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>30-10-2025</v>
+        <v>04-11-2025</v>
       </c>
       <c r="D20" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F20">
-        <v>474</v>
+        <v>187</v>
       </c>
       <c r="G20">
-        <v>575</v>
+        <v>218</v>
       </c>
       <c r="H20">
-        <v>101</v>
+        <v>31</v>
       </c>
       <c r="I20">
-        <v>2016</v>
+        <v>4613</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>-25</v>
+        <v>-54</v>
       </c>
       <c r="L20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M20" t="str">
         <v>Target Hit</v>
       </c>
       <c r="N20">
-        <v>1991</v>
+        <v>4558</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1347,28 +1347,28 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>04-11-2025</v>
+        <v>06-11-2025</v>
       </c>
       <c r="D21" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E21">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F21">
-        <v>187</v>
+        <v>391</v>
       </c>
       <c r="G21">
-        <v>218</v>
+        <v>350</v>
       </c>
       <c r="H21">
-        <v>31</v>
+        <v>-41</v>
       </c>
       <c r="I21">
-        <v>4613</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>-2849</v>
       </c>
       <c r="K21">
         <v>-54</v>
@@ -1377,10 +1377,10 @@
         <v>Yes</v>
       </c>
       <c r="M21" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N21">
-        <v>4558</v>
+        <v>-2903</v>
       </c>
       <c r="O21">
         <v>0</v>
@@ -1394,40 +1394,40 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>06-11-2025</v>
+        <v>07-11-2025</v>
       </c>
       <c r="D22" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E22">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F22">
-        <v>391</v>
+        <v>185</v>
       </c>
       <c r="G22">
-        <v>350</v>
+        <v>159</v>
       </c>
       <c r="H22">
-        <v>-41</v>
+        <v>-26</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>-2849</v>
+        <v>-3908</v>
       </c>
       <c r="K22">
         <v>-54</v>
       </c>
       <c r="L22" t="str">
-        <v>Yes</v>
+        <v>yes</v>
       </c>
       <c r="M22" t="str">
         <v>Stop Loss Hit</v>
       </c>
       <c r="N22">
-        <v>-2903</v>
+        <v>-3962</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -1444,37 +1444,37 @@
         <v>07-11-2025</v>
       </c>
       <c r="D23" t="str">
-        <v>NiftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E23">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F23">
-        <v>185</v>
+        <v>479</v>
       </c>
       <c r="G23">
-        <v>159</v>
+        <v>383</v>
       </c>
       <c r="H23">
-        <v>-26</v>
+        <v>-96</v>
       </c>
       <c r="I23">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>-3908</v>
+        <v>-3834</v>
       </c>
       <c r="K23">
-        <v>-54</v>
+        <v>-40</v>
       </c>
       <c r="L23" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="M23" t="str">
         <v>Stop Loss Hit</v>
       </c>
       <c r="N23">
-        <v>-3962</v>
+        <v>-3874</v>
       </c>
       <c r="O23">
         <v>0</v>
@@ -1491,28 +1491,28 @@
         <v>07-11-2025</v>
       </c>
       <c r="D24" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E24">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F24">
-        <v>479</v>
+        <v>402</v>
       </c>
       <c r="G24">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="H24">
-        <v>-96</v>
+        <v>-25</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>-3834</v>
+        <v>-1751</v>
       </c>
       <c r="K24">
-        <v>-40</v>
+        <v>-54</v>
       </c>
       <c r="L24" t="str">
         <v>Yes</v>
@@ -1521,7 +1521,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N24">
-        <v>-3874</v>
+        <v>-1805</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -1535,19 +1535,19 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>07-11-2025</v>
+        <v>10-11-2025</v>
       </c>
       <c r="D25" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E25">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F25">
-        <v>402</v>
+        <v>180</v>
       </c>
       <c r="G25">
-        <v>377</v>
+        <v>155</v>
       </c>
       <c r="H25">
         <v>-25</v>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>-1751</v>
+        <v>-3788</v>
       </c>
       <c r="K25">
         <v>-54</v>
@@ -1568,7 +1568,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N25">
-        <v>-1805</v>
+        <v>-3842</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -1582,40 +1582,40 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>10-11-2025</v>
+        <v>11-11-2025</v>
       </c>
       <c r="D26" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E26">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>180</v>
+        <v>498</v>
       </c>
       <c r="G26">
-        <v>155</v>
+        <v>597</v>
       </c>
       <c r="H26">
-        <v>-25</v>
+        <v>99</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>3951</v>
       </c>
       <c r="J26">
-        <v>-3788</v>
+        <v>0</v>
       </c>
       <c r="K26">
-        <v>-54</v>
+        <v>-40</v>
       </c>
       <c r="L26" t="str">
         <v>Yes</v>
       </c>
       <c r="M26" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N26">
-        <v>-3842</v>
+        <v>3911</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -1629,40 +1629,40 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>11-11-2025</v>
+        <v>12-11-2025</v>
       </c>
       <c r="D27" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E27">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F27">
-        <v>498</v>
+        <v>196</v>
       </c>
       <c r="G27">
-        <v>597</v>
+        <v>176</v>
       </c>
       <c r="H27">
-        <v>99</v>
+        <v>-20</v>
       </c>
       <c r="I27">
-        <v>3951</v>
+        <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>-2940</v>
       </c>
       <c r="K27">
-        <v>-40</v>
+        <v>-54</v>
       </c>
       <c r="L27" t="str">
         <v>Yes</v>
       </c>
       <c r="M27" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N27">
-        <v>3911</v>
+        <v>-2994</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -1685,19 +1685,19 @@
         <v>75</v>
       </c>
       <c r="F28">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="G28">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="H28">
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>-2940</v>
+        <v>-3383</v>
       </c>
       <c r="K28">
         <v>-54</v>
@@ -1709,7 +1709,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N28">
-        <v>-2994</v>
+        <v>-3437</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -1723,7 +1723,7 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>12-11-2025</v>
+        <v>13-11-2025</v>
       </c>
       <c r="D29" t="str">
         <v>NiftyCE</v>
@@ -1732,19 +1732,19 @@
         <v>75</v>
       </c>
       <c r="F29">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G29">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="H29">
-        <v>-23</v>
+        <v>34</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="J29">
-        <v>-3383</v>
+        <v>0</v>
       </c>
       <c r="K29">
         <v>-54</v>
@@ -1753,10 +1753,10 @@
         <v>Yes</v>
       </c>
       <c r="M29" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N29">
-        <v>-3437</v>
+        <v>5046</v>
       </c>
       <c r="O29">
         <v>0</v>
@@ -1770,40 +1770,40 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>13-11-2025</v>
+        <v>14-11-2025</v>
       </c>
       <c r="D30" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E30">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F30">
-        <v>206</v>
+        <v>518</v>
       </c>
       <c r="G30">
-        <v>240</v>
+        <v>414</v>
       </c>
       <c r="H30">
-        <v>34</v>
+        <v>-104</v>
       </c>
       <c r="I30">
-        <v>5100</v>
+        <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>-4144</v>
       </c>
       <c r="K30">
-        <v>-54</v>
+        <v>-40</v>
       </c>
       <c r="L30" t="str">
         <v>Yes</v>
       </c>
       <c r="M30" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N30">
-        <v>5046</v>
+        <v>-4184</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -1817,40 +1817,40 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>14-11-2025</v>
+        <v>17-11-2025</v>
       </c>
       <c r="D31" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E31">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F31">
-        <v>518</v>
+        <v>410</v>
       </c>
       <c r="G31">
-        <v>414</v>
+        <v>439</v>
       </c>
       <c r="H31">
-        <v>-104</v>
+        <v>29</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>2006</v>
       </c>
       <c r="J31">
-        <v>-4144</v>
+        <v>0</v>
       </c>
       <c r="K31">
-        <v>-40</v>
+        <v>-54</v>
       </c>
       <c r="L31" t="str">
         <v>Yes</v>
       </c>
       <c r="M31" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N31">
-        <v>-4184</v>
+        <v>1952</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -1864,7 +1864,7 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>17-11-2025</v>
+        <v>19-11-2025</v>
       </c>
       <c r="D32" t="str">
         <v>BankniftyCE</v>
@@ -1873,19 +1873,19 @@
         <v>35</v>
       </c>
       <c r="F32">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="G32">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="H32">
-        <v>29</v>
+        <v>-11</v>
       </c>
       <c r="I32">
-        <v>2006</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>-739</v>
       </c>
       <c r="K32">
         <v>-54</v>
@@ -1894,10 +1894,10 @@
         <v>Yes</v>
       </c>
       <c r="M32" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N32">
-        <v>1952</v>
+        <v>-793</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -1911,31 +1911,31 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>19-11-2025</v>
+        <v>20-11-2025</v>
       </c>
       <c r="D33" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E33">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>420</v>
+        <v>499</v>
       </c>
       <c r="G33">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="H33">
-        <v>-11</v>
+        <v>-75</v>
       </c>
       <c r="I33">
         <v>0</v>
       </c>
       <c r="J33">
-        <v>-739</v>
+        <v>-3002</v>
       </c>
       <c r="K33">
-        <v>-54</v>
+        <v>-40</v>
       </c>
       <c r="L33" t="str">
         <v>Yes</v>
@@ -1944,7 +1944,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N33">
-        <v>-793</v>
+        <v>-3042</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -1958,40 +1958,40 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>20-11-2025</v>
+        <v>21-11-2025</v>
       </c>
       <c r="D34" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E34">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F34">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="G34">
-        <v>424</v>
+        <v>518</v>
       </c>
       <c r="H34">
-        <v>-75</v>
+        <v>39</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>2757</v>
       </c>
       <c r="J34">
-        <v>-3002</v>
+        <v>0</v>
       </c>
       <c r="K34">
-        <v>-40</v>
+        <v>-54</v>
       </c>
       <c r="L34" t="str">
         <v>Yes</v>
       </c>
       <c r="M34" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N34">
-        <v>-3042</v>
+        <v>2703</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2005,25 +2005,25 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>21-11-2025</v>
+        <v>24-11-2025</v>
       </c>
       <c r="D35" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E35">
         <v>35</v>
       </c>
       <c r="F35">
-        <v>479</v>
+        <v>405</v>
       </c>
       <c r="G35">
-        <v>518</v>
+        <v>448</v>
       </c>
       <c r="H35">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I35">
-        <v>2757</v>
+        <v>3010</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -2038,7 +2038,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N35">
-        <v>2703</v>
+        <v>2956</v>
       </c>
       <c r="O35">
         <v>0</v>
@@ -2055,22 +2055,22 @@
         <v>24-11-2025</v>
       </c>
       <c r="D36" t="str">
-        <v>BankniftyCE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E36">
         <v>35</v>
       </c>
       <c r="F36">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="G36">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="H36">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I36">
-        <v>3010</v>
+        <v>2734</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2085,7 +2085,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N36">
-        <v>2956</v>
+        <v>2680</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2099,43 +2099,43 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>24-11-2025</v>
+        <v>26-11-2025</v>
       </c>
       <c r="D37" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E37">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F37">
-        <v>434</v>
+        <v>214</v>
       </c>
       <c r="G37">
-        <v>473</v>
+        <v>243</v>
       </c>
       <c r="H37">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I37">
-        <v>2734</v>
+        <v>4409</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>-54</v>
+        <v>-216</v>
       </c>
       <c r="L37" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M37" t="str">
         <v>Target Hit</v>
       </c>
       <c r="N37">
-        <v>2680</v>
+        <v>4193</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="38">
@@ -2146,43 +2146,43 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>26-11-2025</v>
+        <v>03-12-2025</v>
       </c>
       <c r="D38" t="str">
-        <v>NiftyCE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E38">
         <v>75</v>
       </c>
       <c r="F38">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="G38">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="H38">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I38">
-        <v>4409</v>
+        <v>1459</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>-216</v>
+        <v>-24</v>
       </c>
       <c r="L38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M38" t="str">
         <v>Target Hit</v>
       </c>
       <c r="N38">
-        <v>4193</v>
+        <v>1435</v>
       </c>
       <c r="O38">
-        <v>3000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2196,28 +2196,28 @@
         <v>03-12-2025</v>
       </c>
       <c r="D39" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E39">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F39">
-        <v>185</v>
+        <v>463</v>
       </c>
       <c r="G39">
-        <v>204</v>
+        <v>482</v>
       </c>
       <c r="H39">
         <v>19</v>
       </c>
       <c r="I39">
-        <v>1459</v>
+        <v>662</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L39" t="str">
         <v>Yes</v>
@@ -2226,7 +2226,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N39">
-        <v>1435</v>
+        <v>642</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -2240,40 +2240,40 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>03-12-2025</v>
+        <v>05-12-2025</v>
       </c>
       <c r="D40" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E40">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F40">
-        <v>463</v>
+        <v>196</v>
       </c>
       <c r="G40">
-        <v>482</v>
+        <v>156</v>
       </c>
       <c r="H40">
-        <v>19</v>
+        <v>-40</v>
       </c>
       <c r="I40">
-        <v>662</v>
+        <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>-3004</v>
       </c>
       <c r="K40">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L40" t="str">
-        <v>Yes</v>
+        <v>yes</v>
       </c>
       <c r="M40" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N40">
-        <v>642</v>
+        <v>-3028</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -2290,37 +2290,37 @@
         <v>05-12-2025</v>
       </c>
       <c r="D41" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E41">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F41">
-        <v>196</v>
+        <v>406</v>
       </c>
       <c r="G41">
-        <v>156</v>
+        <v>345</v>
       </c>
       <c r="H41">
-        <v>-40</v>
+        <v>-62</v>
       </c>
       <c r="I41">
         <v>0</v>
       </c>
       <c r="J41">
-        <v>-3004</v>
+        <v>-2156</v>
       </c>
       <c r="K41">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L41" t="str">
-        <v>yes</v>
+        <v>Yes</v>
       </c>
       <c r="M41" t="str">
         <v>Stop Loss Hit</v>
       </c>
       <c r="N41">
-        <v>-3028</v>
+        <v>-2176</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -2334,31 +2334,31 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>05-12-2025</v>
+        <v>10-12-2025</v>
       </c>
       <c r="D42" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E42">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F42">
-        <v>406</v>
+        <v>192</v>
       </c>
       <c r="G42">
-        <v>345</v>
+        <v>177</v>
       </c>
       <c r="H42">
-        <v>-62</v>
+        <v>-14</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>-2156</v>
+        <v>-1069</v>
       </c>
       <c r="K42">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L42" t="str">
         <v>Yes</v>
@@ -2367,7 +2367,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N42">
-        <v>-2176</v>
+        <v>-1093</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -2381,31 +2381,31 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>10-12-2025</v>
+        <v>11-12-2025</v>
       </c>
       <c r="D43" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E43">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F43">
-        <v>192</v>
+        <v>406</v>
       </c>
       <c r="G43">
-        <v>177</v>
+        <v>351</v>
       </c>
       <c r="H43">
-        <v>-14</v>
+        <v>-55</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>-1069</v>
+        <v>-1936</v>
       </c>
       <c r="K43">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L43" t="str">
         <v>Yes</v>
@@ -2414,7 +2414,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N43">
-        <v>-1093</v>
+        <v>-1956</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>11-12-2025</v>
+        <v>12-12-2025</v>
       </c>
       <c r="D44" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E44">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F44">
-        <v>406</v>
+        <v>528</v>
       </c>
       <c r="G44">
-        <v>351</v>
+        <v>432</v>
       </c>
       <c r="H44">
-        <v>-55</v>
+        <v>-95</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>-1936</v>
+        <v>-1901</v>
       </c>
       <c r="K44">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L44" t="str">
         <v>Yes</v>
@@ -2461,7 +2461,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N44">
-        <v>-1956</v>
+        <v>-1925</v>
       </c>
       <c r="O44">
         <v>0</v>
@@ -2475,28 +2475,28 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>12-12-2025</v>
+        <v>15-12-2025</v>
       </c>
       <c r="D45" t="str">
-        <v>Sensex CE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E45">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F45">
-        <v>528</v>
+        <v>224</v>
       </c>
       <c r="G45">
-        <v>432</v>
+        <v>233</v>
       </c>
       <c r="H45">
-        <v>-95</v>
+        <v>9</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="J45">
-        <v>-1901</v>
+        <v>0</v>
       </c>
       <c r="K45">
         <v>-24</v>
@@ -2505,10 +2505,10 @@
         <v>Yes</v>
       </c>
       <c r="M45" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N45">
-        <v>-1925</v>
+        <v>685</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -2522,31 +2522,31 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>15-12-2025</v>
+        <v>16-12-2025</v>
       </c>
       <c r="D46" t="str">
-        <v>NiftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E46">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F46">
-        <v>224</v>
+        <v>514</v>
       </c>
       <c r="G46">
-        <v>233</v>
+        <v>625</v>
       </c>
       <c r="H46">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="I46">
-        <v>709</v>
+        <v>2227</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="L46" t="str">
         <v>Yes</v>
@@ -2555,7 +2555,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N46">
-        <v>685</v>
+        <v>2227</v>
       </c>
       <c r="O46">
         <v>0</v>
@@ -2572,37 +2572,37 @@
         <v>16-12-2025</v>
       </c>
       <c r="D47" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E47">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="F47">
-        <v>514</v>
+        <v>178</v>
       </c>
       <c r="G47">
-        <v>625</v>
+        <v>164</v>
       </c>
       <c r="H47">
-        <v>111</v>
+        <v>-14</v>
       </c>
       <c r="I47">
-        <v>2227</v>
+        <v>0</v>
       </c>
       <c r="J47">
-        <v>0</v>
+        <v>-1028</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="L47" t="str">
         <v>Yes</v>
       </c>
       <c r="M47" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N47">
-        <v>2227</v>
+        <v>-1052</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -2616,7 +2616,7 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>16-12-2025</v>
+        <v>18-12-2025</v>
       </c>
       <c r="D48" t="str">
         <v>NiftyPE</v>
@@ -2625,19 +2625,19 @@
         <v>75</v>
       </c>
       <c r="F48">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="G48">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="H48">
-        <v>-14</v>
+        <v>17</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1241</v>
       </c>
       <c r="J48">
-        <v>-1028</v>
+        <v>0</v>
       </c>
       <c r="K48">
         <v>-24</v>
@@ -2646,10 +2646,10 @@
         <v>Yes</v>
       </c>
       <c r="M48" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N48">
-        <v>-1052</v>
+        <v>1217</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -2663,28 +2663,28 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>18-12-2025</v>
+        <v>19-12-2025</v>
       </c>
       <c r="D49" t="str">
-        <v>NiftyPE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E49">
         <v>75</v>
       </c>
       <c r="F49">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="G49">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="H49">
-        <v>17</v>
+        <v>-13</v>
       </c>
       <c r="I49">
-        <v>1241</v>
+        <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>-990</v>
       </c>
       <c r="K49">
         <v>-24</v>
@@ -2693,10 +2693,10 @@
         <v>Yes</v>
       </c>
       <c r="M49" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N49">
-        <v>1217</v>
+        <v>-1014</v>
       </c>
       <c r="O49">
         <v>0</v>
@@ -2713,25 +2713,25 @@
         <v>19-12-2025</v>
       </c>
       <c r="D50" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E50">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F50">
-        <v>188</v>
+        <v>475</v>
       </c>
       <c r="G50">
-        <v>175</v>
+        <v>439</v>
       </c>
       <c r="H50">
-        <v>-13</v>
+        <v>-36</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>-990</v>
+        <v>-724</v>
       </c>
       <c r="K50">
         <v>-24</v>
@@ -2743,7 +2743,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N50">
-        <v>-1014</v>
+        <v>-748</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -2757,40 +2757,40 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>19-12-2025</v>
+        <v>22-12-2025</v>
       </c>
       <c r="D51" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E51">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F51">
-        <v>475</v>
+        <v>420</v>
       </c>
       <c r="G51">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="H51">
-        <v>-36</v>
+        <v>22</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="J51">
-        <v>-724</v>
+        <v>0</v>
       </c>
       <c r="K51">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L51" t="str">
         <v>Yes</v>
       </c>
       <c r="M51" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N51">
-        <v>-748</v>
+        <v>755</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -2807,37 +2807,37 @@
         <v>22-12-2025</v>
       </c>
       <c r="D52" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E52">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F52">
-        <v>420</v>
+        <v>195</v>
       </c>
       <c r="G52">
-        <v>442</v>
+        <v>192</v>
       </c>
       <c r="H52">
-        <v>22</v>
+        <v>-4</v>
       </c>
       <c r="I52">
-        <v>775</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>0</v>
+        <v>-270</v>
       </c>
       <c r="K52">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L52" t="str">
         <v>Yes</v>
       </c>
       <c r="M52" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N52">
-        <v>755</v>
+        <v>-294</v>
       </c>
       <c r="O52">
         <v>0</v>
@@ -2854,25 +2854,25 @@
         <v>22-12-2025</v>
       </c>
       <c r="D53" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E53">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F53">
-        <v>195</v>
+        <v>521</v>
       </c>
       <c r="G53">
-        <v>192</v>
+        <v>473</v>
       </c>
       <c r="H53">
-        <v>-4</v>
+        <v>-48</v>
       </c>
       <c r="I53">
         <v>0</v>
       </c>
       <c r="J53">
-        <v>-270</v>
+        <v>-955</v>
       </c>
       <c r="K53">
         <v>-24</v>
@@ -2884,7 +2884,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N53">
-        <v>-294</v>
+        <v>-979</v>
       </c>
       <c r="O53">
         <v>0</v>
@@ -2898,31 +2898,31 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>22-12-2025</v>
+        <v>24-12-2025</v>
       </c>
       <c r="D54" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E54">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F54">
-        <v>521</v>
+        <v>384</v>
       </c>
       <c r="G54">
-        <v>473</v>
+        <v>369</v>
       </c>
       <c r="H54">
-        <v>-48</v>
+        <v>-15</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>-955</v>
+        <v>-518</v>
       </c>
       <c r="K54">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L54" t="str">
         <v>Yes</v>
@@ -2931,7 +2931,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N54">
-        <v>-979</v>
+        <v>-538</v>
       </c>
       <c r="O54">
         <v>0</v>
@@ -2948,25 +2948,25 @@
         <v>24-12-2025</v>
       </c>
       <c r="D55" t="str">
-        <v>BankniftyCE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E55">
         <v>35</v>
       </c>
       <c r="F55">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="G55">
-        <v>369</v>
+        <v>469</v>
       </c>
       <c r="H55">
-        <v>-15</v>
+        <v>43</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1510</v>
       </c>
       <c r="J55">
-        <v>-518</v>
+        <v>0</v>
       </c>
       <c r="K55">
         <v>-20</v>
@@ -2975,10 +2975,10 @@
         <v>Yes</v>
       </c>
       <c r="M55" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N55">
-        <v>-538</v>
+        <v>1490</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -2995,37 +2995,37 @@
         <v>24-12-2025</v>
       </c>
       <c r="D56" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E56">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F56">
-        <v>426</v>
+        <v>198</v>
       </c>
       <c r="G56">
-        <v>469</v>
+        <v>182</v>
       </c>
       <c r="H56">
-        <v>43</v>
+        <v>-16</v>
       </c>
       <c r="I56">
-        <v>1510</v>
+        <v>0</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>-1193</v>
       </c>
       <c r="K56">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L56" t="str">
         <v>Yes</v>
       </c>
       <c r="M56" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N56">
-        <v>1490</v>
+        <v>-1217</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -3039,31 +3039,31 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>24-12-2025</v>
+        <v>26-12-2025</v>
       </c>
       <c r="D57" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E57">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F57">
-        <v>198</v>
+        <v>497</v>
       </c>
       <c r="G57">
-        <v>182</v>
+        <v>486</v>
       </c>
       <c r="H57">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>-1193</v>
+        <v>-406</v>
       </c>
       <c r="K57">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L57" t="str">
         <v>Yes</v>
@@ -3072,7 +3072,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N57">
-        <v>-1217</v>
+        <v>-426</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>26-12-2025</v>
+        <v>29-12-2025</v>
       </c>
       <c r="D58" t="str">
         <v>BankniftyPE</v>
@@ -3095,19 +3095,19 @@
         <v>35</v>
       </c>
       <c r="F58">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="G58">
         <v>486</v>
       </c>
       <c r="H58">
-        <v>-12</v>
+        <v>13</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="J58">
-        <v>-406</v>
+        <v>0</v>
       </c>
       <c r="K58">
         <v>-20</v>
@@ -3116,10 +3116,10 @@
         <v>Yes</v>
       </c>
       <c r="M58" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N58">
-        <v>-426</v>
+        <v>444</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -3136,28 +3136,28 @@
         <v>29-12-2025</v>
       </c>
       <c r="D59" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E59">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F59">
-        <v>473</v>
+        <v>206</v>
       </c>
       <c r="G59">
-        <v>486</v>
+        <v>217</v>
       </c>
       <c r="H59">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I59">
-        <v>464</v>
+        <v>829</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L59" t="str">
         <v>Yes</v>
@@ -3166,7 +3166,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N59">
-        <v>444</v>
+        <v>805</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -3180,31 +3180,31 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>29-12-2025</v>
+        <v>30-12-2025</v>
       </c>
       <c r="D60" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E60">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="F60">
-        <v>206</v>
+        <v>482</v>
       </c>
       <c r="G60">
-        <v>217</v>
+        <v>536</v>
       </c>
       <c r="H60">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="I60">
-        <v>829</v>
+        <v>1874</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L60" t="str">
         <v>Yes</v>
@@ -3213,7 +3213,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N60">
-        <v>805</v>
+        <v>1854</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -3230,37 +3230,37 @@
         <v>30-12-2025</v>
       </c>
       <c r="D61" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E61">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="F61">
-        <v>482</v>
+        <v>217</v>
       </c>
       <c r="G61">
-        <v>536</v>
+        <v>191</v>
       </c>
       <c r="H61">
-        <v>54</v>
+        <v>-26</v>
       </c>
       <c r="I61">
-        <v>1874</v>
+        <v>0</v>
       </c>
       <c r="J61">
-        <v>0</v>
+        <v>-1958</v>
       </c>
       <c r="K61">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L61" t="str">
         <v>Yes</v>
       </c>
       <c r="M61" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N61">
-        <v>1854</v>
+        <v>-1982</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -3277,25 +3277,25 @@
         <v>30-12-2025</v>
       </c>
       <c r="D62" t="str">
-        <v>NiftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E62">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="F62">
-        <v>217</v>
+        <v>501</v>
       </c>
       <c r="G62">
-        <v>191</v>
+        <v>413</v>
       </c>
       <c r="H62">
-        <v>-26</v>
+        <v>-87</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>-1958</v>
+        <v>-1747</v>
       </c>
       <c r="K62">
         <v>-24</v>
@@ -3307,7 +3307,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N62">
-        <v>-1982</v>
+        <v>-1771</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -3321,31 +3321,31 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>30-12-2025</v>
+        <v>31-12-2025</v>
       </c>
       <c r="D63" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E63">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F63">
-        <v>501</v>
+        <v>406</v>
       </c>
       <c r="G63">
-        <v>413</v>
+        <v>391</v>
       </c>
       <c r="H63">
-        <v>-87</v>
+        <v>-15</v>
       </c>
       <c r="I63">
         <v>0</v>
       </c>
       <c r="J63">
-        <v>-1747</v>
+        <v>-458</v>
       </c>
       <c r="K63">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L63" t="str">
         <v>Yes</v>
@@ -3354,7 +3354,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N63">
-        <v>-1771</v>
+        <v>-478</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -3371,37 +3371,37 @@
         <v>31-12-2025</v>
       </c>
       <c r="D64" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E64">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F64">
-        <v>406</v>
+        <v>206</v>
       </c>
       <c r="G64">
-        <v>391</v>
+        <v>230</v>
       </c>
       <c r="H64">
-        <v>-15</v>
+        <v>24</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>1537</v>
       </c>
       <c r="J64">
-        <v>-458</v>
+        <v>0</v>
       </c>
       <c r="K64">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L64" t="str">
         <v>Yes</v>
       </c>
       <c r="M64" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N64">
-        <v>-478</v>
+        <v>1513</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -3418,28 +3418,28 @@
         <v>31-12-2025</v>
       </c>
       <c r="D65" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E65">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F65">
-        <v>206</v>
+        <v>418</v>
       </c>
       <c r="G65">
-        <v>230</v>
+        <v>437</v>
       </c>
       <c r="H65">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I65">
-        <v>1537</v>
+        <v>576</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L65" t="str">
         <v>Yes</v>
@@ -3448,7 +3448,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N65">
-        <v>1513</v>
+        <v>556</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -3465,28 +3465,28 @@
         <v>31-12-2025</v>
       </c>
       <c r="D66" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E66">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F66">
-        <v>418</v>
+        <v>541</v>
       </c>
       <c r="G66">
-        <v>437</v>
+        <v>592</v>
       </c>
       <c r="H66">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="I66">
-        <v>576</v>
+        <v>1025</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L66" t="str">
         <v>Yes</v>
@@ -3495,7 +3495,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N66">
-        <v>556</v>
+        <v>1001</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -3518,16 +3518,16 @@
         <v>20</v>
       </c>
       <c r="F67">
-        <v>541</v>
+        <v>509</v>
       </c>
       <c r="G67">
-        <v>592</v>
+        <v>569</v>
       </c>
       <c r="H67">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="I67">
-        <v>1025</v>
+        <v>1193</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N67">
-        <v>1001</v>
+        <v>1169</v>
       </c>
       <c r="O67">
         <v>0</v>
@@ -3565,19 +3565,19 @@
         <v>20</v>
       </c>
       <c r="F68">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="G68">
-        <v>569</v>
+        <v>487</v>
       </c>
       <c r="H68">
-        <v>60</v>
+        <v>-7</v>
       </c>
       <c r="I68">
-        <v>1193</v>
+        <v>0</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>-136</v>
       </c>
       <c r="K68">
         <v>-24</v>
@@ -3586,10 +3586,10 @@
         <v>Yes</v>
       </c>
       <c r="M68" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N68">
-        <v>1169</v>
+        <v>-160</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -3603,28 +3603,28 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>31-12-2025</v>
+        <v>02-01-2026</v>
       </c>
       <c r="D69" t="str">
-        <v>Sensex CE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E69">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F69">
-        <v>493</v>
+        <v>200</v>
       </c>
       <c r="G69">
-        <v>487</v>
+        <v>236</v>
       </c>
       <c r="H69">
-        <v>-7</v>
+        <v>36</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>2350</v>
       </c>
       <c r="J69">
-        <v>-136</v>
+        <v>0</v>
       </c>
       <c r="K69">
         <v>-24</v>
@@ -3633,10 +3633,10 @@
         <v>Yes</v>
       </c>
       <c r="M69" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N69">
-        <v>-160</v>
+        <v>2326</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -3653,25 +3653,25 @@
         <v>02-01-2026</v>
       </c>
       <c r="D70" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E70">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F70">
-        <v>200</v>
+        <v>532</v>
       </c>
       <c r="G70">
-        <v>236</v>
+        <v>527</v>
       </c>
       <c r="H70">
-        <v>36</v>
+        <v>-5</v>
       </c>
       <c r="I70">
-        <v>2350</v>
+        <v>0</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>-99</v>
       </c>
       <c r="K70">
         <v>-24</v>
@@ -3680,10 +3680,10 @@
         <v>Yes</v>
       </c>
       <c r="M70" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N70">
-        <v>2326</v>
+        <v>-123</v>
       </c>
       <c r="O70">
         <v>0</v>
@@ -3706,19 +3706,19 @@
         <v>20</v>
       </c>
       <c r="F71">
-        <v>532</v>
+        <v>471</v>
       </c>
       <c r="G71">
-        <v>527</v>
+        <v>439</v>
       </c>
       <c r="H71">
-        <v>-5</v>
+        <v>-32</v>
       </c>
       <c r="I71">
         <v>0</v>
       </c>
       <c r="J71">
-        <v>-99</v>
+        <v>-641</v>
       </c>
       <c r="K71">
         <v>-24</v>
@@ -3730,7 +3730,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N71">
-        <v>-123</v>
+        <v>-665</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -3744,28 +3744,28 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>02-01-2026</v>
+        <v>05-01-2026</v>
       </c>
       <c r="D72" t="str">
-        <v>Sensex CE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E72">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F72">
-        <v>471</v>
+        <v>188</v>
       </c>
       <c r="G72">
-        <v>439</v>
+        <v>181</v>
       </c>
       <c r="H72">
-        <v>-32</v>
+        <v>-8</v>
       </c>
       <c r="I72">
         <v>0</v>
       </c>
       <c r="J72">
-        <v>-641</v>
+        <v>-488</v>
       </c>
       <c r="K72">
         <v>-24</v>
@@ -3777,7 +3777,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N72">
-        <v>-665</v>
+        <v>-512</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -3791,28 +3791,28 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>05-01-2026</v>
+        <v>06-01-2026</v>
       </c>
       <c r="D73" t="str">
-        <v>NiftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E73">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F73">
-        <v>188</v>
+        <v>473</v>
       </c>
       <c r="G73">
-        <v>181</v>
+        <v>376</v>
       </c>
       <c r="H73">
-        <v>-8</v>
+        <v>-97</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
       <c r="J73">
-        <v>-488</v>
+        <v>-1945</v>
       </c>
       <c r="K73">
         <v>-24</v>
@@ -3824,7 +3824,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N73">
-        <v>-512</v>
+        <v>-1969</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -3838,31 +3838,31 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>06-01-2026</v>
+        <v>07-01-2026</v>
       </c>
       <c r="D74" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E74">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F74">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="G74">
-        <v>376</v>
+        <v>472</v>
       </c>
       <c r="H74">
-        <v>-97</v>
+        <v>-28</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
       <c r="J74">
-        <v>-1945</v>
+        <v>-842</v>
       </c>
       <c r="K74">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L74" t="str">
         <v>Yes</v>
@@ -3871,7 +3871,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N74">
-        <v>-1969</v>
+        <v>-862</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -3885,31 +3885,31 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>07-01-2026</v>
+        <v>08-01-2026</v>
       </c>
       <c r="D75" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E75">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F75">
-        <v>500</v>
+        <v>192</v>
       </c>
       <c r="G75">
-        <v>472</v>
+        <v>181</v>
       </c>
       <c r="H75">
-        <v>-28</v>
+        <v>-11</v>
       </c>
       <c r="I75">
         <v>0</v>
       </c>
       <c r="J75">
-        <v>-842</v>
+        <v>-744</v>
       </c>
       <c r="K75">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L75" t="str">
         <v>Yes</v>
@@ -3918,7 +3918,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N75">
-        <v>-862</v>
+        <v>-768</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -3935,28 +3935,28 @@
         <v>08-01-2026</v>
       </c>
       <c r="D76" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E76">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F76">
-        <v>192</v>
+        <v>495</v>
       </c>
       <c r="G76">
-        <v>181</v>
+        <v>465</v>
       </c>
       <c r="H76">
-        <v>-11</v>
+        <v>-30</v>
       </c>
       <c r="I76">
         <v>0</v>
       </c>
       <c r="J76">
-        <v>-744</v>
+        <v>-900</v>
       </c>
       <c r="K76">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L76" t="str">
         <v>Yes</v>
@@ -3965,7 +3965,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N76">
-        <v>-768</v>
+        <v>-920</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -3979,40 +3979,40 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>08-01-2026</v>
+        <v>09-01-2026</v>
       </c>
       <c r="D77" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E77">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F77">
-        <v>495</v>
+        <v>190</v>
       </c>
       <c r="G77">
-        <v>465</v>
+        <v>212</v>
       </c>
       <c r="H77">
-        <v>-30</v>
+        <v>23</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>1472</v>
       </c>
       <c r="J77">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K77">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L77" t="str">
         <v>Yes</v>
       </c>
       <c r="M77" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N77">
-        <v>-920</v>
+        <v>1448</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -4029,22 +4029,22 @@
         <v>09-01-2026</v>
       </c>
       <c r="D78" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E78">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F78">
-        <v>190</v>
+        <v>512</v>
       </c>
       <c r="G78">
-        <v>212</v>
+        <v>529</v>
       </c>
       <c r="H78">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I78">
-        <v>1472</v>
+        <v>501</v>
       </c>
       <c r="J78">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N78">
-        <v>1448</v>
+        <v>477</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -4073,28 +4073,28 @@
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>09-01-2026</v>
+        <v>12-01-2026</v>
       </c>
       <c r="D79" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E79">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F79">
-        <v>512</v>
+        <v>202</v>
       </c>
       <c r="G79">
-        <v>529</v>
+        <v>176</v>
       </c>
       <c r="H79">
-        <v>17</v>
+        <v>-27</v>
       </c>
       <c r="I79">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="J79">
-        <v>0</v>
+        <v>-1723</v>
       </c>
       <c r="K79">
         <v>-24</v>
@@ -4103,10 +4103,10 @@
         <v>Yes</v>
       </c>
       <c r="M79" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N79">
-        <v>477</v>
+        <v>-1747</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>12-01-2026</v>
+        <v>13-01-2026</v>
       </c>
       <c r="D80" t="str">
         <v>NiftyPE</v>
@@ -4129,19 +4129,19 @@
         <v>65</v>
       </c>
       <c r="F80">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="G80">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="H80">
-        <v>-27</v>
+        <v>30</v>
       </c>
       <c r="I80">
-        <v>0</v>
+        <v>1957</v>
       </c>
       <c r="J80">
-        <v>-1723</v>
+        <v>0</v>
       </c>
       <c r="K80">
         <v>-24</v>
@@ -4150,10 +4150,10 @@
         <v>Yes</v>
       </c>
       <c r="M80" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N80">
-        <v>-1747</v>
+        <v>1933</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -4170,28 +4170,28 @@
         <v>13-01-2026</v>
       </c>
       <c r="D81" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E81">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F81">
-        <v>190</v>
+        <v>519</v>
       </c>
       <c r="G81">
-        <v>220</v>
+        <v>554</v>
       </c>
       <c r="H81">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I81">
-        <v>1957</v>
+        <v>1050</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L81" t="str">
         <v>Yes</v>
@@ -4200,7 +4200,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N81">
-        <v>1933</v>
+        <v>1030</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -4214,31 +4214,31 @@
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>13-01-2026</v>
+        <v>14-01-2026</v>
       </c>
       <c r="D82" t="str">
-        <v>BankniftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E82">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F82">
-        <v>519</v>
+        <v>756</v>
       </c>
       <c r="G82">
-        <v>554</v>
+        <v>848</v>
       </c>
       <c r="H82">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="I82">
-        <v>1050</v>
+        <v>1842</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L82" t="str">
         <v>Yes</v>
@@ -4247,7 +4247,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N82">
-        <v>1030</v>
+        <v>1818</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -4261,31 +4261,31 @@
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>14-01-2026</v>
+        <v>16-01-2026</v>
       </c>
       <c r="D83" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E83">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F83">
-        <v>756</v>
+        <v>402</v>
       </c>
       <c r="G83">
-        <v>848</v>
+        <v>465</v>
       </c>
       <c r="H83">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="I83">
-        <v>1842</v>
+        <v>1869</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L83" t="str">
         <v>Yes</v>
@@ -4294,7 +4294,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N83">
-        <v>1818</v>
+        <v>1849</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -4311,28 +4311,28 @@
         <v>16-01-2026</v>
       </c>
       <c r="D84" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E84">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F84">
-        <v>402</v>
+        <v>609</v>
       </c>
       <c r="G84">
-        <v>465</v>
+        <v>705</v>
       </c>
       <c r="H84">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="I84">
-        <v>1869</v>
+        <v>1927</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84">
-        <v>-20</v>
+        <v>-90</v>
       </c>
       <c r="L84" t="str">
         <v>Yes</v>
@@ -4341,7 +4341,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N84">
-        <v>1849</v>
+        <v>1837</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -4355,31 +4355,31 @@
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>16-01-2026</v>
+        <v>19-01-2026</v>
       </c>
       <c r="D85" t="str">
-        <v>Sensex CE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E85">
         <v>20</v>
       </c>
       <c r="F85">
-        <v>609</v>
+        <v>782</v>
       </c>
       <c r="G85">
-        <v>705</v>
+        <v>890</v>
       </c>
       <c r="H85">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="I85">
-        <v>1927</v>
+        <v>2165</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85">
-        <v>-90</v>
+        <v>-24</v>
       </c>
       <c r="L85" t="str">
         <v>Yes</v>
@@ -4388,7 +4388,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N85">
-        <v>1837</v>
+        <v>2141</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -4405,37 +4405,37 @@
         <v>19-01-2026</v>
       </c>
       <c r="D86" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E86">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F86">
-        <v>782</v>
+        <v>503</v>
       </c>
       <c r="G86">
-        <v>890</v>
+        <v>541</v>
       </c>
       <c r="H86">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="I86">
-        <v>2165</v>
+        <v>1158</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L86" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M86" t="str">
         <v>Target Hit</v>
       </c>
       <c r="N86">
-        <v>2141</v>
+        <v>1138</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -4449,40 +4449,40 @@
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>19-01-2026</v>
+        <v>20-01-2026</v>
       </c>
       <c r="D87" t="str">
-        <v>BankniftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E87">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F87">
-        <v>503</v>
+        <v>844</v>
       </c>
       <c r="G87">
-        <v>541</v>
+        <v>899</v>
       </c>
       <c r="H87">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="I87">
-        <v>1158</v>
+        <v>1083</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M87" t="str">
         <v>Target Hit</v>
       </c>
       <c r="N87">
-        <v>1138</v>
+        <v>1059</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -4496,40 +4496,40 @@
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>20-01-2026</v>
+        <v>21-01-2026</v>
       </c>
       <c r="D88" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E88">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F88">
-        <v>844</v>
+        <v>498</v>
       </c>
       <c r="G88">
-        <v>899</v>
+        <v>605</v>
       </c>
       <c r="H88">
-        <v>54</v>
+        <v>107</v>
       </c>
       <c r="I88">
-        <v>1083</v>
+        <v>3218</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88">
-        <v>-24</v>
+        <v>-20</v>
       </c>
       <c r="L88" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M88" t="str">
         <v>Target Hit</v>
       </c>
       <c r="N88">
-        <v>1059</v>
+        <v>3198</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -4543,31 +4543,31 @@
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>21-01-2026</v>
+        <v>22-01-2026</v>
       </c>
       <c r="D89" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E89">
         <v>30</v>
       </c>
       <c r="F89">
-        <v>498</v>
+        <v>387</v>
       </c>
       <c r="G89">
-        <v>605</v>
+        <v>474</v>
       </c>
       <c r="H89">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="I89">
-        <v>3218</v>
+        <v>2609</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89">
-        <v>-20</v>
+        <v>-24</v>
       </c>
       <c r="L89" t="str">
         <v>No</v>
@@ -4576,7 +4576,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N89">
-        <v>3198</v>
+        <v>2585</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -4593,28 +4593,28 @@
         <v>22-01-2026</v>
       </c>
       <c r="D90" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E90">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F90">
-        <v>387</v>
+        <v>211</v>
       </c>
       <c r="G90">
-        <v>474</v>
+        <v>271</v>
       </c>
       <c r="H90">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="I90">
-        <v>2609</v>
+        <v>3900</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90">
-        <v>-24</v>
+        <v>-26</v>
       </c>
       <c r="L90" t="str">
         <v>No</v>
@@ -4623,7 +4623,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N90">
-        <v>2585</v>
+        <v>3874</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -4640,28 +4640,28 @@
         <v>22-01-2026</v>
       </c>
       <c r="D91" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E91">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F91">
-        <v>211</v>
+        <v>615</v>
       </c>
       <c r="G91">
-        <v>271</v>
+        <v>734</v>
       </c>
       <c r="H91">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="I91">
-        <v>3900</v>
+        <v>2373</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91">
-        <v>-26</v>
+        <v>-24</v>
       </c>
       <c r="L91" t="str">
         <v>No</v>
@@ -4670,7 +4670,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N91">
-        <v>3874</v>
+        <v>2349</v>
       </c>
       <c r="O91">
         <v>0</v>
@@ -4684,40 +4684,40 @@
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>22-01-2026</v>
+        <v>23-01-2026</v>
       </c>
       <c r="D92" t="str">
-        <v>Sensex CE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E92">
         <v>20</v>
       </c>
       <c r="F92">
-        <v>615</v>
+        <v>782</v>
       </c>
       <c r="G92">
-        <v>734</v>
+        <v>764</v>
       </c>
       <c r="H92">
-        <v>119</v>
+        <v>-18</v>
       </c>
       <c r="I92">
-        <v>2373</v>
+        <v>0</v>
       </c>
       <c r="J92">
-        <v>0</v>
+        <v>-353</v>
       </c>
       <c r="K92">
-        <v>-24</v>
+        <v>-98</v>
       </c>
       <c r="L92" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M92" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N92">
-        <v>2349</v>
+        <v>-451</v>
       </c>
       <c r="O92">
         <v>0</v>
@@ -4734,37 +4734,37 @@
         <v>23-01-2026</v>
       </c>
       <c r="D93" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E93">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F93">
-        <v>782</v>
+        <v>191</v>
       </c>
       <c r="G93">
-        <v>764</v>
+        <v>223</v>
       </c>
       <c r="H93">
-        <v>-18</v>
+        <v>33</v>
       </c>
       <c r="I93">
-        <v>0</v>
+        <v>2122</v>
       </c>
       <c r="J93">
-        <v>-353</v>
+        <v>0</v>
       </c>
       <c r="K93">
-        <v>-98</v>
+        <v>-105</v>
       </c>
       <c r="L93" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M93" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N93">
-        <v>-451</v>
+        <v>2017</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -4781,37 +4781,37 @@
         <v>23-01-2026</v>
       </c>
       <c r="D94" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E94">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F94">
-        <v>191</v>
+        <v>471</v>
       </c>
       <c r="G94">
-        <v>223</v>
+        <v>500</v>
       </c>
       <c r="H94">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I94">
-        <v>2122</v>
+        <v>861</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94">
-        <v>-105</v>
+        <v>-80</v>
       </c>
       <c r="L94" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M94" t="str">
         <v>Target Hit</v>
       </c>
       <c r="N94">
-        <v>2017</v>
+        <v>781</v>
       </c>
       <c r="O94">
         <v>0</v>
@@ -4825,40 +4825,40 @@
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>23-01-2026</v>
+        <v>29-01-2026</v>
       </c>
       <c r="D95" t="str">
-        <v>BankniftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E95">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F95">
-        <v>471</v>
+        <v>784</v>
       </c>
       <c r="G95">
-        <v>500</v>
+        <v>690</v>
       </c>
       <c r="H95">
-        <v>29</v>
+        <v>-94</v>
       </c>
       <c r="I95">
-        <v>861</v>
+        <v>0</v>
       </c>
       <c r="J95">
-        <v>0</v>
+        <v>-1886</v>
       </c>
       <c r="K95">
-        <v>-80</v>
+        <v>-25</v>
       </c>
       <c r="L95" t="str">
         <v>Yes</v>
       </c>
       <c r="M95" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N95">
-        <v>781</v>
+        <v>-1911</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -4872,28 +4872,28 @@
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>29-01-2026</v>
+        <v>30-01-2026</v>
       </c>
       <c r="D96" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E96">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F96">
-        <v>784</v>
+        <v>509</v>
       </c>
       <c r="G96">
-        <v>690</v>
+        <v>494</v>
       </c>
       <c r="H96">
-        <v>-94</v>
+        <v>-15</v>
       </c>
       <c r="I96">
         <v>0</v>
       </c>
       <c r="J96">
-        <v>-1886</v>
+        <v>-454</v>
       </c>
       <c r="K96">
         <v>-25</v>
@@ -4905,7 +4905,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N96">
-        <v>-1911</v>
+        <v>-479</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -4919,28 +4919,28 @@
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>30-01-2026</v>
+        <v>05-02-2026</v>
       </c>
       <c r="D97" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E97">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F97">
-        <v>509</v>
+        <v>202</v>
       </c>
       <c r="G97">
-        <v>494</v>
+        <v>242</v>
       </c>
       <c r="H97">
-        <v>-15</v>
+        <v>39</v>
       </c>
       <c r="I97">
-        <v>0</v>
+        <v>2551</v>
       </c>
       <c r="J97">
-        <v>-454</v>
+        <v>0</v>
       </c>
       <c r="K97">
         <v>-25</v>
@@ -4949,10 +4949,10 @@
         <v>Yes</v>
       </c>
       <c r="M97" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N97">
-        <v>-479</v>
+        <v>2526</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>05-02-2026</v>
       </c>
       <c r="D98" t="str">
-        <v>NiftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E98">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F98">
-        <v>202</v>
+        <v>808</v>
       </c>
       <c r="G98">
-        <v>242</v>
+        <v>879</v>
       </c>
       <c r="H98">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="I98">
-        <v>2551</v>
+        <v>1428</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98">
-        <v>-25</v>
+        <v>-22</v>
       </c>
       <c r="L98" t="str">
         <v>Yes</v>
@@ -4999,7 +4999,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N98">
-        <v>2526</v>
+        <v>1406</v>
       </c>
       <c r="O98">
         <v>0</v>
@@ -5013,7 +5013,7 @@
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>05-02-2026</v>
+        <v>06-02-2026</v>
       </c>
       <c r="D99" t="str">
         <v>Sensex PE</v>
@@ -5022,31 +5022,31 @@
         <v>20</v>
       </c>
       <c r="F99">
-        <v>808</v>
+        <v>825</v>
       </c>
       <c r="G99">
-        <v>879</v>
+        <v>773</v>
       </c>
       <c r="H99">
-        <v>71</v>
+        <v>-52</v>
       </c>
       <c r="I99">
-        <v>1428</v>
+        <v>0</v>
       </c>
       <c r="J99">
-        <v>0</v>
+        <v>-1043</v>
       </c>
       <c r="K99">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="L99" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M99" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N99">
-        <v>1406</v>
+        <v>-1063</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -5060,40 +5060,40 @@
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>06-02-2026</v>
+        <v>09-02-2026</v>
       </c>
       <c r="D100" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E100">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F100">
-        <v>825</v>
+        <v>205</v>
       </c>
       <c r="G100">
-        <v>773</v>
+        <v>241</v>
       </c>
       <c r="H100">
-        <v>-52</v>
+        <v>36</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>2360</v>
       </c>
       <c r="J100">
-        <v>-1043</v>
+        <v>0</v>
       </c>
       <c r="K100">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="L100" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M100" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N100">
-        <v>-1063</v>
+        <v>2335</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -5110,37 +5110,37 @@
         <v>09-02-2026</v>
       </c>
       <c r="D101" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E101">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F101">
-        <v>205</v>
+        <v>408</v>
       </c>
       <c r="G101">
-        <v>241</v>
+        <v>393</v>
       </c>
       <c r="H101">
-        <v>36</v>
+        <v>-14</v>
       </c>
       <c r="I101">
-        <v>2360</v>
+        <v>0</v>
       </c>
       <c r="J101">
-        <v>0</v>
+        <v>-431</v>
       </c>
       <c r="K101">
         <v>-25</v>
       </c>
       <c r="L101" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M101" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N101">
-        <v>2335</v>
+        <v>-456</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -5154,40 +5154,40 @@
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>09-02-2026</v>
+        <v>10-02-2026</v>
       </c>
       <c r="D102" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E102">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F102">
-        <v>408</v>
+        <v>203</v>
       </c>
       <c r="G102">
-        <v>393</v>
+        <v>205</v>
       </c>
       <c r="H102">
-        <v>-14</v>
+        <v>2</v>
       </c>
       <c r="I102">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="J102">
-        <v>-431</v>
+        <v>0</v>
       </c>
       <c r="K102">
         <v>-25</v>
       </c>
       <c r="L102" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M102" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N102">
-        <v>-456</v>
+        <v>82</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -5204,22 +5204,22 @@
         <v>10-02-2026</v>
       </c>
       <c r="D103" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E103">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F103">
-        <v>203</v>
+        <v>599</v>
       </c>
       <c r="G103">
-        <v>205</v>
+        <v>626</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I103">
-        <v>107</v>
+        <v>538</v>
       </c>
       <c r="J103">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N103">
-        <v>82</v>
+        <v>513</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -5251,22 +5251,22 @@
         <v>10-02-2026</v>
       </c>
       <c r="D104" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E104">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F104">
-        <v>599</v>
+        <v>516</v>
       </c>
       <c r="G104">
-        <v>626</v>
+        <v>543</v>
       </c>
       <c r="H104">
         <v>27</v>
       </c>
       <c r="I104">
-        <v>538</v>
+        <v>805</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -5281,7 +5281,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N104">
-        <v>513</v>
+        <v>780</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -5295,40 +5295,40 @@
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>10-02-2026</v>
+        <v>11-02-2026</v>
       </c>
       <c r="D105" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E105">
         <v>30</v>
       </c>
       <c r="F105">
-        <v>516</v>
+        <v>415</v>
       </c>
       <c r="G105">
-        <v>543</v>
+        <v>364</v>
       </c>
       <c r="H105">
-        <v>27</v>
+        <v>-52</v>
       </c>
       <c r="I105">
-        <v>805</v>
+        <v>0</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>-1551</v>
       </c>
       <c r="K105">
         <v>-25</v>
       </c>
       <c r="L105" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M105" t="str">
-        <v>Target Hit</v>
+        <v>Own Trade</v>
       </c>
       <c r="N105">
-        <v>780</v>
+        <v>-1576</v>
       </c>
       <c r="O105">
         <v>0</v>
@@ -5342,40 +5342,40 @@
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>11-02-2026</v>
+        <v>12-02-2026</v>
       </c>
       <c r="D106" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E106">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F106">
-        <v>415</v>
+        <v>780</v>
       </c>
       <c r="G106">
-        <v>364</v>
+        <v>819</v>
       </c>
       <c r="H106">
-        <v>-52</v>
+        <v>39</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>779</v>
       </c>
       <c r="J106">
-        <v>-1551</v>
+        <v>0</v>
       </c>
       <c r="K106">
         <v>-25</v>
       </c>
       <c r="L106" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M106" t="str">
-        <v>Own Trade</v>
+        <v>Target Hit</v>
       </c>
       <c r="N106">
-        <v>-1576</v>
+        <v>754</v>
       </c>
       <c r="O106">
         <v>0</v>
@@ -5392,22 +5392,22 @@
         <v>12-02-2026</v>
       </c>
       <c r="D107" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E107">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F107">
-        <v>780</v>
+        <v>486</v>
       </c>
       <c r="G107">
-        <v>819</v>
+        <v>497</v>
       </c>
       <c r="H107">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="I107">
-        <v>779</v>
+        <v>334</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -5422,7 +5422,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N107">
-        <v>754</v>
+        <v>309</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -5436,25 +5436,25 @@
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>12-02-2026</v>
+        <v>13-02-2026</v>
       </c>
       <c r="D108" t="str">
-        <v>BankniftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E108">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F108">
-        <v>486</v>
+        <v>818</v>
       </c>
       <c r="G108">
-        <v>497</v>
+        <v>925</v>
       </c>
       <c r="H108">
-        <v>11</v>
+        <v>107</v>
       </c>
       <c r="I108">
-        <v>334</v>
+        <v>2141</v>
       </c>
       <c r="J108">
         <v>0</v>
@@ -5469,7 +5469,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N108">
-        <v>309</v>
+        <v>2116</v>
       </c>
       <c r="O108">
         <v>0</v>
@@ -5483,7 +5483,7 @@
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>13-02-2026</v>
+        <v>18-02-2026</v>
       </c>
       <c r="D109" t="str">
         <v>Sensex PE</v>
@@ -5492,19 +5492,19 @@
         <v>20</v>
       </c>
       <c r="F109">
-        <v>818</v>
+        <v>681</v>
       </c>
       <c r="G109">
-        <v>925</v>
+        <v>581</v>
       </c>
       <c r="H109">
-        <v>107</v>
+        <v>-100</v>
       </c>
       <c r="I109">
-        <v>2141</v>
+        <v>0</v>
       </c>
       <c r="J109">
-        <v>0</v>
+        <v>-2007</v>
       </c>
       <c r="K109">
         <v>-25</v>
@@ -5513,10 +5513,10 @@
         <v>Yes</v>
       </c>
       <c r="M109" t="str">
-        <v>Target Hit</v>
+        <v/>
       </c>
       <c r="N109">
-        <v>2116</v>
+        <v>-2032</v>
       </c>
       <c r="O109">
         <v>0</v>
@@ -5533,37 +5533,37 @@
         <v>18-02-2026</v>
       </c>
       <c r="D110" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E110">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F110">
-        <v>681</v>
+        <v>375</v>
       </c>
       <c r="G110">
-        <v>581</v>
+        <v>418</v>
       </c>
       <c r="H110">
-        <v>-100</v>
+        <v>43</v>
       </c>
       <c r="I110">
-        <v>0</v>
+        <v>1285</v>
       </c>
       <c r="J110">
-        <v>-2007</v>
+        <v>0</v>
       </c>
       <c r="K110">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="L110" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="M110" t="str">
         <v/>
       </c>
       <c r="N110">
-        <v>-2032</v>
+        <v>1257</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -5577,25 +5577,25 @@
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>18-02-2026</v>
+        <v>19-02-2026</v>
       </c>
       <c r="D111" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E111">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F111">
-        <v>375</v>
+        <v>717</v>
       </c>
       <c r="G111">
-        <v>418</v>
+        <v>958</v>
       </c>
       <c r="H111">
-        <v>43</v>
+        <v>241</v>
       </c>
       <c r="I111">
-        <v>1285</v>
+        <v>4828</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -5604,13 +5604,13 @@
         <v>-28</v>
       </c>
       <c r="L111" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="M111" t="str">
-        <v/>
+        <v>Target Hit</v>
       </c>
       <c r="N111">
-        <v>1257</v>
+        <v>4800</v>
       </c>
       <c r="O111">
         <v>0</v>
@@ -5624,28 +5624,28 @@
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>19-02-2026</v>
+        <v>20-02-2026</v>
       </c>
       <c r="D112" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E112">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F112">
-        <v>717</v>
+        <v>398</v>
       </c>
       <c r="G112">
-        <v>958</v>
+        <v>343</v>
       </c>
       <c r="H112">
-        <v>241</v>
+        <v>-55</v>
       </c>
       <c r="I112">
-        <v>4828</v>
+        <v>0</v>
       </c>
       <c r="J112">
-        <v>0</v>
+        <v>-1649</v>
       </c>
       <c r="K112">
         <v>-28</v>
@@ -5654,10 +5654,10 @@
         <v>Yes</v>
       </c>
       <c r="M112" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N112">
-        <v>4800</v>
+        <v>-1677</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -5671,40 +5671,40 @@
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>20-02-2026</v>
+        <v>24-02-2026</v>
       </c>
       <c r="D113" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E113">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F113">
-        <v>398</v>
+        <v>683</v>
       </c>
       <c r="G113">
-        <v>343</v>
+        <v>828</v>
       </c>
       <c r="H113">
-        <v>-55</v>
+        <v>145</v>
       </c>
       <c r="I113">
-        <v>0</v>
+        <v>2898</v>
       </c>
       <c r="J113">
-        <v>-1649</v>
+        <v>0</v>
       </c>
       <c r="K113">
-        <v>-28</v>
+        <v>-27</v>
       </c>
       <c r="L113" t="str">
         <v>Yes</v>
       </c>
       <c r="M113" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N113">
-        <v>-1677</v>
+        <v>2871</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -5721,22 +5721,22 @@
         <v>24-02-2026</v>
       </c>
       <c r="D114" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E114">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F114">
-        <v>683</v>
+        <v>208</v>
       </c>
       <c r="G114">
-        <v>828</v>
+        <v>244</v>
       </c>
       <c r="H114">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="I114">
-        <v>2898</v>
+        <v>2386</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -5751,7 +5751,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N114">
-        <v>2871</v>
+        <v>2359</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -5765,25 +5765,25 @@
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>24-02-2026</v>
+        <v>25-02-2026</v>
       </c>
       <c r="D115" t="str">
-        <v>NiftyPE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E115">
         <v>65</v>
       </c>
       <c r="F115">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G115">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="H115">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I115">
-        <v>2386</v>
+        <v>1898</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -5798,7 +5798,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N115">
-        <v>2359</v>
+        <v>1871</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -5821,19 +5821,19 @@
         <v>65</v>
       </c>
       <c r="F116">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="G116">
-        <v>237</v>
+        <v>174</v>
       </c>
       <c r="H116">
-        <v>29</v>
+        <v>-21</v>
       </c>
       <c r="I116">
-        <v>1898</v>
+        <v>0</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>-1342</v>
       </c>
       <c r="K116">
         <v>-27</v>
@@ -5845,7 +5845,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N116">
-        <v>1871</v>
+        <v>-1369</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -5862,25 +5862,25 @@
         <v>25-02-2026</v>
       </c>
       <c r="D117" t="str">
-        <v>NiftyCE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E117">
         <v>65</v>
       </c>
       <c r="F117">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G117">
-        <v>174</v>
+        <v>240</v>
       </c>
       <c r="H117">
-        <v>-21</v>
+        <v>41</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>2685</v>
       </c>
       <c r="J117">
-        <v>-1342</v>
+        <v>0</v>
       </c>
       <c r="K117">
         <v>-27</v>
@@ -5892,7 +5892,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N117">
-        <v>-1369</v>
+        <v>2658</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -5906,7 +5906,7 @@
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>25-02-2026</v>
+        <v>27-02-2026</v>
       </c>
       <c r="D118" t="str">
         <v>NiftyPE</v>
@@ -5915,16 +5915,16 @@
         <v>65</v>
       </c>
       <c r="F118">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="G118">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="H118">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="I118">
-        <v>2685</v>
+        <v>1456</v>
       </c>
       <c r="J118">
         <v>0</v>
@@ -5939,7 +5939,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N118">
-        <v>2658</v>
+        <v>1429</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -5953,7 +5953,7 @@
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>27-02-2026</v>
+        <v>02-03-2026</v>
       </c>
       <c r="D119" t="str">
         <v>NiftyPE</v>
@@ -5962,16 +5962,16 @@
         <v>65</v>
       </c>
       <c r="F119">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="G119">
-        <v>214</v>
+        <v>240</v>
       </c>
       <c r="H119">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I119">
-        <v>1456</v>
+        <v>4986</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -5986,7 +5986,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N119">
-        <v>1429</v>
+        <v>4959</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -6000,25 +6000,25 @@
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>02-03-2026</v>
+        <v>05-03-2026</v>
       </c>
       <c r="D120" t="str">
-        <v>NiftyPE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E120">
         <v>65</v>
       </c>
       <c r="F120">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="G120">
-        <v>240</v>
+        <v>216</v>
       </c>
       <c r="H120">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I120">
-        <v>4986</v>
+        <v>1843</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6033,7 +6033,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N120">
-        <v>4959</v>
+        <v>1816</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -6047,31 +6047,31 @@
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>05-03-2026</v>
+        <v>11-03-2026</v>
       </c>
       <c r="D121" t="str">
-        <v>NiftyCE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E121">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F121">
-        <v>188</v>
+        <v>495</v>
       </c>
       <c r="G121">
-        <v>216</v>
+        <v>598</v>
       </c>
       <c r="H121">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="I121">
-        <v>1843</v>
+        <v>3096</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121">
-        <v>-27</v>
+        <v>-32</v>
       </c>
       <c r="L121" t="str">
         <v>Yes</v>
@@ -6080,7 +6080,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N121">
-        <v>1816</v>
+        <v>3064</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -6097,28 +6097,28 @@
         <v>11-03-2026</v>
       </c>
       <c r="D122" t="str">
-        <v>BankniftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E122">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F122">
-        <v>495</v>
+        <v>705</v>
       </c>
       <c r="G122">
-        <v>598</v>
+        <v>817</v>
       </c>
       <c r="H122">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="I122">
-        <v>3096</v>
+        <v>2249</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122">
-        <v>-32</v>
+        <v>-30</v>
       </c>
       <c r="L122" t="str">
         <v>Yes</v>
@@ -6127,7 +6127,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N122">
-        <v>3064</v>
+        <v>2219</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -6141,40 +6141,40 @@
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>11-03-2026</v>
+        <v>13-03-2026</v>
       </c>
       <c r="D123" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E123">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F123">
-        <v>705</v>
+        <v>543</v>
       </c>
       <c r="G123">
-        <v>817</v>
+        <v>474</v>
       </c>
       <c r="H123">
-        <v>112</v>
+        <v>-69</v>
       </c>
       <c r="I123">
-        <v>2249</v>
+        <v>0</v>
       </c>
       <c r="J123">
-        <v>0</v>
+        <v>-2076</v>
       </c>
       <c r="K123">
-        <v>-30</v>
+        <v>-27</v>
       </c>
       <c r="L123" t="str">
         <v>Yes</v>
       </c>
       <c r="M123" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N123">
-        <v>2219</v>
+        <v>-2103</v>
       </c>
       <c r="O123">
         <v>0</v>
@@ -6191,37 +6191,37 @@
         <v>13-03-2026</v>
       </c>
       <c r="D124" t="str">
-        <v>BankniftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E124">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F124">
-        <v>543</v>
+        <v>711</v>
       </c>
       <c r="G124">
-        <v>474</v>
+        <v>712</v>
       </c>
       <c r="H124">
-        <v>-69</v>
+        <v>1</v>
       </c>
       <c r="I124">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J124">
-        <v>-2076</v>
+        <v>0</v>
       </c>
       <c r="K124">
-        <v>-27</v>
+        <v>-20</v>
       </c>
       <c r="L124" t="str">
         <v>Yes</v>
       </c>
       <c r="M124" t="str">
-        <v>Stop Loss Hit</v>
+        <v/>
       </c>
       <c r="N124">
-        <v>-2103</v>
+        <v>5</v>
       </c>
       <c r="O124">
         <v>0</v>
@@ -6235,40 +6235,40 @@
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>13-03-2026</v>
+        <v>18-03-2026</v>
       </c>
       <c r="D125" t="str">
-        <v>Sensex PE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E125">
         <v>20</v>
       </c>
       <c r="F125">
-        <v>711</v>
+        <v>695</v>
       </c>
       <c r="G125">
-        <v>712</v>
+        <v>622</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>-74</v>
       </c>
       <c r="I125">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J125">
-        <v>0</v>
+        <v>-1471</v>
       </c>
       <c r="K125">
-        <v>-20</v>
+        <v>-18</v>
       </c>
       <c r="L125" t="str">
         <v>Yes</v>
       </c>
       <c r="M125" t="str">
-        <v/>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N125">
-        <v>5</v>
+        <v>-1489</v>
       </c>
       <c r="O125">
         <v>0</v>
@@ -6285,25 +6285,25 @@
         <v>18-03-2026</v>
       </c>
       <c r="D126" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E126">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F126">
-        <v>695</v>
+        <v>492</v>
       </c>
       <c r="G126">
-        <v>622</v>
+        <v>433</v>
       </c>
       <c r="H126">
-        <v>-74</v>
+        <v>-59</v>
       </c>
       <c r="I126">
         <v>0</v>
       </c>
       <c r="J126">
-        <v>-1471</v>
+        <v>-1766</v>
       </c>
       <c r="K126">
         <v>-18</v>
@@ -6315,7 +6315,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N126">
-        <v>-1489</v>
+        <v>-1784</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -6332,28 +6332,28 @@
         <v>18-03-2026</v>
       </c>
       <c r="D127" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E127">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F127">
-        <v>492</v>
+        <v>213</v>
       </c>
       <c r="G127">
-        <v>433</v>
+        <v>183</v>
       </c>
       <c r="H127">
-        <v>-59</v>
+        <v>-29</v>
       </c>
       <c r="I127">
         <v>0</v>
       </c>
       <c r="J127">
-        <v>-1766</v>
+        <v>-1892</v>
       </c>
       <c r="K127">
-        <v>-18</v>
+        <v>-20</v>
       </c>
       <c r="L127" t="str">
         <v>Yes</v>
@@ -6362,7 +6362,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N127">
-        <v>-1784</v>
+        <v>-1912</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -6376,28 +6376,28 @@
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>18-03-2026</v>
+        <v>19-03-2026</v>
       </c>
       <c r="D128" t="str">
-        <v>NiftyCE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E128">
         <v>65</v>
       </c>
       <c r="F128">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="G128">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="H128">
-        <v>-29</v>
+        <v>23</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>1472</v>
       </c>
       <c r="J128">
-        <v>-1892</v>
+        <v>0</v>
       </c>
       <c r="K128">
         <v>-20</v>
@@ -6406,10 +6406,10 @@
         <v>Yes</v>
       </c>
       <c r="M128" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N128">
-        <v>-1912</v>
+        <v>1452</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -6423,28 +6423,28 @@
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>19-03-2026</v>
+        <v>23-03-2026</v>
       </c>
       <c r="D129" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E129">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="F129">
-        <v>200</v>
+        <v>526</v>
       </c>
       <c r="G129">
-        <v>222</v>
+        <v>457</v>
       </c>
       <c r="H129">
-        <v>23</v>
+        <v>-69</v>
       </c>
       <c r="I129">
-        <v>1472</v>
+        <v>0</v>
       </c>
       <c r="J129">
-        <v>0</v>
+        <v>-2081</v>
       </c>
       <c r="K129">
         <v>-20</v>
@@ -6453,10 +6453,10 @@
         <v>Yes</v>
       </c>
       <c r="M129" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N129">
-        <v>1452</v>
+        <v>-2101</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -6470,40 +6470,40 @@
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>23-03-2026</v>
+        <v>25-03-2026</v>
       </c>
       <c r="D130" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E130">
         <v>30</v>
       </c>
       <c r="F130">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="G130">
-        <v>457</v>
+        <v>534</v>
       </c>
       <c r="H130">
-        <v>-69</v>
+        <v>30</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="J130">
-        <v>-2081</v>
+        <v>0</v>
       </c>
       <c r="K130">
-        <v>-20</v>
+        <v>-27</v>
       </c>
       <c r="L130" t="str">
         <v>Yes</v>
       </c>
       <c r="M130" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N130">
-        <v>-2101</v>
+        <v>882</v>
       </c>
       <c r="O130">
         <v>0</v>
@@ -6520,22 +6520,22 @@
         <v>25-03-2026</v>
       </c>
       <c r="D131" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E131">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="F131">
-        <v>504</v>
+        <v>193</v>
       </c>
       <c r="G131">
-        <v>534</v>
+        <v>223</v>
       </c>
       <c r="H131">
         <v>30</v>
       </c>
       <c r="I131">
-        <v>909</v>
+        <v>1957</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -6550,7 +6550,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N131">
-        <v>882</v>
+        <v>1930</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -6567,22 +6567,22 @@
         <v>25-03-2026</v>
       </c>
       <c r="D132" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E132">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F132">
-        <v>193</v>
+        <v>664</v>
       </c>
       <c r="G132">
-        <v>223</v>
+        <v>821</v>
       </c>
       <c r="H132">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="I132">
-        <v>1957</v>
+        <v>3139</v>
       </c>
       <c r="J132">
         <v>0</v>
@@ -6597,7 +6597,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N132">
-        <v>1930</v>
+        <v>3112</v>
       </c>
       <c r="O132">
         <v>0</v>
@@ -6611,28 +6611,28 @@
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>25-03-2026</v>
+        <v>27-03-2026</v>
       </c>
       <c r="D133" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E133">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F133">
-        <v>664</v>
+        <v>528</v>
       </c>
       <c r="G133">
-        <v>821</v>
+        <v>459</v>
       </c>
       <c r="H133">
-        <v>157</v>
+        <v>-69</v>
       </c>
       <c r="I133">
-        <v>3139</v>
+        <v>0</v>
       </c>
       <c r="J133">
-        <v>0</v>
+        <v>-2082</v>
       </c>
       <c r="K133">
         <v>-27</v>
@@ -6641,10 +6641,10 @@
         <v>Yes</v>
       </c>
       <c r="M133" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N133">
-        <v>3112</v>
+        <v>-2109</v>
       </c>
       <c r="O133">
         <v>0</v>
@@ -6658,40 +6658,40 @@
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>27-03-2026</v>
+        <v>08-04-2026</v>
       </c>
       <c r="D134" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E134">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F134">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="G134">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="H134">
-        <v>-69</v>
+        <v>-54</v>
       </c>
       <c r="I134">
         <v>0</v>
       </c>
       <c r="J134">
-        <v>-2082</v>
+        <v>-3247</v>
       </c>
       <c r="K134">
-        <v>-27</v>
+        <v>-105</v>
       </c>
       <c r="L134" t="str">
         <v>Yes</v>
       </c>
       <c r="M134" t="str">
-        <v>Stop Loss Hit</v>
+        <v>2 Lot 1L invested</v>
       </c>
       <c r="N134">
-        <v>-2109</v>
+        <v>-3352</v>
       </c>
       <c r="O134">
         <v>0</v>
@@ -6705,40 +6705,40 @@
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>08-04-2026</v>
+        <v>10-04-2026</v>
       </c>
       <c r="D135" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E135">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="F135">
-        <v>484</v>
+        <v>188</v>
       </c>
       <c r="G135">
-        <v>430</v>
+        <v>159</v>
       </c>
       <c r="H135">
-        <v>-54</v>
+        <v>-29</v>
       </c>
       <c r="I135">
         <v>0</v>
       </c>
       <c r="J135">
-        <v>-3247</v>
+        <v>-3790</v>
       </c>
       <c r="K135">
-        <v>-105</v>
+        <v>-102</v>
       </c>
       <c r="L135" t="str">
         <v>Yes</v>
       </c>
       <c r="M135" t="str">
-        <v>2 Lot 1L invested</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N135">
-        <v>-3352</v>
+        <v>-3892</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>10-04-2026</v>
+        <v>16-04-2026</v>
       </c>
       <c r="D136" t="str">
         <v>NiftyCE</v>
@@ -6761,22 +6761,22 @@
         <v>130</v>
       </c>
       <c r="F136">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="G136">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="H136">
-        <v>-29</v>
+        <v>-37</v>
       </c>
       <c r="I136">
         <v>0</v>
       </c>
       <c r="J136">
-        <v>-3790</v>
+        <v>-4817</v>
       </c>
       <c r="K136">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="L136" t="str">
         <v>Yes</v>
@@ -6785,7 +6785,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N136">
-        <v>-3892</v>
+        <v>-4917</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -6802,37 +6802,37 @@
         <v>16-04-2026</v>
       </c>
       <c r="D137" t="str">
-        <v>NiftyCE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E137">
         <v>130</v>
       </c>
       <c r="F137">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G137">
-        <v>169</v>
+        <v>218</v>
       </c>
       <c r="H137">
-        <v>-37</v>
+        <v>14</v>
       </c>
       <c r="I137">
-        <v>0</v>
+        <v>1879</v>
       </c>
       <c r="J137">
-        <v>-4817</v>
+        <v>0</v>
       </c>
       <c r="K137">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="L137" t="str">
         <v>Yes</v>
       </c>
       <c r="M137" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N137">
-        <v>-4917</v>
+        <v>1799</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -6849,37 +6849,37 @@
         <v>16-04-2026</v>
       </c>
       <c r="D138" t="str">
-        <v>NiftyPE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E138">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="F138">
-        <v>203</v>
+        <v>597</v>
       </c>
       <c r="G138">
-        <v>218</v>
+        <v>480</v>
       </c>
       <c r="H138">
-        <v>14</v>
+        <v>-117</v>
       </c>
       <c r="I138">
-        <v>1879</v>
+        <v>0</v>
       </c>
       <c r="J138">
-        <v>0</v>
+        <v>-4684</v>
       </c>
       <c r="K138">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="L138" t="str">
         <v>Yes</v>
       </c>
       <c r="M138" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N138">
-        <v>1799</v>
+        <v>-4784</v>
       </c>
       <c r="O138">
         <v>0</v>
@@ -6896,25 +6896,25 @@
         <v>16-04-2026</v>
       </c>
       <c r="D139" t="str">
-        <v>Sensex CE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E139">
         <v>40</v>
       </c>
       <c r="F139">
-        <v>597</v>
+        <v>716</v>
       </c>
       <c r="G139">
-        <v>480</v>
+        <v>813</v>
       </c>
       <c r="H139">
-        <v>-117</v>
+        <v>97</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>3886</v>
       </c>
       <c r="J139">
-        <v>-4684</v>
+        <v>0</v>
       </c>
       <c r="K139">
         <v>-100</v>
@@ -6923,10 +6923,10 @@
         <v>Yes</v>
       </c>
       <c r="M139" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N139">
-        <v>-4784</v>
+        <v>3786</v>
       </c>
       <c r="O139">
         <v>0</v>
@@ -6943,25 +6943,25 @@
         <v>16-04-2026</v>
       </c>
       <c r="D140" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyBullCE</v>
       </c>
       <c r="E140">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F140">
-        <v>716</v>
+        <v>264</v>
       </c>
       <c r="G140">
-        <v>813</v>
+        <v>224</v>
       </c>
       <c r="H140">
-        <v>97</v>
+        <v>-40</v>
       </c>
       <c r="I140">
-        <v>3886</v>
+        <v>0</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>-2610</v>
       </c>
       <c r="K140">
         <v>-100</v>
@@ -6970,10 +6970,10 @@
         <v>Yes</v>
       </c>
       <c r="M140" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N140">
-        <v>3786</v>
+        <v>-2710</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -6990,25 +6990,25 @@
         <v>16-04-2026</v>
       </c>
       <c r="D141" t="str">
-        <v>NiftyBullCE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E141">
         <v>65</v>
       </c>
       <c r="F141">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G141">
-        <v>224</v>
+        <v>286</v>
       </c>
       <c r="H141">
-        <v>-40</v>
+        <v>30</v>
       </c>
       <c r="I141">
-        <v>0</v>
+        <v>1953</v>
       </c>
       <c r="J141">
-        <v>-2610</v>
+        <v>0</v>
       </c>
       <c r="K141">
         <v>-100</v>
@@ -7017,10 +7017,10 @@
         <v>Yes</v>
       </c>
       <c r="M141" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N141">
-        <v>-2710</v>
+        <v>1853</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -7034,28 +7034,28 @@
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>16-04-2026</v>
+        <v>17-04-2026</v>
       </c>
       <c r="D142" t="str">
-        <v>NiftyBullPE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E142">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="F142">
-        <v>256</v>
+        <v>190</v>
       </c>
       <c r="G142">
-        <v>286</v>
+        <v>178</v>
       </c>
       <c r="H142">
-        <v>30</v>
+        <v>-12</v>
       </c>
       <c r="I142">
-        <v>1953</v>
+        <v>0</v>
       </c>
       <c r="J142">
-        <v>0</v>
+        <v>-1573</v>
       </c>
       <c r="K142">
         <v>-100</v>
@@ -7064,10 +7064,10 @@
         <v>Yes</v>
       </c>
       <c r="M142" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N142">
-        <v>1853</v>
+        <v>-1673</v>
       </c>
       <c r="O142">
         <v>0</v>
@@ -7084,25 +7084,25 @@
         <v>17-04-2026</v>
       </c>
       <c r="D143" t="str">
-        <v>NiftyCE</v>
+        <v>NiftyBullCE</v>
       </c>
       <c r="E143">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="F143">
-        <v>190</v>
+        <v>252</v>
       </c>
       <c r="G143">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="H143">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="I143">
         <v>0</v>
       </c>
       <c r="J143">
-        <v>-1573</v>
+        <v>-926</v>
       </c>
       <c r="K143">
         <v>-100</v>
@@ -7114,7 +7114,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N143">
-        <v>-1673</v>
+        <v>-1026</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -7128,28 +7128,28 @@
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>17-04-2026</v>
+        <v>20-04-2026</v>
       </c>
       <c r="D144" t="str">
-        <v>NiftyBullCE</v>
+        <v>SensexBullCE</v>
       </c>
       <c r="E144">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F144">
-        <v>252</v>
+        <v>684</v>
       </c>
       <c r="G144">
-        <v>238</v>
+        <v>676</v>
       </c>
       <c r="H144">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="I144">
         <v>0</v>
       </c>
       <c r="J144">
-        <v>-926</v>
+        <v>-168</v>
       </c>
       <c r="K144">
         <v>-100</v>
@@ -7161,7 +7161,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N144">
-        <v>-1026</v>
+        <v>-268</v>
       </c>
       <c r="O144">
         <v>0</v>
@@ -7178,25 +7178,25 @@
         <v>20-04-2026</v>
       </c>
       <c r="D145" t="str">
-        <v>SensexBullCE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E145">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F145">
-        <v>684</v>
+        <v>254</v>
       </c>
       <c r="G145">
-        <v>676</v>
+        <v>219</v>
       </c>
       <c r="H145">
-        <v>-8</v>
+        <v>-35</v>
       </c>
       <c r="I145">
         <v>0</v>
       </c>
       <c r="J145">
-        <v>-168</v>
+        <v>-2285</v>
       </c>
       <c r="K145">
         <v>-100</v>
@@ -7208,7 +7208,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N145">
-        <v>-268</v>
+        <v>-2385</v>
       </c>
       <c r="O145">
         <v>0</v>
@@ -7225,37 +7225,37 @@
         <v>20-04-2026</v>
       </c>
       <c r="D146" t="str">
-        <v>NiftyBullPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E146">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F146">
-        <v>254</v>
+        <v>830</v>
       </c>
       <c r="G146">
-        <v>219</v>
+        <v>932</v>
       </c>
       <c r="H146">
-        <v>-35</v>
+        <v>102</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>6114</v>
       </c>
       <c r="J146">
-        <v>-2285</v>
+        <v>0</v>
       </c>
       <c r="K146">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="L146" t="str">
         <v>Yes</v>
       </c>
       <c r="M146" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N146">
-        <v>-2385</v>
+        <v>5964</v>
       </c>
       <c r="O146">
         <v>0</v>
@@ -7272,25 +7272,25 @@
         <v>20-04-2026</v>
       </c>
       <c r="D147" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E147">
         <v>60</v>
       </c>
       <c r="F147">
-        <v>830</v>
+        <v>780</v>
       </c>
       <c r="G147">
-        <v>932</v>
+        <v>724</v>
       </c>
       <c r="H147">
-        <v>102</v>
+        <v>-56</v>
       </c>
       <c r="I147">
-        <v>6114</v>
+        <v>0</v>
       </c>
       <c r="J147">
-        <v>0</v>
+        <v>-3345</v>
       </c>
       <c r="K147">
         <v>-150</v>
@@ -7299,10 +7299,10 @@
         <v>Yes</v>
       </c>
       <c r="M147" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N147">
-        <v>5964</v>
+        <v>-3495</v>
       </c>
       <c r="O147">
         <v>0</v>
@@ -7316,40 +7316,40 @@
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>20-04-2026</v>
+        <v>21-04-2026</v>
       </c>
       <c r="D148" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E148">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F148">
-        <v>780</v>
+        <v>584</v>
       </c>
       <c r="G148">
-        <v>724</v>
+        <v>628</v>
       </c>
       <c r="H148">
-        <v>-56</v>
+        <v>44</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>1740</v>
       </c>
       <c r="J148">
-        <v>-3345</v>
+        <v>0</v>
       </c>
       <c r="K148">
-        <v>-150</v>
+        <v>-100</v>
       </c>
       <c r="L148" t="str">
         <v>Yes</v>
       </c>
       <c r="M148" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N148">
-        <v>-3495</v>
+        <v>1640</v>
       </c>
       <c r="O148">
         <v>0</v>
@@ -7366,25 +7366,25 @@
         <v>21-04-2026</v>
       </c>
       <c r="D149" t="str">
-        <v>Sensex CE</v>
+        <v>SensexBullCE</v>
       </c>
       <c r="E149">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F149">
-        <v>584</v>
+        <v>703</v>
       </c>
       <c r="G149">
-        <v>628</v>
+        <v>683</v>
       </c>
       <c r="H149">
-        <v>44</v>
+        <v>-20</v>
       </c>
       <c r="I149">
-        <v>1740</v>
+        <v>0</v>
       </c>
       <c r="J149">
-        <v>0</v>
+        <v>-392</v>
       </c>
       <c r="K149">
         <v>-100</v>
@@ -7393,10 +7393,10 @@
         <v>Yes</v>
       </c>
       <c r="M149" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N149">
-        <v>1640</v>
+        <v>-492</v>
       </c>
       <c r="O149">
         <v>0</v>
@@ -7410,28 +7410,28 @@
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>21-04-2026</v>
+        <v>22-04-2026</v>
       </c>
       <c r="D150" t="str">
-        <v>SensexBullCE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E150">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F150">
-        <v>703</v>
+        <v>249</v>
       </c>
       <c r="G150">
-        <v>683</v>
+        <v>296</v>
       </c>
       <c r="H150">
-        <v>-20</v>
+        <v>47</v>
       </c>
       <c r="I150">
-        <v>0</v>
+        <v>3032</v>
       </c>
       <c r="J150">
-        <v>-392</v>
+        <v>0</v>
       </c>
       <c r="K150">
         <v>-100</v>
@@ -7440,10 +7440,10 @@
         <v>Yes</v>
       </c>
       <c r="M150" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N150">
-        <v>-492</v>
+        <v>2932</v>
       </c>
       <c r="O150">
         <v>0</v>
@@ -7460,22 +7460,22 @@
         <v>22-04-2026</v>
       </c>
       <c r="D151" t="str">
-        <v>NiftyBullPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E151">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="F151">
-        <v>249</v>
+        <v>201</v>
       </c>
       <c r="G151">
-        <v>296</v>
+        <v>237</v>
       </c>
       <c r="H151">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="I151">
-        <v>3032</v>
+        <v>4732</v>
       </c>
       <c r="J151">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N151">
-        <v>2932</v>
+        <v>4632</v>
       </c>
       <c r="O151">
         <v>0</v>
@@ -7504,7 +7504,7 @@
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>22-04-2026</v>
+        <v>23-04-2026</v>
       </c>
       <c r="D152" t="str">
         <v>NiftyPE</v>
@@ -7513,31 +7513,31 @@
         <v>130</v>
       </c>
       <c r="F152">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G152">
-        <v>237</v>
+        <v>161</v>
       </c>
       <c r="H152">
-        <v>36</v>
+        <v>-31</v>
       </c>
       <c r="I152">
-        <v>4732</v>
+        <v>0</v>
       </c>
       <c r="J152">
-        <v>0</v>
+        <v>-4004</v>
       </c>
       <c r="K152">
-        <v>-100</v>
+        <v>-94</v>
       </c>
       <c r="L152" t="str">
         <v>Yes</v>
       </c>
       <c r="M152" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N152">
-        <v>4632</v>
+        <v>-4098</v>
       </c>
       <c r="O152">
         <v>0</v>
@@ -7554,28 +7554,28 @@
         <v>23-04-2026</v>
       </c>
       <c r="D153" t="str">
-        <v>NiftyPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E153">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="F153">
-        <v>192</v>
+        <v>239</v>
       </c>
       <c r="G153">
-        <v>161</v>
+        <v>203</v>
       </c>
       <c r="H153">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="I153">
         <v>0</v>
       </c>
       <c r="J153">
-        <v>-4004</v>
+        <v>-2278</v>
       </c>
       <c r="K153">
-        <v>-94</v>
+        <v>-90</v>
       </c>
       <c r="L153" t="str">
         <v>Yes</v>
@@ -7584,7 +7584,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N153">
-        <v>-4098</v>
+        <v>-2368</v>
       </c>
       <c r="O153">
         <v>0</v>
@@ -7598,28 +7598,28 @@
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>23-04-2026</v>
+        <v>28-04-2026</v>
       </c>
       <c r="D154" t="str">
-        <v>NiftyBullPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E154">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="F154">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="G154">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="H154">
-        <v>-35</v>
+        <v>-37</v>
       </c>
       <c r="I154">
         <v>0</v>
       </c>
       <c r="J154">
-        <v>-2278</v>
+        <v>-4804</v>
       </c>
       <c r="K154">
         <v>-90</v>
@@ -7631,7 +7631,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N154">
-        <v>-2368</v>
+        <v>-4894</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -7648,25 +7648,25 @@
         <v>28-04-2026</v>
       </c>
       <c r="D155" t="str">
-        <v>NiftyPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E155">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="F155">
-        <v>208</v>
+        <v>522</v>
       </c>
       <c r="G155">
-        <v>171</v>
+        <v>452</v>
       </c>
       <c r="H155">
-        <v>-37</v>
+        <v>-70</v>
       </c>
       <c r="I155">
         <v>0</v>
       </c>
       <c r="J155">
-        <v>-4804</v>
+        <v>-4189</v>
       </c>
       <c r="K155">
         <v>-90</v>
@@ -7678,7 +7678,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N155">
-        <v>-4894</v>
+        <v>-4279</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -7695,25 +7695,25 @@
         <v>28-04-2026</v>
       </c>
       <c r="D156" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E156">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F156">
-        <v>522</v>
+        <v>256</v>
       </c>
       <c r="G156">
-        <v>452</v>
+        <v>221</v>
       </c>
       <c r="H156">
-        <v>-70</v>
+        <v>-35</v>
       </c>
       <c r="I156">
         <v>0</v>
       </c>
       <c r="J156">
-        <v>-4189</v>
+        <v>-2301</v>
       </c>
       <c r="K156">
         <v>-90</v>
@@ -7725,7 +7725,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N156">
-        <v>-4279</v>
+        <v>-2391</v>
       </c>
       <c r="O156">
         <v>0</v>
@@ -7742,28 +7742,28 @@
         <v>28-04-2026</v>
       </c>
       <c r="D157" t="str">
-        <v>NiftyBullPE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E157">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F157">
-        <v>256</v>
+        <v>722</v>
       </c>
       <c r="G157">
-        <v>221</v>
+        <v>622</v>
       </c>
       <c r="H157">
-        <v>-35</v>
+        <v>-100</v>
       </c>
       <c r="I157">
         <v>0</v>
       </c>
       <c r="J157">
-        <v>-2301</v>
+        <v>-2005</v>
       </c>
       <c r="K157">
-        <v>-90</v>
+        <v>-91</v>
       </c>
       <c r="L157" t="str">
         <v>Yes</v>
@@ -7772,7 +7772,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N157">
-        <v>-2391</v>
+        <v>-2096</v>
       </c>
       <c r="O157">
         <v>0</v>
@@ -7786,40 +7786,40 @@
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>28-04-2026</v>
+        <v>29-04-2026</v>
       </c>
       <c r="D158" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E158">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="F158">
-        <v>722</v>
+        <v>199</v>
       </c>
       <c r="G158">
-        <v>622</v>
+        <v>273</v>
       </c>
       <c r="H158">
+        <v>74</v>
+      </c>
+      <c r="I158">
+        <v>9672</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
         <v>-100</v>
       </c>
-      <c r="I158">
-        <v>0</v>
-      </c>
-      <c r="J158">
-        <v>-2005</v>
-      </c>
-      <c r="K158">
-        <v>-91</v>
-      </c>
       <c r="L158" t="str">
         <v>Yes</v>
       </c>
       <c r="M158" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N158">
-        <v>-2096</v>
+        <v>9572</v>
       </c>
       <c r="O158">
         <v>0</v>
@@ -7836,22 +7836,22 @@
         <v>29-04-2026</v>
       </c>
       <c r="D159" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E159">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="F159">
-        <v>199</v>
+        <v>600</v>
       </c>
       <c r="G159">
-        <v>273</v>
+        <v>699</v>
       </c>
       <c r="H159">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I159">
-        <v>9672</v>
+        <v>3974</v>
       </c>
       <c r="J159">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N159">
-        <v>9572</v>
+        <v>3874</v>
       </c>
       <c r="O159">
         <v>0</v>
@@ -7883,22 +7883,22 @@
         <v>29-04-2026</v>
       </c>
       <c r="D160" t="str">
-        <v>Sensex CE</v>
+        <v>NiftyBullCE</v>
       </c>
       <c r="E160">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="F160">
-        <v>600</v>
+        <v>257</v>
       </c>
       <c r="G160">
-        <v>699</v>
+        <v>367</v>
       </c>
       <c r="H160">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="I160">
-        <v>3974</v>
+        <v>7173</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N160">
-        <v>3874</v>
+        <v>7073</v>
       </c>
       <c r="O160">
         <v>0</v>
@@ -7930,22 +7930,22 @@
         <v>29-04-2026</v>
       </c>
       <c r="D161" t="str">
-        <v>NiftyBullCE</v>
+        <v>SensexBullCE</v>
       </c>
       <c r="E161">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F161">
-        <v>257</v>
+        <v>675</v>
       </c>
       <c r="G161">
-        <v>367</v>
+        <v>960</v>
       </c>
       <c r="H161">
-        <v>110</v>
+        <v>285</v>
       </c>
       <c r="I161">
-        <v>7173</v>
+        <v>5696</v>
       </c>
       <c r="J161">
         <v>0</v>
@@ -7960,7 +7960,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N161">
-        <v>7073</v>
+        <v>5596</v>
       </c>
       <c r="O161">
         <v>0</v>
@@ -7974,28 +7974,28 @@
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>29-04-2026</v>
+        <v>30-04-2026</v>
       </c>
       <c r="D162" t="str">
-        <v>SensexBullCE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E162">
         <v>20</v>
       </c>
       <c r="F162">
-        <v>675</v>
+        <v>746</v>
       </c>
       <c r="G162">
-        <v>960</v>
+        <v>639</v>
       </c>
       <c r="H162">
-        <v>285</v>
+        <v>-107</v>
       </c>
       <c r="I162">
-        <v>5696</v>
+        <v>0</v>
       </c>
       <c r="J162">
-        <v>0</v>
+        <v>-2131</v>
       </c>
       <c r="K162">
         <v>-100</v>
@@ -8004,10 +8004,10 @@
         <v>Yes</v>
       </c>
       <c r="M162" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N162">
-        <v>5596</v>
+        <v>-2231</v>
       </c>
       <c r="O162">
         <v>0</v>
@@ -8024,25 +8024,25 @@
         <v>30-04-2026</v>
       </c>
       <c r="D163" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E163">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F163">
-        <v>746</v>
+        <v>251</v>
       </c>
       <c r="G163">
-        <v>639</v>
+        <v>216</v>
       </c>
       <c r="H163">
-        <v>-107</v>
+        <v>-35</v>
       </c>
       <c r="I163">
         <v>0</v>
       </c>
       <c r="J163">
-        <v>-2131</v>
+        <v>-2269</v>
       </c>
       <c r="K163">
         <v>-100</v>
@@ -8054,7 +8054,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N163">
-        <v>-2231</v>
+        <v>-2369</v>
       </c>
       <c r="O163">
         <v>0</v>
@@ -8071,25 +8071,25 @@
         <v>30-04-2026</v>
       </c>
       <c r="D164" t="str">
-        <v>NiftyBullPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E164">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F164">
-        <v>251</v>
+        <v>750</v>
       </c>
       <c r="G164">
-        <v>216</v>
+        <v>655</v>
       </c>
       <c r="H164">
-        <v>-35</v>
+        <v>-95</v>
       </c>
       <c r="I164">
         <v>0</v>
       </c>
       <c r="J164">
-        <v>-2269</v>
+        <v>-3796</v>
       </c>
       <c r="K164">
         <v>-100</v>
@@ -8101,7 +8101,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N164">
-        <v>-2369</v>
+        <v>-3896</v>
       </c>
       <c r="O164">
         <v>0</v>
@@ -8124,19 +8124,19 @@
         <v>40</v>
       </c>
       <c r="F165">
-        <v>750</v>
+        <v>734</v>
       </c>
       <c r="G165">
-        <v>655</v>
+        <v>796</v>
       </c>
       <c r="H165">
-        <v>-95</v>
+        <v>62</v>
       </c>
       <c r="I165">
-        <v>0</v>
+        <v>2462</v>
       </c>
       <c r="J165">
-        <v>-3796</v>
+        <v>0</v>
       </c>
       <c r="K165">
         <v>-100</v>
@@ -8145,10 +8145,10 @@
         <v>Yes</v>
       </c>
       <c r="M165" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N165">
-        <v>-3896</v>
+        <v>2362</v>
       </c>
       <c r="O165">
         <v>0</v>
@@ -8165,25 +8165,25 @@
         <v>30-04-2026</v>
       </c>
       <c r="D166" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E166">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="F166">
-        <v>734</v>
+        <v>198</v>
       </c>
       <c r="G166">
-        <v>796</v>
+        <v>186</v>
       </c>
       <c r="H166">
-        <v>62</v>
+        <v>-11</v>
       </c>
       <c r="I166">
-        <v>2462</v>
+        <v>0</v>
       </c>
       <c r="J166">
-        <v>0</v>
+        <v>-1476</v>
       </c>
       <c r="K166">
         <v>-100</v>
@@ -8192,10 +8192,10 @@
         <v>Yes</v>
       </c>
       <c r="M166" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N166">
-        <v>2362</v>
+        <v>-1576</v>
       </c>
       <c r="O166">
         <v>0</v>
@@ -8209,28 +8209,28 @@
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>30-04-2026</v>
+        <v>04-05-2026</v>
       </c>
       <c r="D167" t="str">
-        <v>NiftyPE</v>
+        <v>SensexBullCE</v>
       </c>
       <c r="E167">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="F167">
-        <v>198</v>
+        <v>695</v>
       </c>
       <c r="G167">
-        <v>186</v>
+        <v>594</v>
       </c>
       <c r="H167">
-        <v>-11</v>
+        <v>-101</v>
       </c>
       <c r="I167">
         <v>0</v>
       </c>
       <c r="J167">
-        <v>-1476</v>
+        <v>-2010</v>
       </c>
       <c r="K167">
         <v>-100</v>
@@ -8242,7 +8242,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N167">
-        <v>-1576</v>
+        <v>-2110</v>
       </c>
       <c r="O167">
         <v>0</v>
@@ -8259,25 +8259,25 @@
         <v>04-05-2026</v>
       </c>
       <c r="D168" t="str">
-        <v>SensexBullCE</v>
+        <v>NiftyBullCE</v>
       </c>
       <c r="E168">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F168">
-        <v>695</v>
+        <v>258</v>
       </c>
       <c r="G168">
-        <v>594</v>
+        <v>217</v>
       </c>
       <c r="H168">
-        <v>-101</v>
+        <v>-42</v>
       </c>
       <c r="I168">
         <v>0</v>
       </c>
       <c r="J168">
-        <v>-2010</v>
+        <v>-2720</v>
       </c>
       <c r="K168">
         <v>-100</v>
@@ -8289,7 +8289,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N168">
-        <v>-2110</v>
+        <v>-2820</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -8306,25 +8306,25 @@
         <v>04-05-2026</v>
       </c>
       <c r="D169" t="str">
-        <v>NiftyBullCE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E169">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F169">
-        <v>258</v>
+        <v>508</v>
       </c>
       <c r="G169">
-        <v>217</v>
+        <v>604</v>
       </c>
       <c r="H169">
-        <v>-42</v>
+        <v>96</v>
       </c>
       <c r="I169">
-        <v>0</v>
+        <v>5778</v>
       </c>
       <c r="J169">
-        <v>-2720</v>
+        <v>0</v>
       </c>
       <c r="K169">
         <v>-100</v>
@@ -8333,10 +8333,10 @@
         <v>Yes</v>
       </c>
       <c r="M169" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N169">
-        <v>-2820</v>
+        <v>5678</v>
       </c>
       <c r="O169">
         <v>0</v>
@@ -8353,25 +8353,25 @@
         <v>04-05-2026</v>
       </c>
       <c r="D170" t="str">
-        <v>BankniftyPE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E170">
         <v>60</v>
       </c>
       <c r="F170">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G170">
-        <v>604</v>
+        <v>493</v>
       </c>
       <c r="H170">
-        <v>96</v>
+        <v>-17</v>
       </c>
       <c r="I170">
-        <v>5778</v>
+        <v>0</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>-1023</v>
       </c>
       <c r="K170">
         <v>-100</v>
@@ -8380,10 +8380,10 @@
         <v>Yes</v>
       </c>
       <c r="M170" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N170">
-        <v>5678</v>
+        <v>-1123</v>
       </c>
       <c r="O170">
         <v>0</v>
@@ -8397,28 +8397,28 @@
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>04-05-2026</v>
+        <v>05-05-2026</v>
       </c>
       <c r="D171" t="str">
-        <v>BankniftyCE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E171">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F171">
-        <v>510</v>
+        <v>719</v>
       </c>
       <c r="G171">
-        <v>493</v>
+        <v>615</v>
       </c>
       <c r="H171">
-        <v>-17</v>
+        <v>-104</v>
       </c>
       <c r="I171">
         <v>0</v>
       </c>
       <c r="J171">
-        <v>-1023</v>
+        <v>-2072</v>
       </c>
       <c r="K171">
         <v>-100</v>
@@ -8430,7 +8430,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N171">
-        <v>-1123</v>
+        <v>-2172</v>
       </c>
       <c r="O171">
         <v>0</v>
@@ -8447,25 +8447,25 @@
         <v>05-05-2026</v>
       </c>
       <c r="D172" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E172">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F172">
-        <v>719</v>
+        <v>271</v>
       </c>
       <c r="G172">
-        <v>615</v>
+        <v>235</v>
       </c>
       <c r="H172">
-        <v>-104</v>
+        <v>-36</v>
       </c>
       <c r="I172">
         <v>0</v>
       </c>
       <c r="J172">
-        <v>-2072</v>
+        <v>-2327</v>
       </c>
       <c r="K172">
         <v>-100</v>
@@ -8477,7 +8477,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N172">
-        <v>-2172</v>
+        <v>-2427</v>
       </c>
       <c r="O172">
         <v>0</v>
@@ -8494,25 +8494,25 @@
         <v>05-05-2026</v>
       </c>
       <c r="D173" t="str">
-        <v>NiftyBullPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E173">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F173">
-        <v>271</v>
+        <v>717</v>
       </c>
       <c r="G173">
-        <v>235</v>
+        <v>622</v>
       </c>
       <c r="H173">
-        <v>-36</v>
+        <v>-96</v>
       </c>
       <c r="I173">
         <v>0</v>
       </c>
       <c r="J173">
-        <v>-2327</v>
+        <v>-3826</v>
       </c>
       <c r="K173">
         <v>-100</v>
@@ -8524,7 +8524,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N173">
-        <v>-2427</v>
+        <v>-3926</v>
       </c>
       <c r="O173">
         <v>0</v>
@@ -8541,25 +8541,25 @@
         <v>05-05-2026</v>
       </c>
       <c r="D174" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E174">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="F174">
-        <v>717</v>
+        <v>183</v>
       </c>
       <c r="G174">
-        <v>622</v>
+        <v>147</v>
       </c>
       <c r="H174">
-        <v>-96</v>
+        <v>-35</v>
       </c>
       <c r="I174">
         <v>0</v>
       </c>
       <c r="J174">
-        <v>-3826</v>
+        <v>-4583</v>
       </c>
       <c r="K174">
         <v>-100</v>
@@ -8571,7 +8571,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N174">
-        <v>-3926</v>
+        <v>-4683</v>
       </c>
       <c r="O174">
         <v>0</v>
@@ -8585,28 +8585,28 @@
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>05-05-2026</v>
+        <v>06-05-2026</v>
       </c>
       <c r="D175" t="str">
-        <v>NiftyPE</v>
+        <v>SensexBullCE</v>
       </c>
       <c r="E175">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="F175">
-        <v>183</v>
+        <v>738</v>
       </c>
       <c r="G175">
-        <v>147</v>
+        <v>637</v>
       </c>
       <c r="H175">
-        <v>-35</v>
+        <v>-101</v>
       </c>
       <c r="I175">
         <v>0</v>
       </c>
       <c r="J175">
-        <v>-4583</v>
+        <v>-2018</v>
       </c>
       <c r="K175">
         <v>-100</v>
@@ -8618,7 +8618,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N175">
-        <v>-4683</v>
+        <v>-2118</v>
       </c>
       <c r="O175">
         <v>0</v>
@@ -8635,16 +8635,16 @@
         <v>06-05-2026</v>
       </c>
       <c r="D176" t="str">
-        <v>SensexBullCE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E176">
         <v>20</v>
       </c>
       <c r="F176">
-        <v>738</v>
+        <v>589</v>
       </c>
       <c r="G176">
-        <v>637</v>
+        <v>489</v>
       </c>
       <c r="H176">
         <v>-101</v>
@@ -8653,7 +8653,7 @@
         <v>0</v>
       </c>
       <c r="J176">
-        <v>-2018</v>
+        <v>-2015</v>
       </c>
       <c r="K176">
         <v>-100</v>
@@ -8665,7 +8665,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N176">
-        <v>-2118</v>
+        <v>-2115</v>
       </c>
       <c r="O176">
         <v>0</v>
@@ -8682,25 +8682,25 @@
         <v>06-05-2026</v>
       </c>
       <c r="D177" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyBullCE</v>
       </c>
       <c r="E177">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F177">
-        <v>589</v>
+        <v>239</v>
       </c>
       <c r="G177">
-        <v>489</v>
+        <v>222</v>
       </c>
       <c r="H177">
-        <v>-101</v>
+        <v>-16</v>
       </c>
       <c r="I177">
         <v>0</v>
       </c>
       <c r="J177">
-        <v>-2015</v>
+        <v>-1053</v>
       </c>
       <c r="K177">
         <v>-100</v>
@@ -8712,7 +8712,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N177">
-        <v>-2115</v>
+        <v>-1153</v>
       </c>
       <c r="O177">
         <v>0</v>
@@ -8735,19 +8735,19 @@
         <v>65</v>
       </c>
       <c r="F178">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G178">
-        <v>222</v>
+        <v>399</v>
       </c>
       <c r="H178">
-        <v>-16</v>
+        <v>146</v>
       </c>
       <c r="I178">
-        <v>0</v>
+        <v>9467</v>
       </c>
       <c r="J178">
-        <v>-1053</v>
+        <v>0</v>
       </c>
       <c r="K178">
         <v>-100</v>
@@ -8756,10 +8756,10 @@
         <v>Yes</v>
       </c>
       <c r="M178" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N178">
-        <v>-1153</v>
+        <v>9367</v>
       </c>
       <c r="O178">
         <v>0</v>
@@ -8776,25 +8776,25 @@
         <v>06-05-2026</v>
       </c>
       <c r="D179" t="str">
-        <v>NiftyBullCE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E179">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F179">
-        <v>254</v>
+        <v>527</v>
       </c>
       <c r="G179">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="H179">
-        <v>146</v>
+        <v>-47</v>
       </c>
       <c r="I179">
-        <v>9467</v>
+        <v>0</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>-2816</v>
       </c>
       <c r="K179">
         <v>-100</v>
@@ -8803,10 +8803,10 @@
         <v>Yes</v>
       </c>
       <c r="M179" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N179">
-        <v>9367</v>
+        <v>-2916</v>
       </c>
       <c r="O179">
         <v>0</v>
@@ -8823,25 +8823,25 @@
         <v>06-05-2026</v>
       </c>
       <c r="D180" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E180">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="F180">
-        <v>527</v>
+        <v>211</v>
       </c>
       <c r="G180">
-        <v>480</v>
+        <v>195</v>
       </c>
       <c r="H180">
-        <v>-47</v>
+        <v>-16</v>
       </c>
       <c r="I180">
         <v>0</v>
       </c>
       <c r="J180">
-        <v>-2816</v>
+        <v>-2074</v>
       </c>
       <c r="K180">
         <v>-100</v>
@@ -8853,7 +8853,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N180">
-        <v>-2916</v>
+        <v>-2174</v>
       </c>
       <c r="O180">
         <v>0</v>
@@ -8876,31 +8876,31 @@
         <v>130</v>
       </c>
       <c r="F181">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="G181">
-        <v>195</v>
+        <v>267</v>
       </c>
       <c r="H181">
-        <v>-16</v>
+        <v>70</v>
       </c>
       <c r="I181">
-        <v>0</v>
+        <v>9094</v>
       </c>
       <c r="J181">
-        <v>-2074</v>
+        <v>0</v>
       </c>
       <c r="K181">
-        <v>-100</v>
+        <v>-71</v>
       </c>
       <c r="L181" t="str">
         <v>Yes</v>
       </c>
       <c r="M181" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N181">
-        <v>-2174</v>
+        <v>9023</v>
       </c>
       <c r="O181">
         <v>0</v>
@@ -8914,31 +8914,31 @@
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>06-05-2026</v>
+        <v>08-05-2026</v>
       </c>
       <c r="D182" t="str">
-        <v>NiftyCE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E182">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="F182">
-        <v>197</v>
+        <v>607</v>
       </c>
       <c r="G182">
-        <v>267</v>
+        <v>634</v>
       </c>
       <c r="H182">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="I182">
-        <v>9094</v>
+        <v>536</v>
       </c>
       <c r="J182">
         <v>0</v>
       </c>
       <c r="K182">
-        <v>-71</v>
+        <v>-100</v>
       </c>
       <c r="L182" t="str">
         <v>Yes</v>
@@ -8947,7 +8947,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N182">
-        <v>9023</v>
+        <v>436</v>
       </c>
       <c r="O182">
         <v>0</v>
@@ -8964,22 +8964,22 @@
         <v>08-05-2026</v>
       </c>
       <c r="D183" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E183">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F183">
-        <v>607</v>
+        <v>266</v>
       </c>
       <c r="G183">
-        <v>634</v>
+        <v>282</v>
       </c>
       <c r="H183">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I183">
-        <v>536</v>
+        <v>1011</v>
       </c>
       <c r="J183">
         <v>0</v>
@@ -8994,7 +8994,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N183">
-        <v>436</v>
+        <v>911</v>
       </c>
       <c r="O183">
         <v>0</v>
@@ -9011,22 +9011,22 @@
         <v>08-05-2026</v>
       </c>
       <c r="D184" t="str">
-        <v>NiftyBullPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E184">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F184">
-        <v>266</v>
+        <v>496</v>
       </c>
       <c r="G184">
-        <v>282</v>
+        <v>534</v>
       </c>
       <c r="H184">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I184">
-        <v>1011</v>
+        <v>2265</v>
       </c>
       <c r="J184">
         <v>0</v>
@@ -9041,7 +9041,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N184">
-        <v>911</v>
+        <v>2165</v>
       </c>
       <c r="O184">
         <v>0</v>
@@ -9058,22 +9058,22 @@
         <v>08-05-2026</v>
       </c>
       <c r="D185" t="str">
-        <v>BankniftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E185">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F185">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="G185">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H185">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I185">
-        <v>2265</v>
+        <v>2037</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -9088,7 +9088,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N185">
-        <v>2165</v>
+        <v>1937</v>
       </c>
       <c r="O185">
         <v>0</v>
@@ -9105,22 +9105,22 @@
         <v>08-05-2026</v>
       </c>
       <c r="D186" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E186">
+        <v>130</v>
+      </c>
+      <c r="F186">
+        <v>204</v>
+      </c>
+      <c r="G186">
+        <v>243</v>
+      </c>
+      <c r="H186">
         <v>40</v>
       </c>
-      <c r="F186">
-        <v>481</v>
-      </c>
-      <c r="G186">
-        <v>532</v>
-      </c>
-      <c r="H186">
-        <v>51</v>
-      </c>
       <c r="I186">
-        <v>2037</v>
+        <v>5135</v>
       </c>
       <c r="J186">
         <v>0</v>
@@ -9135,7 +9135,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N186">
-        <v>1937</v>
+        <v>5035</v>
       </c>
       <c r="O186">
         <v>0</v>
@@ -9149,28 +9149,28 @@
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>08-05-2026</v>
+        <v>11-05-2026</v>
       </c>
       <c r="D187" t="str">
-        <v>NiftyPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E187">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="F187">
-        <v>204</v>
+        <v>242</v>
       </c>
       <c r="G187">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="H187">
-        <v>40</v>
+        <v>-35</v>
       </c>
       <c r="I187">
-        <v>5135</v>
+        <v>0</v>
       </c>
       <c r="J187">
-        <v>0</v>
+        <v>-2275</v>
       </c>
       <c r="K187">
         <v>-100</v>
@@ -9179,10 +9179,10 @@
         <v>Yes</v>
       </c>
       <c r="M187" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N187">
-        <v>5035</v>
+        <v>-2375</v>
       </c>
       <c r="O187">
         <v>0</v>
@@ -9199,25 +9199,25 @@
         <v>11-05-2026</v>
       </c>
       <c r="D188" t="str">
-        <v>NiftyBullPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E188">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F188">
-        <v>242</v>
+        <v>498</v>
       </c>
       <c r="G188">
-        <v>207</v>
+        <v>428</v>
       </c>
       <c r="H188">
-        <v>-35</v>
+        <v>-70</v>
       </c>
       <c r="I188">
         <v>0</v>
       </c>
       <c r="J188">
-        <v>-2275</v>
+        <v>-4175</v>
       </c>
       <c r="K188">
         <v>-100</v>
@@ -9229,7 +9229,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N188">
-        <v>-2375</v>
+        <v>-4275</v>
       </c>
       <c r="O188">
         <v>0</v>
@@ -9246,25 +9246,25 @@
         <v>11-05-2026</v>
       </c>
       <c r="D189" t="str">
-        <v>BankniftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E189">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F189">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="G189">
-        <v>428</v>
+        <v>546</v>
       </c>
       <c r="H189">
-        <v>-70</v>
+        <v>27</v>
       </c>
       <c r="I189">
-        <v>0</v>
+        <v>1092</v>
       </c>
       <c r="J189">
-        <v>-4175</v>
+        <v>0</v>
       </c>
       <c r="K189">
         <v>-100</v>
@@ -9273,10 +9273,10 @@
         <v>Yes</v>
       </c>
       <c r="M189" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N189">
-        <v>-4275</v>
+        <v>992</v>
       </c>
       <c r="O189">
         <v>0</v>
@@ -9293,28 +9293,28 @@
         <v>11-05-2026</v>
       </c>
       <c r="D190" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E190">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="F190">
-        <v>518</v>
+        <v>196</v>
       </c>
       <c r="G190">
-        <v>546</v>
+        <v>206</v>
       </c>
       <c r="H190">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I190">
-        <v>1092</v>
+        <v>1268</v>
       </c>
       <c r="J190">
         <v>0</v>
       </c>
       <c r="K190">
-        <v>-100</v>
+        <v>-102</v>
       </c>
       <c r="L190" t="str">
         <v>Yes</v>
@@ -9323,7 +9323,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N190">
-        <v>992</v>
+        <v>1166</v>
       </c>
       <c r="O190">
         <v>0</v>
@@ -9337,31 +9337,31 @@
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>11-05-2026</v>
+        <v>12-05-2026</v>
       </c>
       <c r="D191" t="str">
-        <v>NiftyPE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E191">
+        <v>20</v>
+      </c>
+      <c r="F191">
+        <v>574</v>
+      </c>
+      <c r="G191">
+        <v>704</v>
+      </c>
+      <c r="H191">
         <v>130</v>
       </c>
-      <c r="F191">
-        <v>196</v>
-      </c>
-      <c r="G191">
-        <v>206</v>
-      </c>
-      <c r="H191">
-        <v>10</v>
-      </c>
       <c r="I191">
-        <v>1268</v>
+        <v>2601</v>
       </c>
       <c r="J191">
         <v>0</v>
       </c>
       <c r="K191">
-        <v>-102</v>
+        <v>-100</v>
       </c>
       <c r="L191" t="str">
         <v>Yes</v>
@@ -9370,7 +9370,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N191">
-        <v>1166</v>
+        <v>2501</v>
       </c>
       <c r="O191">
         <v>0</v>
@@ -9387,22 +9387,22 @@
         <v>12-05-2026</v>
       </c>
       <c r="D192" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E192">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F192">
-        <v>574</v>
+        <v>258</v>
       </c>
       <c r="G192">
-        <v>704</v>
+        <v>294</v>
       </c>
       <c r="H192">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="I192">
-        <v>2601</v>
+        <v>2298</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -9417,7 +9417,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N192">
-        <v>2501</v>
+        <v>2198</v>
       </c>
       <c r="O192">
         <v>0</v>
@@ -9434,22 +9434,22 @@
         <v>12-05-2026</v>
       </c>
       <c r="D193" t="str">
-        <v>NiftyBullPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E193">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="F193">
+        <v>212</v>
+      </c>
+      <c r="G193">
         <v>258</v>
       </c>
-      <c r="G193">
-        <v>294</v>
-      </c>
       <c r="H193">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="I193">
-        <v>2298</v>
+        <v>5950</v>
       </c>
       <c r="J193">
         <v>0</v>
@@ -9464,7 +9464,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N193">
-        <v>2198</v>
+        <v>5850</v>
       </c>
       <c r="O193">
         <v>0</v>
@@ -9478,40 +9478,40 @@
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>12-05-2026</v>
+        <v>13-05-2026</v>
       </c>
       <c r="D194" t="str">
-        <v>NiftyPE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E194">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="F194">
-        <v>212</v>
+        <v>616</v>
       </c>
       <c r="G194">
-        <v>258</v>
+        <v>512</v>
       </c>
       <c r="H194">
-        <v>46</v>
+        <v>-104</v>
       </c>
       <c r="I194">
-        <v>5950</v>
+        <v>0</v>
       </c>
       <c r="J194">
-        <v>0</v>
+        <v>-2075</v>
       </c>
       <c r="K194">
-        <v>-100</v>
+        <v>-85</v>
       </c>
       <c r="L194" t="str">
         <v>Yes</v>
       </c>
       <c r="M194" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N194">
-        <v>5850</v>
+        <v>-2160</v>
       </c>
       <c r="O194">
         <v>0</v>
@@ -9528,25 +9528,25 @@
         <v>13-05-2026</v>
       </c>
       <c r="D195" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E195">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F195">
-        <v>616</v>
+        <v>247</v>
       </c>
       <c r="G195">
-        <v>512</v>
+        <v>215</v>
       </c>
       <c r="H195">
-        <v>-104</v>
+        <v>-32</v>
       </c>
       <c r="I195">
         <v>0</v>
       </c>
       <c r="J195">
-        <v>-2075</v>
+        <v>-2106</v>
       </c>
       <c r="K195">
         <v>-85</v>
@@ -9558,7 +9558,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N195">
-        <v>-2160</v>
+        <v>-2191</v>
       </c>
       <c r="O195">
         <v>0</v>
@@ -9575,28 +9575,28 @@
         <v>13-05-2026</v>
       </c>
       <c r="D196" t="str">
-        <v>NiftyBullPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E196">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F196">
-        <v>247</v>
+        <v>504</v>
       </c>
       <c r="G196">
-        <v>215</v>
+        <v>437</v>
       </c>
       <c r="H196">
-        <v>-32</v>
+        <v>-67</v>
       </c>
       <c r="I196">
         <v>0</v>
       </c>
       <c r="J196">
-        <v>-2106</v>
+        <v>-4047</v>
       </c>
       <c r="K196">
-        <v>-85</v>
+        <v>-86</v>
       </c>
       <c r="L196" t="str">
         <v>Yes</v>
@@ -9605,7 +9605,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N196">
-        <v>-2191</v>
+        <v>-4133</v>
       </c>
       <c r="O196">
         <v>0</v>
@@ -9619,40 +9619,40 @@
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>13-05-2026</v>
+        <v>14-05-2026</v>
       </c>
       <c r="D197" t="str">
-        <v>BankniftyPE</v>
+        <v>SensexBullCE</v>
       </c>
       <c r="E197">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F197">
-        <v>504</v>
+        <v>673</v>
       </c>
       <c r="G197">
-        <v>437</v>
+        <v>771</v>
       </c>
       <c r="H197">
-        <v>-67</v>
+        <v>99</v>
       </c>
       <c r="I197">
-        <v>0</v>
+        <v>1970</v>
       </c>
       <c r="J197">
-        <v>-4047</v>
+        <v>0</v>
       </c>
       <c r="K197">
-        <v>-86</v>
+        <v>-104</v>
       </c>
       <c r="L197" t="str">
         <v>Yes</v>
       </c>
       <c r="M197" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N197">
-        <v>-4133</v>
+        <v>1866</v>
       </c>
       <c r="O197">
         <v>0</v>
@@ -9669,28 +9669,28 @@
         <v>14-05-2026</v>
       </c>
       <c r="D198" t="str">
-        <v>SensexBullCE</v>
+        <v>NiftyBullCE</v>
       </c>
       <c r="E198">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F198">
-        <v>673</v>
+        <v>254</v>
       </c>
       <c r="G198">
-        <v>771</v>
+        <v>258</v>
       </c>
       <c r="H198">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="I198">
-        <v>1970</v>
+        <v>302</v>
       </c>
       <c r="J198">
         <v>0</v>
       </c>
       <c r="K198">
-        <v>-104</v>
+        <v>-102</v>
       </c>
       <c r="L198" t="str">
         <v>Yes</v>
@@ -9699,7 +9699,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N198">
-        <v>1866</v>
+        <v>201</v>
       </c>
       <c r="O198">
         <v>0</v>
@@ -9716,28 +9716,28 @@
         <v>14-05-2026</v>
       </c>
       <c r="D199" t="str">
-        <v>NiftyBullCE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E199">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F199">
-        <v>254</v>
+        <v>499</v>
       </c>
       <c r="G199">
-        <v>258</v>
+        <v>546</v>
       </c>
       <c r="H199">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="I199">
-        <v>302</v>
+        <v>2797</v>
       </c>
       <c r="J199">
         <v>0</v>
       </c>
       <c r="K199">
-        <v>-102</v>
+        <v>-104</v>
       </c>
       <c r="L199" t="str">
         <v>Yes</v>
@@ -9746,7 +9746,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N199">
-        <v>201</v>
+        <v>2693</v>
       </c>
       <c r="O199">
         <v>0</v>
@@ -9763,22 +9763,22 @@
         <v>14-05-2026</v>
       </c>
       <c r="D200" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E200">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="F200">
-        <v>499</v>
+        <v>582</v>
       </c>
       <c r="G200">
-        <v>546</v>
+        <v>776</v>
       </c>
       <c r="H200">
-        <v>47</v>
+        <v>194</v>
       </c>
       <c r="I200">
-        <v>2797</v>
+        <v>7759</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -9793,7 +9793,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N200">
-        <v>2693</v>
+        <v>7655</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -9810,22 +9810,22 @@
         <v>14-05-2026</v>
       </c>
       <c r="D201" t="str">
-        <v>Sensex CE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E201">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="F201">
-        <v>582</v>
+        <v>195</v>
       </c>
       <c r="G201">
-        <v>776</v>
+        <v>211</v>
       </c>
       <c r="H201">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="I201">
-        <v>7759</v>
+        <v>2074</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -9840,7 +9840,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N201">
-        <v>7655</v>
+        <v>1970</v>
       </c>
       <c r="O201">
         <v>0</v>
@@ -9854,31 +9854,31 @@
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>14-05-2026</v>
+        <v>18-05-2026</v>
       </c>
       <c r="D202" t="str">
-        <v>NiftyCE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E202">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="F202">
-        <v>195</v>
+        <v>609</v>
       </c>
       <c r="G202">
-        <v>211</v>
+        <v>672</v>
       </c>
       <c r="H202">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="I202">
-        <v>2074</v>
+        <v>1260</v>
       </c>
       <c r="J202">
         <v>0</v>
       </c>
       <c r="K202">
-        <v>-104</v>
+        <v>-98</v>
       </c>
       <c r="L202" t="str">
         <v>Yes</v>
@@ -9887,7 +9887,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N202">
-        <v>1970</v>
+        <v>1162</v>
       </c>
       <c r="O202">
         <v>0</v>
@@ -9904,22 +9904,22 @@
         <v>18-05-2026</v>
       </c>
       <c r="D203" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E203">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F203">
-        <v>609</v>
+        <v>249</v>
       </c>
       <c r="G203">
-        <v>672</v>
+        <v>300</v>
       </c>
       <c r="H203">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="I203">
-        <v>1260</v>
+        <v>3315</v>
       </c>
       <c r="J203">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N203">
-        <v>1162</v>
+        <v>3217</v>
       </c>
       <c r="O203">
         <v>0</v>
@@ -9951,22 +9951,22 @@
         <v>18-05-2026</v>
       </c>
       <c r="D204" t="str">
-        <v>NiftyBullPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E204">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F204">
-        <v>249</v>
+        <v>530</v>
       </c>
       <c r="G204">
-        <v>300</v>
+        <v>587</v>
       </c>
       <c r="H204">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I204">
-        <v>3315</v>
+        <v>2280</v>
       </c>
       <c r="J204">
         <v>0</v>
@@ -9981,7 +9981,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N204">
-        <v>3217</v>
+        <v>2182</v>
       </c>
       <c r="O204">
         <v>0</v>
@@ -9998,22 +9998,22 @@
         <v>18-05-2026</v>
       </c>
       <c r="D205" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E205">
-        <v>40</v>
+        <v>130</v>
       </c>
       <c r="F205">
-        <v>530</v>
+        <v>215</v>
       </c>
       <c r="G205">
-        <v>587</v>
+        <v>250</v>
       </c>
       <c r="H205">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="I205">
-        <v>2280</v>
+        <v>4439</v>
       </c>
       <c r="J205">
         <v>0</v>
@@ -10028,7 +10028,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N205">
-        <v>2182</v>
+        <v>4341</v>
       </c>
       <c r="O205">
         <v>0</v>
@@ -10042,40 +10042,40 @@
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>18-05-2026</v>
+        <v>20-05-2026</v>
       </c>
       <c r="D206" t="str">
-        <v>NiftyPE</v>
+        <v>SensexBullPE</v>
       </c>
       <c r="E206">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="F206">
-        <v>215</v>
+        <v>610</v>
       </c>
       <c r="G206">
-        <v>250</v>
+        <v>510</v>
       </c>
       <c r="H206">
-        <v>34</v>
+        <v>-100</v>
       </c>
       <c r="I206">
-        <v>4439</v>
+        <v>0</v>
       </c>
       <c r="J206">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="K206">
-        <v>-98</v>
+        <v>-92</v>
       </c>
       <c r="L206" t="str">
         <v>Yes</v>
       </c>
       <c r="M206" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N206">
-        <v>4341</v>
+        <v>-2092</v>
       </c>
       <c r="O206">
         <v>0</v>
@@ -10092,25 +10092,25 @@
         <v>20-05-2026</v>
       </c>
       <c r="D207" t="str">
-        <v>SensexBullPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E207">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F207">
-        <v>610</v>
+        <v>252</v>
       </c>
       <c r="G207">
-        <v>510</v>
+        <v>230</v>
       </c>
       <c r="H207">
-        <v>-100</v>
+        <v>-23</v>
       </c>
       <c r="I207">
         <v>0</v>
       </c>
       <c r="J207">
-        <v>-2000</v>
+        <v>-1466</v>
       </c>
       <c r="K207">
         <v>-92</v>
@@ -10122,7 +10122,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N207">
-        <v>-2092</v>
+        <v>-1558</v>
       </c>
       <c r="O207">
         <v>0</v>
@@ -10139,25 +10139,25 @@
         <v>20-05-2026</v>
       </c>
       <c r="D208" t="str">
-        <v>NiftyBullPE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E208">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F208">
-        <v>252</v>
+        <v>493</v>
       </c>
       <c r="G208">
-        <v>230</v>
+        <v>433</v>
       </c>
       <c r="H208">
-        <v>-23</v>
+        <v>-60</v>
       </c>
       <c r="I208">
         <v>0</v>
       </c>
       <c r="J208">
-        <v>-1466</v>
+        <v>-3597</v>
       </c>
       <c r="K208">
         <v>-92</v>
@@ -10169,7 +10169,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N208">
-        <v>-1558</v>
+        <v>-3689</v>
       </c>
       <c r="O208">
         <v>0</v>
@@ -10186,28 +10186,28 @@
         <v>20-05-2026</v>
       </c>
       <c r="D209" t="str">
-        <v>BankniftyPE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E209">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="F209">
-        <v>493</v>
+        <v>205</v>
       </c>
       <c r="G209">
-        <v>433</v>
+        <v>185</v>
       </c>
       <c r="H209">
-        <v>-60</v>
+        <v>-19</v>
       </c>
       <c r="I209">
         <v>0</v>
       </c>
       <c r="J209">
-        <v>-3597</v>
+        <v>-2496</v>
       </c>
       <c r="K209">
-        <v>-92</v>
+        <v>-94</v>
       </c>
       <c r="L209" t="str">
         <v>Yes</v>
@@ -10216,7 +10216,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N209">
-        <v>-3689</v>
+        <v>-2590</v>
       </c>
       <c r="O209">
         <v>0</v>
@@ -10230,31 +10230,31 @@
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>20-05-2026</v>
+        <v>21-05-2026</v>
       </c>
       <c r="D210" t="str">
-        <v>NiftyPE</v>
+        <v>NiftyBullPE</v>
       </c>
       <c r="E210">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="F210">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="G210">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="H210">
-        <v>-19</v>
+        <v>-35</v>
       </c>
       <c r="I210">
         <v>0</v>
       </c>
       <c r="J210">
-        <v>-2496</v>
+        <v>-2291</v>
       </c>
       <c r="K210">
-        <v>-94</v>
+        <v>-80</v>
       </c>
       <c r="L210" t="str">
         <v>Yes</v>
@@ -10263,7 +10263,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N210">
-        <v>-2590</v>
+        <v>-2371</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -10277,31 +10277,31 @@
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>21-05-2026</v>
+        <v>22-05-2026</v>
       </c>
       <c r="D211" t="str">
-        <v>NiftyBullPE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E211">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F211">
-        <v>242</v>
+        <v>616</v>
       </c>
       <c r="G211">
-        <v>207</v>
+        <v>572</v>
       </c>
       <c r="H211">
-        <v>-35</v>
+        <v>-44</v>
       </c>
       <c r="I211">
         <v>0</v>
       </c>
       <c r="J211">
-        <v>-2291</v>
+        <v>-2648</v>
       </c>
       <c r="K211">
-        <v>-80</v>
+        <v>-98</v>
       </c>
       <c r="L211" t="str">
         <v>Yes</v>
@@ -10310,7 +10310,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N211">
-        <v>-2371</v>
+        <v>-2746</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -10327,25 +10327,25 @@
         <v>22-05-2026</v>
       </c>
       <c r="D212" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E212">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F212">
-        <v>616</v>
+        <v>500</v>
       </c>
       <c r="G212">
-        <v>572</v>
+        <v>469</v>
       </c>
       <c r="H212">
-        <v>-44</v>
+        <v>-31</v>
       </c>
       <c r="I212">
         <v>0</v>
       </c>
       <c r="J212">
-        <v>-2648</v>
+        <v>-2769</v>
       </c>
       <c r="K212">
         <v>-98</v>
@@ -10357,7 +10357,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N212">
-        <v>-2746</v>
+        <v>-2867</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -10371,31 +10371,31 @@
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>22-05-2026</v>
+        <v>25-05-2026</v>
       </c>
       <c r="D213" t="str">
-        <v>BankniftyCE</v>
+        <v>NiftyCE</v>
       </c>
       <c r="E213">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="F213">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="G213">
-        <v>469</v>
+        <v>170</v>
       </c>
       <c r="H213">
-        <v>-31</v>
+        <v>-19</v>
       </c>
       <c r="I213">
         <v>0</v>
       </c>
       <c r="J213">
-        <v>-2769</v>
+        <v>-3760</v>
       </c>
       <c r="K213">
-        <v>-98</v>
+        <v>-160</v>
       </c>
       <c r="L213" t="str">
         <v>Yes</v>
@@ -10404,7 +10404,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N213">
-        <v>-2867</v>
+        <v>-3920</v>
       </c>
       <c r="O213">
         <v>0</v>
@@ -10421,28 +10421,28 @@
         <v>25-05-2026</v>
       </c>
       <c r="D214" t="str">
-        <v>NiftyCE</v>
+        <v>Sensex CE</v>
       </c>
       <c r="E214">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="F214">
-        <v>190</v>
+        <v>613</v>
       </c>
       <c r="G214">
-        <v>170</v>
+        <v>570</v>
       </c>
       <c r="H214">
-        <v>-19</v>
+        <v>-43</v>
       </c>
       <c r="I214">
         <v>0</v>
       </c>
       <c r="J214">
-        <v>-3760</v>
+        <v>-2578</v>
       </c>
       <c r="K214">
-        <v>-160</v>
+        <v>-155</v>
       </c>
       <c r="L214" t="str">
         <v>Yes</v>
@@ -10451,7 +10451,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N214">
-        <v>-3920</v>
+        <v>-2733</v>
       </c>
       <c r="O214">
         <v>0</v>
@@ -10474,22 +10474,22 @@
         <v>60</v>
       </c>
       <c r="F215">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="G215">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="H215">
-        <v>-43</v>
+        <v>-58</v>
       </c>
       <c r="I215">
         <v>0</v>
       </c>
       <c r="J215">
-        <v>-2578</v>
+        <v>-3473</v>
       </c>
       <c r="K215">
-        <v>-155</v>
+        <v>-154</v>
       </c>
       <c r="L215" t="str">
         <v>Yes</v>
@@ -10498,7 +10498,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N215">
-        <v>-2733</v>
+        <v>-3627</v>
       </c>
       <c r="O215">
         <v>0</v>
@@ -10515,28 +10515,28 @@
         <v>25-05-2026</v>
       </c>
       <c r="D216" t="str">
-        <v>Sensex CE</v>
+        <v>BankniftyCE</v>
       </c>
       <c r="E216">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F216">
-        <v>606</v>
+        <v>482</v>
       </c>
       <c r="G216">
-        <v>548</v>
+        <v>430</v>
       </c>
       <c r="H216">
-        <v>-58</v>
+        <v>-52</v>
       </c>
       <c r="I216">
         <v>0</v>
       </c>
       <c r="J216">
-        <v>-3473</v>
+        <v>-4649</v>
       </c>
       <c r="K216">
-        <v>-154</v>
+        <v>-150</v>
       </c>
       <c r="L216" t="str">
         <v>Yes</v>
@@ -10545,7 +10545,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N216">
-        <v>-3627</v>
+        <v>-4799</v>
       </c>
       <c r="O216">
         <v>0</v>
@@ -10568,19 +10568,19 @@
         <v>90</v>
       </c>
       <c r="F217">
-        <v>482</v>
+        <v>497</v>
       </c>
       <c r="G217">
-        <v>430</v>
+        <v>611</v>
       </c>
       <c r="H217">
-        <v>-52</v>
+        <v>113</v>
       </c>
       <c r="I217">
-        <v>0</v>
+        <v>10197</v>
       </c>
       <c r="J217">
-        <v>-4649</v>
+        <v>0</v>
       </c>
       <c r="K217">
         <v>-150</v>
@@ -10589,10 +10589,10 @@
         <v>Yes</v>
       </c>
       <c r="M217" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N217">
-        <v>-4799</v>
+        <v>10047</v>
       </c>
       <c r="O217">
         <v>0</v>
@@ -10606,40 +10606,40 @@
         <v/>
       </c>
       <c r="C218" t="str">
-        <v>25-05-2026</v>
+        <v>26-05-2026</v>
       </c>
       <c r="D218" t="str">
-        <v>BankniftyCE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E218">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="F218">
-        <v>497</v>
+        <v>539</v>
       </c>
       <c r="G218">
-        <v>611</v>
+        <v>444</v>
       </c>
       <c r="H218">
-        <v>113</v>
+        <v>-95</v>
       </c>
       <c r="I218">
-        <v>10197</v>
+        <v>0</v>
       </c>
       <c r="J218">
-        <v>0</v>
+        <v>-5685</v>
       </c>
       <c r="K218">
-        <v>-150</v>
+        <v>-146</v>
       </c>
       <c r="L218" t="str">
         <v>Yes</v>
       </c>
       <c r="M218" t="str">
-        <v>Target Hit</v>
+        <v>Stop Loss Hit</v>
       </c>
       <c r="N218">
-        <v>10047</v>
+        <v>-5831</v>
       </c>
       <c r="O218">
         <v>0</v>
@@ -10656,25 +10656,25 @@
         <v>26-05-2026</v>
       </c>
       <c r="D219" t="str">
-        <v>Sensex PE</v>
+        <v>NiftyPE</v>
       </c>
       <c r="E219">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="F219">
-        <v>539</v>
+        <v>179</v>
       </c>
       <c r="G219">
-        <v>444</v>
+        <v>223</v>
       </c>
       <c r="H219">
-        <v>-95</v>
+        <v>44</v>
       </c>
       <c r="I219">
-        <v>0</v>
+        <v>8658</v>
       </c>
       <c r="J219">
-        <v>-5685</v>
+        <v>0</v>
       </c>
       <c r="K219">
         <v>-146</v>
@@ -10683,10 +10683,10 @@
         <v>Yes</v>
       </c>
       <c r="M219" t="str">
-        <v>Stop Loss Hit</v>
+        <v>Target Hit</v>
       </c>
       <c r="N219">
-        <v>-5831</v>
+        <v>8512</v>
       </c>
       <c r="O219">
         <v>0</v>
@@ -10700,31 +10700,31 @@
         <v/>
       </c>
       <c r="C220" t="str">
-        <v>26-05-2026</v>
+        <v>29-05-2026</v>
       </c>
       <c r="D220" t="str">
-        <v>NiftyPE</v>
+        <v>Sensex PE</v>
       </c>
       <c r="E220">
-        <v>195</v>
+        <v>60</v>
       </c>
       <c r="F220">
-        <v>179</v>
+        <v>396</v>
       </c>
       <c r="G220">
-        <v>223</v>
+        <v>493</v>
       </c>
       <c r="H220">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="I220">
-        <v>8658</v>
+        <v>5782</v>
       </c>
       <c r="J220">
         <v>0</v>
       </c>
       <c r="K220">
-        <v>-146</v>
+        <v>-61</v>
       </c>
       <c r="L220" t="str">
         <v>Yes</v>
@@ -10733,7 +10733,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N220">
-        <v>8512</v>
+        <v>5721</v>
       </c>
       <c r="O220">
         <v>0</v>
@@ -10747,40 +10747,40 @@
         <v/>
       </c>
       <c r="C221" t="str">
-        <v>29-05-2026</v>
+        <v>01-06-2026</v>
       </c>
       <c r="D221" t="str">
-        <v>Sensex PE</v>
+        <v>BankniftyPE</v>
       </c>
       <c r="E221">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F221">
-        <v>396</v>
+        <v>522.8</v>
       </c>
       <c r="G221">
-        <v>493</v>
+        <v>496.85</v>
       </c>
       <c r="H221">
-        <v>96</v>
+        <v>-25.949999999999932</v>
       </c>
       <c r="I221">
-        <v>5782</v>
+        <v>0</v>
       </c>
       <c r="J221">
-        <v>0</v>
+        <v>3243.999999999992</v>
       </c>
       <c r="K221">
-        <v>-61</v>
+        <v>130</v>
       </c>
       <c r="L221" t="str">
-        <v>Yes</v>
+        <v>YES</v>
       </c>
       <c r="M221" t="str">
-        <v>Target Hit</v>
+        <v/>
       </c>
       <c r="N221">
-        <v>5721</v>
+        <v>-3243.999999999992</v>
       </c>
       <c r="O221">
         <v>0</v>

--- a/server/trades.xlsx
+++ b/server/trades.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O221"/>
+  <dimension ref="A1:O220"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,7 +454,7 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>14-10-2025</v>
+        <v>14-10-2024</v>
       </c>
       <c r="D2" t="str">
         <v>BankniftyPE</v>
@@ -478,7 +478,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L2" t="str">
         <v>Yes</v>
@@ -501,7 +501,7 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>15-10-2025</v>
+        <v>15-10-2024</v>
       </c>
       <c r="D3" t="str">
         <v>NiftyCE</v>
@@ -525,7 +525,7 @@
         <v>-2254</v>
       </c>
       <c r="K3">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L3" t="str">
         <v>Yes</v>
@@ -548,7 +548,7 @@
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>15-10-2025</v>
+        <v>15-10-2024</v>
       </c>
       <c r="D4" t="str">
         <v>NiftyCE</v>
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L4" t="str">
         <v>Yes</v>
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>15-10-2025</v>
+        <v>15-10-2024</v>
       </c>
       <c r="D5" t="str">
         <v>BankniftyCE</v>
@@ -619,7 +619,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L5" t="str">
         <v>Yes</v>
@@ -642,7 +642,7 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>17-10-2025</v>
+        <v>17-10-2024</v>
       </c>
       <c r="D6" t="str">
         <v>Sensex CE</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L6" t="str">
         <v>Yes</v>
@@ -689,7 +689,7 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>17-10-2025</v>
+        <v>17-10-2024</v>
       </c>
       <c r="D7" t="str">
         <v>BankniftyCE</v>
@@ -713,7 +713,7 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L7" t="str">
         <v>Yes</v>
@@ -736,7 +736,7 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>17-10-2025</v>
+        <v>17-10-2024</v>
       </c>
       <c r="D8" t="str">
         <v>NiftyCE</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L8" t="str">
         <v>Yes</v>
@@ -783,7 +783,7 @@
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>17-10-2025</v>
+        <v>17-10-2024</v>
       </c>
       <c r="D9" t="str">
         <v>BankniftyPE</v>
@@ -807,7 +807,7 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L9" t="str">
         <v>Yes</v>
@@ -830,7 +830,7 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>20-10-2025</v>
+        <v>20-10-2024</v>
       </c>
       <c r="D10" t="str">
         <v>BankniftyCE</v>
@@ -854,7 +854,7 @@
         <v>-994</v>
       </c>
       <c r="K10">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L10" t="str">
         <v>Yes</v>
@@ -877,7 +877,7 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>23-10-2025</v>
+        <v>23-10-2024</v>
       </c>
       <c r="D11" t="str">
         <v>Sensex PE</v>
@@ -901,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L11" t="str">
         <v>Yes</v>
@@ -924,7 +924,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>23-10-2025</v>
+        <v>23-10-2024</v>
       </c>
       <c r="D12" t="str">
         <v>Sensex PE</v>
@@ -948,7 +948,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L12" t="str">
         <v>Yes</v>
@@ -971,7 +971,7 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>23-10-2025</v>
+        <v>23-10-2024</v>
       </c>
       <c r="D13" t="str">
         <v>NiftyCE</v>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L13" t="str">
         <v>Yes</v>
@@ -1018,7 +1018,7 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>24-10-2025</v>
+        <v>24-10-2024</v>
       </c>
       <c r="D14" t="str">
         <v>BankniftyPE</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L14" t="str">
         <v>Yes</v>
@@ -1065,7 +1065,7 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>27-10-2025</v>
+        <v>27-10-2024</v>
       </c>
       <c r="D15" t="str">
         <v>BankniftyCE</v>
@@ -1089,7 +1089,7 @@
         <v>-2107</v>
       </c>
       <c r="K15">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L15" t="str">
         <v>Yes</v>
@@ -1112,7 +1112,7 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>27-10-2025</v>
+        <v>27-10-2024</v>
       </c>
       <c r="D16" t="str">
         <v>Sensex CE</v>
@@ -1136,7 +1136,7 @@
         <v>-1501</v>
       </c>
       <c r="K16">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L16" t="str">
         <v>yes</v>
@@ -1159,7 +1159,7 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>29-10-2025</v>
+        <v>29-10-2024</v>
       </c>
       <c r="D17" t="str">
         <v>NiftyCE</v>
@@ -1183,7 +1183,7 @@
         <v>-1849</v>
       </c>
       <c r="K17">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L17" t="str">
         <v>yes</v>
@@ -1206,7 +1206,7 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>29-10-2025</v>
+        <v>29-10-2024</v>
       </c>
       <c r="D18" t="str">
         <v>BankniftyCE</v>
@@ -1230,7 +1230,7 @@
         <v>-693</v>
       </c>
       <c r="K18">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L18" t="str">
         <v>yes</v>
@@ -1253,7 +1253,7 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>30-10-2025</v>
+        <v>30-10-2024</v>
       </c>
       <c r="D19" t="str">
         <v>Sensex PE</v>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L19" t="str">
         <v>No</v>
@@ -1300,7 +1300,7 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>04-11-2025</v>
+        <v>04-11-2024</v>
       </c>
       <c r="D20" t="str">
         <v>NiftyPE</v>
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L20" t="str">
         <v>Yes</v>
@@ -1347,7 +1347,7 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>06-11-2025</v>
+        <v>06-11-2024</v>
       </c>
       <c r="D21" t="str">
         <v>BankniftyPE</v>
@@ -1371,7 +1371,7 @@
         <v>-2849</v>
       </c>
       <c r="K21">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L21" t="str">
         <v>Yes</v>
@@ -1394,7 +1394,7 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>07-11-2025</v>
+        <v>07-11-2024</v>
       </c>
       <c r="D22" t="str">
         <v>NiftyPE</v>
@@ -1418,7 +1418,7 @@
         <v>-3908</v>
       </c>
       <c r="K22">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L22" t="str">
         <v>yes</v>
@@ -1441,7 +1441,7 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>07-11-2025</v>
+        <v>07-11-2024</v>
       </c>
       <c r="D23" t="str">
         <v>Sensex PE</v>
@@ -1465,7 +1465,7 @@
         <v>-3834</v>
       </c>
       <c r="K23">
-        <v>-40</v>
+        <v>40</v>
       </c>
       <c r="L23" t="str">
         <v>Yes</v>
@@ -1488,7 +1488,7 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>07-11-2025</v>
+        <v>07-11-2024</v>
       </c>
       <c r="D24" t="str">
         <v>BankniftyCE</v>
@@ -1512,7 +1512,7 @@
         <v>-1751</v>
       </c>
       <c r="K24">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L24" t="str">
         <v>Yes</v>
@@ -1535,7 +1535,7 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>10-11-2025</v>
+        <v>10-11-2024</v>
       </c>
       <c r="D25" t="str">
         <v>NiftyCE</v>
@@ -1559,7 +1559,7 @@
         <v>-3788</v>
       </c>
       <c r="K25">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L25" t="str">
         <v>Yes</v>
@@ -1582,7 +1582,7 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>11-11-2025</v>
+        <v>11-11-2024</v>
       </c>
       <c r="D26" t="str">
         <v>Sensex PE</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>-40</v>
+        <v>40</v>
       </c>
       <c r="L26" t="str">
         <v>Yes</v>
@@ -1629,7 +1629,7 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>12-11-2025</v>
+        <v>12-11-2024</v>
       </c>
       <c r="D27" t="str">
         <v>NiftyCE</v>
@@ -1653,7 +1653,7 @@
         <v>-2940</v>
       </c>
       <c r="K27">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L27" t="str">
         <v>Yes</v>
@@ -1676,7 +1676,7 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>12-11-2025</v>
+        <v>12-11-2024</v>
       </c>
       <c r="D28" t="str">
         <v>NiftyCE</v>
@@ -1700,7 +1700,7 @@
         <v>-3383</v>
       </c>
       <c r="K28">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L28" t="str">
         <v>Yes</v>
@@ -1723,7 +1723,7 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>13-11-2025</v>
+        <v>13-11-2024</v>
       </c>
       <c r="D29" t="str">
         <v>NiftyCE</v>
@@ -1747,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L29" t="str">
         <v>Yes</v>
@@ -1770,7 +1770,7 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>14-11-2025</v>
+        <v>14-11-2024</v>
       </c>
       <c r="D30" t="str">
         <v>Sensex PE</v>
@@ -1794,7 +1794,7 @@
         <v>-4144</v>
       </c>
       <c r="K30">
-        <v>-40</v>
+        <v>40</v>
       </c>
       <c r="L30" t="str">
         <v>Yes</v>
@@ -1817,7 +1817,7 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>17-11-2025</v>
+        <v>17-11-2024</v>
       </c>
       <c r="D31" t="str">
         <v>BankniftyCE</v>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L31" t="str">
         <v>Yes</v>
@@ -1864,7 +1864,7 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>19-11-2025</v>
+        <v>19-11-2024</v>
       </c>
       <c r="D32" t="str">
         <v>BankniftyCE</v>
@@ -1888,7 +1888,7 @@
         <v>-739</v>
       </c>
       <c r="K32">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L32" t="str">
         <v>Yes</v>
@@ -1911,7 +1911,7 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>20-11-2025</v>
+        <v>20-11-2024</v>
       </c>
       <c r="D33" t="str">
         <v>Sensex CE</v>
@@ -1935,7 +1935,7 @@
         <v>-3002</v>
       </c>
       <c r="K33">
-        <v>-40</v>
+        <v>40</v>
       </c>
       <c r="L33" t="str">
         <v>Yes</v>
@@ -1958,7 +1958,7 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>21-11-2025</v>
+        <v>21-11-2024</v>
       </c>
       <c r="D34" t="str">
         <v>BankniftyPE</v>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L34" t="str">
         <v>Yes</v>
@@ -2005,7 +2005,7 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>24-11-2025</v>
+        <v>24-11-2024</v>
       </c>
       <c r="D35" t="str">
         <v>BankniftyCE</v>
@@ -2029,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L35" t="str">
         <v>Yes</v>
@@ -2052,7 +2052,7 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>24-11-2025</v>
+        <v>24-11-2024</v>
       </c>
       <c r="D36" t="str">
         <v>BankniftyPE</v>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>-54</v>
+        <v>54</v>
       </c>
       <c r="L36" t="str">
         <v>Yes</v>
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>26-11-2025</v>
+        <v>26-11-2024</v>
       </c>
       <c r="D37" t="str">
         <v>NiftyCE</v>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>-216</v>
+        <v>216</v>
       </c>
       <c r="L37" t="str">
         <v>No</v>
@@ -2146,7 +2146,7 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>03-12-2025</v>
+        <v>03-12-2024</v>
       </c>
       <c r="D38" t="str">
         <v>NiftyPE</v>
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L38" t="str">
         <v>Yes</v>
@@ -2193,7 +2193,7 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>03-12-2025</v>
+        <v>03-12-2024</v>
       </c>
       <c r="D39" t="str">
         <v>BankniftyPE</v>
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L39" t="str">
         <v>Yes</v>
@@ -2240,7 +2240,7 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>05-12-2025</v>
+        <v>05-12-2024</v>
       </c>
       <c r="D40" t="str">
         <v>NiftyCE</v>
@@ -2264,7 +2264,7 @@
         <v>-3004</v>
       </c>
       <c r="K40">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L40" t="str">
         <v>yes</v>
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>05-12-2025</v>
+        <v>05-12-2024</v>
       </c>
       <c r="D41" t="str">
         <v>BankniftyCE</v>
@@ -2311,7 +2311,7 @@
         <v>-2156</v>
       </c>
       <c r="K41">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L41" t="str">
         <v>Yes</v>
@@ -2334,7 +2334,7 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>10-12-2025</v>
+        <v>10-12-2024</v>
       </c>
       <c r="D42" t="str">
         <v>NiftyCE</v>
@@ -2358,7 +2358,7 @@
         <v>-1069</v>
       </c>
       <c r="K42">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L42" t="str">
         <v>Yes</v>
@@ -2381,7 +2381,7 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>11-12-2025</v>
+        <v>11-12-2024</v>
       </c>
       <c r="D43" t="str">
         <v>BankniftyCE</v>
@@ -2405,7 +2405,7 @@
         <v>-1936</v>
       </c>
       <c r="K43">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L43" t="str">
         <v>Yes</v>
@@ -2428,7 +2428,7 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>12-12-2025</v>
+        <v>12-12-2024</v>
       </c>
       <c r="D44" t="str">
         <v>Sensex CE</v>
@@ -2452,7 +2452,7 @@
         <v>-1901</v>
       </c>
       <c r="K44">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L44" t="str">
         <v>Yes</v>
@@ -2475,7 +2475,7 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>15-12-2025</v>
+        <v>15-12-2024</v>
       </c>
       <c r="D45" t="str">
         <v>NiftyPE</v>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L45" t="str">
         <v>Yes</v>
@@ -2522,7 +2522,7 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>16-12-2025</v>
+        <v>16-12-2024</v>
       </c>
       <c r="D46" t="str">
         <v>Sensex PE</v>
@@ -2569,7 +2569,7 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>16-12-2025</v>
+        <v>16-12-2024</v>
       </c>
       <c r="D47" t="str">
         <v>NiftyPE</v>
@@ -2593,7 +2593,7 @@
         <v>-1028</v>
       </c>
       <c r="K47">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L47" t="str">
         <v>Yes</v>
@@ -2616,7 +2616,7 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>18-12-2025</v>
+        <v>18-12-2024</v>
       </c>
       <c r="D48" t="str">
         <v>NiftyPE</v>
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L48" t="str">
         <v>Yes</v>
@@ -2663,7 +2663,7 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>19-12-2025</v>
+        <v>19-12-2024</v>
       </c>
       <c r="D49" t="str">
         <v>NiftyCE</v>
@@ -2687,7 +2687,7 @@
         <v>-990</v>
       </c>
       <c r="K49">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L49" t="str">
         <v>Yes</v>
@@ -2710,7 +2710,7 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>19-12-2025</v>
+        <v>19-12-2024</v>
       </c>
       <c r="D50" t="str">
         <v>Sensex CE</v>
@@ -2734,7 +2734,7 @@
         <v>-724</v>
       </c>
       <c r="K50">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L50" t="str">
         <v>Yes</v>
@@ -2757,7 +2757,7 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>22-12-2025</v>
+        <v>22-12-2024</v>
       </c>
       <c r="D51" t="str">
         <v>BankniftyCE</v>
@@ -2781,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L51" t="str">
         <v>Yes</v>
@@ -2804,7 +2804,7 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>22-12-2025</v>
+        <v>22-12-2024</v>
       </c>
       <c r="D52" t="str">
         <v>NiftyCE</v>
@@ -2828,7 +2828,7 @@
         <v>-270</v>
       </c>
       <c r="K52">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L52" t="str">
         <v>Yes</v>
@@ -2851,7 +2851,7 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>22-12-2025</v>
+        <v>22-12-2024</v>
       </c>
       <c r="D53" t="str">
         <v>Sensex CE</v>
@@ -2875,7 +2875,7 @@
         <v>-955</v>
       </c>
       <c r="K53">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L53" t="str">
         <v>Yes</v>
@@ -2898,7 +2898,7 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>24-12-2025</v>
+        <v>24-12-2024</v>
       </c>
       <c r="D54" t="str">
         <v>BankniftyCE</v>
@@ -2922,7 +2922,7 @@
         <v>-518</v>
       </c>
       <c r="K54">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L54" t="str">
         <v>Yes</v>
@@ -2945,7 +2945,7 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>24-12-2025</v>
+        <v>24-12-2024</v>
       </c>
       <c r="D55" t="str">
         <v>BankniftyPE</v>
@@ -2969,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L55" t="str">
         <v>Yes</v>
@@ -2992,7 +2992,7 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>24-12-2025</v>
+        <v>24-12-2024</v>
       </c>
       <c r="D56" t="str">
         <v>NiftyPE</v>
@@ -3016,7 +3016,7 @@
         <v>-1193</v>
       </c>
       <c r="K56">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L56" t="str">
         <v>Yes</v>
@@ -3039,7 +3039,7 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>26-12-2025</v>
+        <v>26-12-2024</v>
       </c>
       <c r="D57" t="str">
         <v>BankniftyPE</v>
@@ -3063,7 +3063,7 @@
         <v>-406</v>
       </c>
       <c r="K57">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L57" t="str">
         <v>Yes</v>
@@ -3086,7 +3086,7 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>29-12-2025</v>
+        <v>29-12-2024</v>
       </c>
       <c r="D58" t="str">
         <v>BankniftyPE</v>
@@ -3110,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L58" t="str">
         <v>Yes</v>
@@ -3133,7 +3133,7 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>29-12-2025</v>
+        <v>29-12-2024</v>
       </c>
       <c r="D59" t="str">
         <v>NiftyPE</v>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L59" t="str">
         <v>Yes</v>
@@ -3180,7 +3180,7 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>30-12-2025</v>
+        <v>30-12-2024</v>
       </c>
       <c r="D60" t="str">
         <v>BankniftyPE</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L60" t="str">
         <v>Yes</v>
@@ -3227,7 +3227,7 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>30-12-2025</v>
+        <v>30-12-2024</v>
       </c>
       <c r="D61" t="str">
         <v>NiftyPE</v>
@@ -3251,7 +3251,7 @@
         <v>-1958</v>
       </c>
       <c r="K61">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L61" t="str">
         <v>Yes</v>
@@ -3274,7 +3274,7 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>30-12-2025</v>
+        <v>30-12-2024</v>
       </c>
       <c r="D62" t="str">
         <v>Sensex PE</v>
@@ -3298,7 +3298,7 @@
         <v>-1747</v>
       </c>
       <c r="K62">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L62" t="str">
         <v>Yes</v>
@@ -3321,7 +3321,7 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>31-12-2025</v>
+        <v>31-12-2024</v>
       </c>
       <c r="D63" t="str">
         <v>BankniftyCE</v>
@@ -3345,7 +3345,7 @@
         <v>-458</v>
       </c>
       <c r="K63">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L63" t="str">
         <v>Yes</v>
@@ -3368,7 +3368,7 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>31-12-2025</v>
+        <v>31-12-2024</v>
       </c>
       <c r="D64" t="str">
         <v>NiftyCE</v>
@@ -3392,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L64" t="str">
         <v>Yes</v>
@@ -3415,7 +3415,7 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>31-12-2025</v>
+        <v>31-12-2024</v>
       </c>
       <c r="D65" t="str">
         <v>BankniftyCE</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L65" t="str">
         <v>Yes</v>
@@ -3462,7 +3462,7 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>31-12-2025</v>
+        <v>31-12-2024</v>
       </c>
       <c r="D66" t="str">
         <v>Sensex CE</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L66" t="str">
         <v>Yes</v>
@@ -3509,7 +3509,7 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>31-12-2025</v>
+        <v>31-12-2024</v>
       </c>
       <c r="D67" t="str">
         <v>Sensex CE</v>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L67" t="str">
         <v>Yes</v>
@@ -3556,7 +3556,7 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>31-12-2025</v>
+        <v>31-12-2024</v>
       </c>
       <c r="D68" t="str">
         <v>Sensex CE</v>
@@ -3580,7 +3580,7 @@
         <v>-136</v>
       </c>
       <c r="K68">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L68" t="str">
         <v>Yes</v>
@@ -3603,7 +3603,7 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>02-01-2026</v>
+        <v>02-01-2025</v>
       </c>
       <c r="D69" t="str">
         <v>NiftyCE</v>
@@ -3627,7 +3627,7 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L69" t="str">
         <v>Yes</v>
@@ -3650,7 +3650,7 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>02-01-2026</v>
+        <v>02-01-2025</v>
       </c>
       <c r="D70" t="str">
         <v>Sensex CE</v>
@@ -3674,7 +3674,7 @@
         <v>-99</v>
       </c>
       <c r="K70">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L70" t="str">
         <v>Yes</v>
@@ -3697,7 +3697,7 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>02-01-2026</v>
+        <v>02-01-2025</v>
       </c>
       <c r="D71" t="str">
         <v>Sensex CE</v>
@@ -3721,7 +3721,7 @@
         <v>-641</v>
       </c>
       <c r="K71">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L71" t="str">
         <v>Yes</v>
@@ -3744,7 +3744,7 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>05-01-2026</v>
+        <v>05-01-2025</v>
       </c>
       <c r="D72" t="str">
         <v>NiftyPE</v>
@@ -3768,7 +3768,7 @@
         <v>-488</v>
       </c>
       <c r="K72">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L72" t="str">
         <v>Yes</v>
@@ -3791,7 +3791,7 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>06-01-2026</v>
+        <v>06-01-2025</v>
       </c>
       <c r="D73" t="str">
         <v>Sensex PE</v>
@@ -3815,7 +3815,7 @@
         <v>-1945</v>
       </c>
       <c r="K73">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L73" t="str">
         <v>Yes</v>
@@ -3838,7 +3838,7 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>07-01-2026</v>
+        <v>07-01-2025</v>
       </c>
       <c r="D74" t="str">
         <v>BankniftyPE</v>
@@ -3862,7 +3862,7 @@
         <v>-842</v>
       </c>
       <c r="K74">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L74" t="str">
         <v>Yes</v>
@@ -3885,7 +3885,7 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>08-01-2026</v>
+        <v>08-01-2025</v>
       </c>
       <c r="D75" t="str">
         <v>NiftyPE</v>
@@ -3909,7 +3909,7 @@
         <v>-744</v>
       </c>
       <c r="K75">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L75" t="str">
         <v>Yes</v>
@@ -3932,7 +3932,7 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>08-01-2026</v>
+        <v>08-01-2025</v>
       </c>
       <c r="D76" t="str">
         <v>BankniftyPE</v>
@@ -3956,7 +3956,7 @@
         <v>-900</v>
       </c>
       <c r="K76">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L76" t="str">
         <v>Yes</v>
@@ -3979,7 +3979,7 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>09-01-2026</v>
+        <v>09-01-2025</v>
       </c>
       <c r="D77" t="str">
         <v>NiftyPE</v>
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L77" t="str">
         <v>Yes</v>
@@ -4026,7 +4026,7 @@
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>09-01-2026</v>
+        <v>09-01-2025</v>
       </c>
       <c r="D78" t="str">
         <v>BankniftyPE</v>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L78" t="str">
         <v>Yes</v>
@@ -4073,7 +4073,7 @@
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>12-01-2026</v>
+        <v>12-01-2025</v>
       </c>
       <c r="D79" t="str">
         <v>NiftyPE</v>
@@ -4097,7 +4097,7 @@
         <v>-1723</v>
       </c>
       <c r="K79">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L79" t="str">
         <v>Yes</v>
@@ -4120,7 +4120,7 @@
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>13-01-2026</v>
+        <v>13-01-2025</v>
       </c>
       <c r="D80" t="str">
         <v>NiftyPE</v>
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L80" t="str">
         <v>Yes</v>
@@ -4167,7 +4167,7 @@
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>13-01-2026</v>
+        <v>13-01-2025</v>
       </c>
       <c r="D81" t="str">
         <v>BankniftyPE</v>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L81" t="str">
         <v>Yes</v>
@@ -4214,7 +4214,7 @@
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>14-01-2026</v>
+        <v>14-01-2025</v>
       </c>
       <c r="D82" t="str">
         <v>Sensex PE</v>
@@ -4238,7 +4238,7 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L82" t="str">
         <v>Yes</v>
@@ -4261,7 +4261,7 @@
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>16-01-2026</v>
+        <v>16-01-2025</v>
       </c>
       <c r="D83" t="str">
         <v>BankniftyCE</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L83" t="str">
         <v>Yes</v>
@@ -4308,7 +4308,7 @@
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>16-01-2026</v>
+        <v>16-01-2025</v>
       </c>
       <c r="D84" t="str">
         <v>Sensex CE</v>
@@ -4332,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L84" t="str">
         <v>Yes</v>
@@ -4355,7 +4355,7 @@
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>19-01-2026</v>
+        <v>19-01-2025</v>
       </c>
       <c r="D85" t="str">
         <v>Sensex PE</v>
@@ -4379,7 +4379,7 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L85" t="str">
         <v>Yes</v>
@@ -4402,7 +4402,7 @@
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>19-01-2026</v>
+        <v>19-01-2025</v>
       </c>
       <c r="D86" t="str">
         <v>BankniftyPE</v>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L86" t="str">
         <v>No</v>
@@ -4449,7 +4449,7 @@
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>20-01-2026</v>
+        <v>20-01-2025</v>
       </c>
       <c r="D87" t="str">
         <v>Sensex PE</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L87" t="str">
         <v>Yes</v>
@@ -4496,7 +4496,7 @@
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>21-01-2026</v>
+        <v>21-01-2025</v>
       </c>
       <c r="D88" t="str">
         <v>BankniftyPE</v>
@@ -4520,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L88" t="str">
         <v>No</v>
@@ -4543,7 +4543,7 @@
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>22-01-2026</v>
+        <v>22-01-2025</v>
       </c>
       <c r="D89" t="str">
         <v>BankniftyCE</v>
@@ -4567,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L89" t="str">
         <v>No</v>
@@ -4590,7 +4590,7 @@
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>22-01-2026</v>
+        <v>22-01-2025</v>
       </c>
       <c r="D90" t="str">
         <v>NiftyCE</v>
@@ -4614,7 +4614,7 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>-26</v>
+        <v>26</v>
       </c>
       <c r="L90" t="str">
         <v>No</v>
@@ -4637,7 +4637,7 @@
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>22-01-2026</v>
+        <v>22-01-2025</v>
       </c>
       <c r="D91" t="str">
         <v>Sensex CE</v>
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>-24</v>
+        <v>24</v>
       </c>
       <c r="L91" t="str">
         <v>No</v>
@@ -4684,7 +4684,7 @@
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>23-01-2026</v>
+        <v>23-01-2025</v>
       </c>
       <c r="D92" t="str">
         <v>Sensex PE</v>
@@ -4708,7 +4708,7 @@
         <v>-353</v>
       </c>
       <c r="K92">
-        <v>-98</v>
+        <v>98</v>
       </c>
       <c r="L92" t="str">
         <v>Yes</v>
@@ -4731,7 +4731,7 @@
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>23-01-2026</v>
+        <v>23-01-2025</v>
       </c>
       <c r="D93" t="str">
         <v>NiftyPE</v>
@@ -4755,7 +4755,7 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="L93" t="str">
         <v>No</v>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>23-01-2026</v>
+        <v>23-01-2025</v>
       </c>
       <c r="D94" t="str">
         <v>BankniftyPE</v>
@@ -4802,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>-80</v>
+        <v>80</v>
       </c>
       <c r="L94" t="str">
         <v>Yes</v>
@@ -4825,7 +4825,7 @@
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>29-01-2026</v>
+        <v>29-01-2025</v>
       </c>
       <c r="D95" t="str">
         <v>Sensex PE</v>
@@ -4849,7 +4849,7 @@
         <v>-1886</v>
       </c>
       <c r="K95">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L95" t="str">
         <v>Yes</v>
@@ -4872,7 +4872,7 @@
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>30-01-2026</v>
+        <v>30-01-2025</v>
       </c>
       <c r="D96" t="str">
         <v>BankniftyPE</v>
@@ -4896,7 +4896,7 @@
         <v>-454</v>
       </c>
       <c r="K96">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L96" t="str">
         <v>Yes</v>
@@ -4919,7 +4919,7 @@
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>05-02-2026</v>
+        <v>05-02-2025</v>
       </c>
       <c r="D97" t="str">
         <v>NiftyPE</v>
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L97" t="str">
         <v>Yes</v>
@@ -4966,7 +4966,7 @@
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>05-02-2026</v>
+        <v>05-02-2025</v>
       </c>
       <c r="D98" t="str">
         <v>Sensex PE</v>
@@ -4990,7 +4990,7 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>-22</v>
+        <v>22</v>
       </c>
       <c r="L98" t="str">
         <v>Yes</v>
@@ -5013,7 +5013,7 @@
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>06-02-2026</v>
+        <v>06-02-2025</v>
       </c>
       <c r="D99" t="str">
         <v>Sensex PE</v>
@@ -5037,7 +5037,7 @@
         <v>-1043</v>
       </c>
       <c r="K99">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L99" t="str">
         <v>No</v>
@@ -5060,7 +5060,7 @@
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>09-02-2026</v>
+        <v>09-02-2025</v>
       </c>
       <c r="D100" t="str">
         <v>NiftyCE</v>
@@ -5084,7 +5084,7 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L100" t="str">
         <v>Yes</v>
@@ -5107,7 +5107,7 @@
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>09-02-2026</v>
+        <v>09-02-2025</v>
       </c>
       <c r="D101" t="str">
         <v>BankniftyCE</v>
@@ -5131,7 +5131,7 @@
         <v>-431</v>
       </c>
       <c r="K101">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L101" t="str">
         <v>No</v>
@@ -5154,7 +5154,7 @@
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>10-02-2026</v>
+        <v>10-02-2025</v>
       </c>
       <c r="D102" t="str">
         <v>NiftyCE</v>
@@ -5178,7 +5178,7 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L102" t="str">
         <v>Yes</v>
@@ -5201,7 +5201,7 @@
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>10-02-2026</v>
+        <v>10-02-2025</v>
       </c>
       <c r="D103" t="str">
         <v>Sensex CE</v>
@@ -5225,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L103" t="str">
         <v>Yes</v>
@@ -5248,7 +5248,7 @@
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>10-02-2026</v>
+        <v>10-02-2025</v>
       </c>
       <c r="D104" t="str">
         <v>BankniftyPE</v>
@@ -5272,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L104" t="str">
         <v>Yes</v>
@@ -5295,7 +5295,7 @@
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>11-02-2026</v>
+        <v>11-02-2025</v>
       </c>
       <c r="D105" t="str">
         <v>BankniftyCE</v>
@@ -5319,7 +5319,7 @@
         <v>-1551</v>
       </c>
       <c r="K105">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L105" t="str">
         <v>No</v>
@@ -5342,7 +5342,7 @@
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>12-02-2026</v>
+        <v>12-02-2025</v>
       </c>
       <c r="D106" t="str">
         <v>Sensex PE</v>
@@ -5366,7 +5366,7 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L106" t="str">
         <v>Yes</v>
@@ -5389,7 +5389,7 @@
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>12-02-2026</v>
+        <v>12-02-2025</v>
       </c>
       <c r="D107" t="str">
         <v>BankniftyPE</v>
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L107" t="str">
         <v>Yes</v>
@@ -5436,7 +5436,7 @@
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>13-02-2026</v>
+        <v>13-02-2025</v>
       </c>
       <c r="D108" t="str">
         <v>Sensex PE</v>
@@ -5460,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L108" t="str">
         <v>Yes</v>
@@ -5483,7 +5483,7 @@
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>18-02-2026</v>
+        <v>18-02-2025</v>
       </c>
       <c r="D109" t="str">
         <v>Sensex PE</v>
@@ -5507,7 +5507,7 @@
         <v>-2007</v>
       </c>
       <c r="K109">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L109" t="str">
         <v>Yes</v>
@@ -5530,7 +5530,7 @@
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>18-02-2026</v>
+        <v>18-02-2025</v>
       </c>
       <c r="D110" t="str">
         <v>BankniftyCE</v>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L110" t="str">
         <v>No</v>
@@ -5577,7 +5577,7 @@
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>19-02-2026</v>
+        <v>19-02-2025</v>
       </c>
       <c r="D111" t="str">
         <v>Sensex PE</v>
@@ -5601,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L111" t="str">
         <v>Yes</v>
@@ -5624,7 +5624,7 @@
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>20-02-2026</v>
+        <v>20-02-2025</v>
       </c>
       <c r="D112" t="str">
         <v>BankniftyCE</v>
@@ -5648,7 +5648,7 @@
         <v>-1649</v>
       </c>
       <c r="K112">
-        <v>-28</v>
+        <v>28</v>
       </c>
       <c r="L112" t="str">
         <v>Yes</v>
@@ -5671,7 +5671,7 @@
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>24-02-2026</v>
+        <v>24-02-2025</v>
       </c>
       <c r="D113" t="str">
         <v>Sensex PE</v>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L113" t="str">
         <v>Yes</v>
@@ -5718,7 +5718,7 @@
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>24-02-2026</v>
+        <v>24-02-2025</v>
       </c>
       <c r="D114" t="str">
         <v>NiftyPE</v>
@@ -5742,7 +5742,7 @@
         <v>0</v>
       </c>
       <c r="K114">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L114" t="str">
         <v>Yes</v>
@@ -5765,7 +5765,7 @@
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>25-02-2026</v>
+        <v>25-02-2025</v>
       </c>
       <c r="D115" t="str">
         <v>NiftyCE</v>
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="K115">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L115" t="str">
         <v>Yes</v>
@@ -5812,7 +5812,7 @@
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>25-02-2026</v>
+        <v>25-02-2025</v>
       </c>
       <c r="D116" t="str">
         <v>NiftyCE</v>
@@ -5836,7 +5836,7 @@
         <v>-1342</v>
       </c>
       <c r="K116">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L116" t="str">
         <v>Yes</v>
@@ -5859,7 +5859,7 @@
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>25-02-2026</v>
+        <v>25-02-2025</v>
       </c>
       <c r="D117" t="str">
         <v>NiftyPE</v>
@@ -5883,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L117" t="str">
         <v>Yes</v>
@@ -5906,7 +5906,7 @@
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>27-02-2026</v>
+        <v>27-02-2025</v>
       </c>
       <c r="D118" t="str">
         <v>NiftyPE</v>
@@ -5930,7 +5930,7 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L118" t="str">
         <v>Yes</v>
@@ -5953,7 +5953,7 @@
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>02-03-2026</v>
+        <v>02-03-2025</v>
       </c>
       <c r="D119" t="str">
         <v>NiftyPE</v>
@@ -5977,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L119" t="str">
         <v>Yes</v>
@@ -6000,7 +6000,7 @@
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>05-03-2026</v>
+        <v>05-03-2025</v>
       </c>
       <c r="D120" t="str">
         <v>NiftyCE</v>
@@ -6024,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L120" t="str">
         <v>Yes</v>
@@ -6047,7 +6047,7 @@
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>11-03-2026</v>
+        <v>11-03-2025</v>
       </c>
       <c r="D121" t="str">
         <v>BankniftyPE</v>
@@ -6071,7 +6071,7 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>-32</v>
+        <v>32</v>
       </c>
       <c r="L121" t="str">
         <v>Yes</v>
@@ -6094,7 +6094,7 @@
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>11-03-2026</v>
+        <v>11-03-2025</v>
       </c>
       <c r="D122" t="str">
         <v>Sensex PE</v>
@@ -6118,7 +6118,7 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>-30</v>
+        <v>30</v>
       </c>
       <c r="L122" t="str">
         <v>Yes</v>
@@ -6141,7 +6141,7 @@
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>13-03-2026</v>
+        <v>13-03-2025</v>
       </c>
       <c r="D123" t="str">
         <v>BankniftyPE</v>
@@ -6165,7 +6165,7 @@
         <v>-2076</v>
       </c>
       <c r="K123">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L123" t="str">
         <v>Yes</v>
@@ -6188,7 +6188,7 @@
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>13-03-2026</v>
+        <v>13-03-2025</v>
       </c>
       <c r="D124" t="str">
         <v>Sensex PE</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L124" t="str">
         <v>Yes</v>
@@ -6235,7 +6235,7 @@
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>18-03-2026</v>
+        <v>18-03-2025</v>
       </c>
       <c r="D125" t="str">
         <v>Sensex CE</v>
@@ -6259,7 +6259,7 @@
         <v>-1471</v>
       </c>
       <c r="K125">
-        <v>-18</v>
+        <v>18</v>
       </c>
       <c r="L125" t="str">
         <v>Yes</v>
@@ -6282,7 +6282,7 @@
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>18-03-2026</v>
+        <v>18-03-2025</v>
       </c>
       <c r="D126" t="str">
         <v>BankniftyCE</v>
@@ -6306,7 +6306,7 @@
         <v>-1766</v>
       </c>
       <c r="K126">
-        <v>-18</v>
+        <v>18</v>
       </c>
       <c r="L126" t="str">
         <v>Yes</v>
@@ -6329,7 +6329,7 @@
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>18-03-2026</v>
+        <v>18-03-2025</v>
       </c>
       <c r="D127" t="str">
         <v>NiftyCE</v>
@@ -6353,7 +6353,7 @@
         <v>-1892</v>
       </c>
       <c r="K127">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L127" t="str">
         <v>Yes</v>
@@ -6376,7 +6376,7 @@
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>19-03-2026</v>
+        <v>19-03-2025</v>
       </c>
       <c r="D128" t="str">
         <v>NiftyPE</v>
@@ -6400,7 +6400,7 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L128" t="str">
         <v>Yes</v>
@@ -6423,7 +6423,7 @@
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>23-03-2026</v>
+        <v>23-03-2025</v>
       </c>
       <c r="D129" t="str">
         <v>BankniftyPE</v>
@@ -6447,7 +6447,7 @@
         <v>-2081</v>
       </c>
       <c r="K129">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="L129" t="str">
         <v>Yes</v>
@@ -6470,7 +6470,7 @@
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>25-03-2026</v>
+        <v>25-03-2025</v>
       </c>
       <c r="D130" t="str">
         <v>BankniftyCE</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L130" t="str">
         <v>Yes</v>
@@ -6517,7 +6517,7 @@
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>25-03-2026</v>
+        <v>25-03-2025</v>
       </c>
       <c r="D131" t="str">
         <v>NiftyCE</v>
@@ -6541,7 +6541,7 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L131" t="str">
         <v>Yes</v>
@@ -6564,7 +6564,7 @@
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>25-03-2026</v>
+        <v>25-03-2025</v>
       </c>
       <c r="D132" t="str">
         <v>Sensex CE</v>
@@ -6588,7 +6588,7 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L132" t="str">
         <v>Yes</v>
@@ -6611,7 +6611,7 @@
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>27-03-2026</v>
+        <v>27-03-2025</v>
       </c>
       <c r="D133" t="str">
         <v>BankniftyPE</v>
@@ -6635,7 +6635,7 @@
         <v>-2082</v>
       </c>
       <c r="K133">
-        <v>-27</v>
+        <v>27</v>
       </c>
       <c r="L133" t="str">
         <v>Yes</v>
@@ -6658,7 +6658,7 @@
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>08-04-2026</v>
+        <v>08-04-2025</v>
       </c>
       <c r="D134" t="str">
         <v>BankniftyCE</v>
@@ -6682,7 +6682,7 @@
         <v>-3247</v>
       </c>
       <c r="K134">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="L134" t="str">
         <v>Yes</v>
@@ -6705,7 +6705,7 @@
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>10-04-2026</v>
+        <v>10-04-2025</v>
       </c>
       <c r="D135" t="str">
         <v>NiftyCE</v>
@@ -6729,7 +6729,7 @@
         <v>-3790</v>
       </c>
       <c r="K135">
-        <v>-102</v>
+        <v>102</v>
       </c>
       <c r="L135" t="str">
         <v>Yes</v>
@@ -6752,7 +6752,7 @@
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>16-04-2026</v>
+        <v>16-04-2025</v>
       </c>
       <c r="D136" t="str">
         <v>NiftyCE</v>
@@ -6776,7 +6776,7 @@
         <v>-4817</v>
       </c>
       <c r="K136">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L136" t="str">
         <v>Yes</v>
@@ -6799,7 +6799,7 @@
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>16-04-2026</v>
+        <v>16-04-2025</v>
       </c>
       <c r="D137" t="str">
         <v>NiftyPE</v>
@@ -6823,7 +6823,7 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>-80</v>
+        <v>80</v>
       </c>
       <c r="L137" t="str">
         <v>Yes</v>
@@ -6846,7 +6846,7 @@
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>16-04-2026</v>
+        <v>16-04-2025</v>
       </c>
       <c r="D138" t="str">
         <v>Sensex CE</v>
@@ -6870,7 +6870,7 @@
         <v>-4684</v>
       </c>
       <c r="K138">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L138" t="str">
         <v>Yes</v>
@@ -6893,7 +6893,7 @@
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>16-04-2026</v>
+        <v>16-04-2025</v>
       </c>
       <c r="D139" t="str">
         <v>Sensex PE</v>
@@ -6917,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="K139">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L139" t="str">
         <v>Yes</v>
@@ -6940,7 +6940,7 @@
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>16-04-2026</v>
+        <v>16-04-2025</v>
       </c>
       <c r="D140" t="str">
         <v>NiftyBullCE</v>
@@ -6964,7 +6964,7 @@
         <v>-2610</v>
       </c>
       <c r="K140">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L140" t="str">
         <v>Yes</v>
@@ -6987,7 +6987,7 @@
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>16-04-2026</v>
+        <v>16-04-2025</v>
       </c>
       <c r="D141" t="str">
         <v>NiftyBullPE</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L141" t="str">
         <v>Yes</v>
@@ -7034,7 +7034,7 @@
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>17-04-2026</v>
+        <v>17-04-2025</v>
       </c>
       <c r="D142" t="str">
         <v>NiftyCE</v>
@@ -7058,7 +7058,7 @@
         <v>-1573</v>
       </c>
       <c r="K142">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L142" t="str">
         <v>Yes</v>
@@ -7081,7 +7081,7 @@
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>17-04-2026</v>
+        <v>17-04-2025</v>
       </c>
       <c r="D143" t="str">
         <v>NiftyBullCE</v>
@@ -7105,7 +7105,7 @@
         <v>-926</v>
       </c>
       <c r="K143">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L143" t="str">
         <v>Yes</v>
@@ -7128,7 +7128,7 @@
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>20-04-2026</v>
+        <v>20-04-2025</v>
       </c>
       <c r="D144" t="str">
         <v>SensexBullCE</v>
@@ -7152,7 +7152,7 @@
         <v>-168</v>
       </c>
       <c r="K144">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L144" t="str">
         <v>Yes</v>
@@ -7175,7 +7175,7 @@
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>20-04-2026</v>
+        <v>20-04-2025</v>
       </c>
       <c r="D145" t="str">
         <v>NiftyBullPE</v>
@@ -7199,7 +7199,7 @@
         <v>-2285</v>
       </c>
       <c r="K145">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L145" t="str">
         <v>Yes</v>
@@ -7222,7 +7222,7 @@
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>20-04-2026</v>
+        <v>20-04-2025</v>
       </c>
       <c r="D146" t="str">
         <v>BankniftyPE</v>
@@ -7246,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="L146" t="str">
         <v>Yes</v>
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>20-04-2026</v>
+        <v>20-04-2025</v>
       </c>
       <c r="D147" t="str">
         <v>BankniftyCE</v>
@@ -7293,7 +7293,7 @@
         <v>-3345</v>
       </c>
       <c r="K147">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="L147" t="str">
         <v>Yes</v>
@@ -7316,7 +7316,7 @@
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>21-04-2026</v>
+        <v>21-04-2025</v>
       </c>
       <c r="D148" t="str">
         <v>Sensex CE</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L148" t="str">
         <v>Yes</v>
@@ -7363,7 +7363,7 @@
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>21-04-2026</v>
+        <v>21-04-2025</v>
       </c>
       <c r="D149" t="str">
         <v>SensexBullCE</v>
@@ -7387,7 +7387,7 @@
         <v>-392</v>
       </c>
       <c r="K149">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L149" t="str">
         <v>Yes</v>
@@ -7410,7 +7410,7 @@
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>22-04-2026</v>
+        <v>22-04-2025</v>
       </c>
       <c r="D150" t="str">
         <v>NiftyBullPE</v>
@@ -7434,7 +7434,7 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L150" t="str">
         <v>Yes</v>
@@ -7457,7 +7457,7 @@
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>22-04-2026</v>
+        <v>22-04-2025</v>
       </c>
       <c r="D151" t="str">
         <v>NiftyPE</v>
@@ -7481,7 +7481,7 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L151" t="str">
         <v>Yes</v>
@@ -7504,7 +7504,7 @@
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>23-04-2026</v>
+        <v>23-04-2025</v>
       </c>
       <c r="D152" t="str">
         <v>NiftyPE</v>
@@ -7528,7 +7528,7 @@
         <v>-4004</v>
       </c>
       <c r="K152">
-        <v>-94</v>
+        <v>94</v>
       </c>
       <c r="L152" t="str">
         <v>Yes</v>
@@ -7551,7 +7551,7 @@
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>23-04-2026</v>
+        <v>23-04-2025</v>
       </c>
       <c r="D153" t="str">
         <v>NiftyBullPE</v>
@@ -7575,7 +7575,7 @@
         <v>-2278</v>
       </c>
       <c r="K153">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L153" t="str">
         <v>Yes</v>
@@ -7598,7 +7598,7 @@
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>28-04-2026</v>
+        <v>28-04-2025</v>
       </c>
       <c r="D154" t="str">
         <v>NiftyPE</v>
@@ -7622,7 +7622,7 @@
         <v>-4804</v>
       </c>
       <c r="K154">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L154" t="str">
         <v>Yes</v>
@@ -7645,7 +7645,7 @@
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>28-04-2026</v>
+        <v>28-04-2025</v>
       </c>
       <c r="D155" t="str">
         <v>BankniftyPE</v>
@@ -7669,7 +7669,7 @@
         <v>-4189</v>
       </c>
       <c r="K155">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L155" t="str">
         <v>Yes</v>
@@ -7692,7 +7692,7 @@
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>28-04-2026</v>
+        <v>28-04-2025</v>
       </c>
       <c r="D156" t="str">
         <v>NiftyBullPE</v>
@@ -7716,7 +7716,7 @@
         <v>-2301</v>
       </c>
       <c r="K156">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="L156" t="str">
         <v>Yes</v>
@@ -7739,7 +7739,7 @@
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>28-04-2026</v>
+        <v>28-04-2025</v>
       </c>
       <c r="D157" t="str">
         <v>SensexBullPE</v>
@@ -7763,7 +7763,7 @@
         <v>-2005</v>
       </c>
       <c r="K157">
-        <v>-91</v>
+        <v>91</v>
       </c>
       <c r="L157" t="str">
         <v>Yes</v>
@@ -7786,7 +7786,7 @@
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>29-04-2026</v>
+        <v>29-04-2025</v>
       </c>
       <c r="D158" t="str">
         <v>NiftyCE</v>
@@ -7810,7 +7810,7 @@
         <v>0</v>
       </c>
       <c r="K158">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L158" t="str">
         <v>Yes</v>
@@ -7833,7 +7833,7 @@
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>29-04-2026</v>
+        <v>29-04-2025</v>
       </c>
       <c r="D159" t="str">
         <v>Sensex CE</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="K159">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L159" t="str">
         <v>Yes</v>
@@ -7880,7 +7880,7 @@
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>29-04-2026</v>
+        <v>29-04-2025</v>
       </c>
       <c r="D160" t="str">
         <v>NiftyBullCE</v>
@@ -7904,7 +7904,7 @@
         <v>0</v>
       </c>
       <c r="K160">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L160" t="str">
         <v>Yes</v>
@@ -7927,7 +7927,7 @@
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>29-04-2026</v>
+        <v>29-04-2025</v>
       </c>
       <c r="D161" t="str">
         <v>SensexBullCE</v>
@@ -7951,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="K161">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L161" t="str">
         <v>Yes</v>
@@ -7974,7 +7974,7 @@
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>30-04-2026</v>
+        <v>30-04-2025</v>
       </c>
       <c r="D162" t="str">
         <v>SensexBullPE</v>
@@ -7998,7 +7998,7 @@
         <v>-2131</v>
       </c>
       <c r="K162">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L162" t="str">
         <v>Yes</v>
@@ -8021,7 +8021,7 @@
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>30-04-2026</v>
+        <v>30-04-2025</v>
       </c>
       <c r="D163" t="str">
         <v>NiftyBullPE</v>
@@ -8045,7 +8045,7 @@
         <v>-2269</v>
       </c>
       <c r="K163">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L163" t="str">
         <v>Yes</v>
@@ -8068,7 +8068,7 @@
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>30-04-2026</v>
+        <v>30-04-2025</v>
       </c>
       <c r="D164" t="str">
         <v>Sensex PE</v>
@@ -8092,7 +8092,7 @@
         <v>-3796</v>
       </c>
       <c r="K164">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L164" t="str">
         <v>Yes</v>
@@ -8115,7 +8115,7 @@
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>30-04-2026</v>
+        <v>30-04-2025</v>
       </c>
       <c r="D165" t="str">
         <v>Sensex PE</v>
@@ -8139,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="K165">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L165" t="str">
         <v>Yes</v>
@@ -8162,7 +8162,7 @@
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>30-04-2026</v>
+        <v>30-04-2025</v>
       </c>
       <c r="D166" t="str">
         <v>NiftyPE</v>
@@ -8186,7 +8186,7 @@
         <v>-1476</v>
       </c>
       <c r="K166">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L166" t="str">
         <v>Yes</v>
@@ -8209,7 +8209,7 @@
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>04-05-2026</v>
+        <v>04-05-2025</v>
       </c>
       <c r="D167" t="str">
         <v>SensexBullCE</v>
@@ -8233,7 +8233,7 @@
         <v>-2010</v>
       </c>
       <c r="K167">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L167" t="str">
         <v>Yes</v>
@@ -8256,7 +8256,7 @@
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>04-05-2026</v>
+        <v>04-05-2025</v>
       </c>
       <c r="D168" t="str">
         <v>NiftyBullCE</v>
@@ -8280,7 +8280,7 @@
         <v>-2720</v>
       </c>
       <c r="K168">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L168" t="str">
         <v>Yes</v>
@@ -8303,7 +8303,7 @@
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>04-05-2026</v>
+        <v>04-05-2025</v>
       </c>
       <c r="D169" t="str">
         <v>BankniftyPE</v>
@@ -8327,7 +8327,7 @@
         <v>0</v>
       </c>
       <c r="K169">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L169" t="str">
         <v>Yes</v>
@@ -8350,7 +8350,7 @@
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>04-05-2026</v>
+        <v>04-05-2025</v>
       </c>
       <c r="D170" t="str">
         <v>BankniftyCE</v>
@@ -8374,7 +8374,7 @@
         <v>-1023</v>
       </c>
       <c r="K170">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L170" t="str">
         <v>Yes</v>
@@ -8397,7 +8397,7 @@
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>05-05-2026</v>
+        <v>05-05-2025</v>
       </c>
       <c r="D171" t="str">
         <v>SensexBullPE</v>
@@ -8421,7 +8421,7 @@
         <v>-2072</v>
       </c>
       <c r="K171">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L171" t="str">
         <v>Yes</v>
@@ -8444,7 +8444,7 @@
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>05-05-2026</v>
+        <v>05-05-2025</v>
       </c>
       <c r="D172" t="str">
         <v>NiftyBullPE</v>
@@ -8468,7 +8468,7 @@
         <v>-2327</v>
       </c>
       <c r="K172">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L172" t="str">
         <v>Yes</v>
@@ -8491,7 +8491,7 @@
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>05-05-2026</v>
+        <v>05-05-2025</v>
       </c>
       <c r="D173" t="str">
         <v>Sensex PE</v>
@@ -8515,7 +8515,7 @@
         <v>-3826</v>
       </c>
       <c r="K173">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L173" t="str">
         <v>Yes</v>
@@ -8538,7 +8538,7 @@
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>05-05-2026</v>
+        <v>05-05-2025</v>
       </c>
       <c r="D174" t="str">
         <v>NiftyPE</v>
@@ -8562,7 +8562,7 @@
         <v>-4583</v>
       </c>
       <c r="K174">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L174" t="str">
         <v>Yes</v>
@@ -8585,7 +8585,7 @@
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>06-05-2026</v>
+        <v>06-05-2025</v>
       </c>
       <c r="D175" t="str">
         <v>SensexBullCE</v>
@@ -8609,7 +8609,7 @@
         <v>-2018</v>
       </c>
       <c r="K175">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L175" t="str">
         <v>Yes</v>
@@ -8632,7 +8632,7 @@
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>06-05-2026</v>
+        <v>06-05-2025</v>
       </c>
       <c r="D176" t="str">
         <v>SensexBullPE</v>
@@ -8656,7 +8656,7 @@
         <v>-2015</v>
       </c>
       <c r="K176">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L176" t="str">
         <v>Yes</v>
@@ -8679,7 +8679,7 @@
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>06-05-2026</v>
+        <v>06-05-2025</v>
       </c>
       <c r="D177" t="str">
         <v>NiftyBullCE</v>
@@ -8703,7 +8703,7 @@
         <v>-1053</v>
       </c>
       <c r="K177">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L177" t="str">
         <v>Yes</v>
@@ -8726,7 +8726,7 @@
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>06-05-2026</v>
+        <v>06-05-2025</v>
       </c>
       <c r="D178" t="str">
         <v>NiftyBullCE</v>
@@ -8750,7 +8750,7 @@
         <v>0</v>
       </c>
       <c r="K178">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L178" t="str">
         <v>Yes</v>
@@ -8773,7 +8773,7 @@
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>06-05-2026</v>
+        <v>06-05-2025</v>
       </c>
       <c r="D179" t="str">
         <v>BankniftyCE</v>
@@ -8797,7 +8797,7 @@
         <v>-2816</v>
       </c>
       <c r="K179">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L179" t="str">
         <v>Yes</v>
@@ -8820,7 +8820,7 @@
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>06-05-2026</v>
+        <v>06-05-2025</v>
       </c>
       <c r="D180" t="str">
         <v>NiftyCE</v>
@@ -8844,7 +8844,7 @@
         <v>-2074</v>
       </c>
       <c r="K180">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L180" t="str">
         <v>Yes</v>
@@ -8867,7 +8867,7 @@
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>06-05-2026</v>
+        <v>06-05-2025</v>
       </c>
       <c r="D181" t="str">
         <v>NiftyCE</v>
@@ -8891,7 +8891,7 @@
         <v>0</v>
       </c>
       <c r="K181">
-        <v>-71</v>
+        <v>71</v>
       </c>
       <c r="L181" t="str">
         <v>Yes</v>
@@ -8914,7 +8914,7 @@
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>08-05-2026</v>
+        <v>08-05-2025</v>
       </c>
       <c r="D182" t="str">
         <v>SensexBullPE</v>
@@ -8938,7 +8938,7 @@
         <v>0</v>
       </c>
       <c r="K182">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L182" t="str">
         <v>Yes</v>
@@ -8961,7 +8961,7 @@
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>08-05-2026</v>
+        <v>08-05-2025</v>
       </c>
       <c r="D183" t="str">
         <v>NiftyBullPE</v>
@@ -8985,7 +8985,7 @@
         <v>0</v>
       </c>
       <c r="K183">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L183" t="str">
         <v>Yes</v>
@@ -9008,7 +9008,7 @@
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>08-05-2026</v>
+        <v>08-05-2025</v>
       </c>
       <c r="D184" t="str">
         <v>BankniftyPE</v>
@@ -9032,7 +9032,7 @@
         <v>0</v>
       </c>
       <c r="K184">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L184" t="str">
         <v>Yes</v>
@@ -9055,7 +9055,7 @@
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>08-05-2026</v>
+        <v>08-05-2025</v>
       </c>
       <c r="D185" t="str">
         <v>Sensex PE</v>
@@ -9079,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="K185">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L185" t="str">
         <v>Yes</v>
@@ -9102,7 +9102,7 @@
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>08-05-2026</v>
+        <v>08-05-2025</v>
       </c>
       <c r="D186" t="str">
         <v>NiftyPE</v>
@@ -9126,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="K186">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L186" t="str">
         <v>Yes</v>
@@ -9149,7 +9149,7 @@
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>11-05-2026</v>
+        <v>11-05-2025</v>
       </c>
       <c r="D187" t="str">
         <v>NiftyBullPE</v>
@@ -9173,7 +9173,7 @@
         <v>-2275</v>
       </c>
       <c r="K187">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L187" t="str">
         <v>Yes</v>
@@ -9196,7 +9196,7 @@
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>11-05-2026</v>
+        <v>11-05-2025</v>
       </c>
       <c r="D188" t="str">
         <v>BankniftyPE</v>
@@ -9220,7 +9220,7 @@
         <v>-4175</v>
       </c>
       <c r="K188">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L188" t="str">
         <v>Yes</v>
@@ -9243,7 +9243,7 @@
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>11-05-2026</v>
+        <v>11-05-2025</v>
       </c>
       <c r="D189" t="str">
         <v>Sensex PE</v>
@@ -9267,7 +9267,7 @@
         <v>0</v>
       </c>
       <c r="K189">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L189" t="str">
         <v>Yes</v>
@@ -9290,7 +9290,7 @@
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>11-05-2026</v>
+        <v>11-05-2025</v>
       </c>
       <c r="D190" t="str">
         <v>NiftyPE</v>
@@ -9314,7 +9314,7 @@
         <v>0</v>
       </c>
       <c r="K190">
-        <v>-102</v>
+        <v>102</v>
       </c>
       <c r="L190" t="str">
         <v>Yes</v>
@@ -9337,7 +9337,7 @@
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>12-05-2026</v>
+        <v>12-05-2025</v>
       </c>
       <c r="D191" t="str">
         <v>SensexBullPE</v>
@@ -9361,7 +9361,7 @@
         <v>0</v>
       </c>
       <c r="K191">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L191" t="str">
         <v>Yes</v>
@@ -9384,7 +9384,7 @@
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>12-05-2026</v>
+        <v>12-05-2025</v>
       </c>
       <c r="D192" t="str">
         <v>NiftyBullPE</v>
@@ -9408,7 +9408,7 @@
         <v>0</v>
       </c>
       <c r="K192">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L192" t="str">
         <v>Yes</v>
@@ -9431,7 +9431,7 @@
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>12-05-2026</v>
+        <v>12-05-2025</v>
       </c>
       <c r="D193" t="str">
         <v>NiftyPE</v>
@@ -9455,7 +9455,7 @@
         <v>0</v>
       </c>
       <c r="K193">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L193" t="str">
         <v>Yes</v>
@@ -9478,7 +9478,7 @@
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>13-05-2026</v>
+        <v>13-05-2025</v>
       </c>
       <c r="D194" t="str">
         <v>SensexBullPE</v>
@@ -9502,7 +9502,7 @@
         <v>-2075</v>
       </c>
       <c r="K194">
-        <v>-85</v>
+        <v>85</v>
       </c>
       <c r="L194" t="str">
         <v>Yes</v>
@@ -9525,7 +9525,7 @@
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>13-05-2026</v>
+        <v>13-05-2025</v>
       </c>
       <c r="D195" t="str">
         <v>NiftyBullPE</v>
@@ -9549,7 +9549,7 @@
         <v>-2106</v>
       </c>
       <c r="K195">
-        <v>-85</v>
+        <v>85</v>
       </c>
       <c r="L195" t="str">
         <v>Yes</v>
@@ -9572,7 +9572,7 @@
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>13-05-2026</v>
+        <v>13-05-2025</v>
       </c>
       <c r="D196" t="str">
         <v>BankniftyPE</v>
@@ -9596,7 +9596,7 @@
         <v>-4047</v>
       </c>
       <c r="K196">
-        <v>-86</v>
+        <v>86</v>
       </c>
       <c r="L196" t="str">
         <v>Yes</v>
@@ -9619,7 +9619,7 @@
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>14-05-2026</v>
+        <v>14-05-2025</v>
       </c>
       <c r="D197" t="str">
         <v>SensexBullCE</v>
@@ -9643,7 +9643,7 @@
         <v>0</v>
       </c>
       <c r="K197">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="L197" t="str">
         <v>Yes</v>
@@ -9666,7 +9666,7 @@
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>14-05-2026</v>
+        <v>14-05-2025</v>
       </c>
       <c r="D198" t="str">
         <v>NiftyBullCE</v>
@@ -9690,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="K198">
-        <v>-102</v>
+        <v>102</v>
       </c>
       <c r="L198" t="str">
         <v>Yes</v>
@@ -9713,7 +9713,7 @@
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>14-05-2026</v>
+        <v>14-05-2025</v>
       </c>
       <c r="D199" t="str">
         <v>BankniftyCE</v>
@@ -9737,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="K199">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="L199" t="str">
         <v>Yes</v>
@@ -9760,7 +9760,7 @@
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>14-05-2026</v>
+        <v>14-05-2025</v>
       </c>
       <c r="D200" t="str">
         <v>Sensex CE</v>
@@ -9784,7 +9784,7 @@
         <v>0</v>
       </c>
       <c r="K200">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="L200" t="str">
         <v>Yes</v>
@@ -9807,7 +9807,7 @@
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>14-05-2026</v>
+        <v>14-05-2025</v>
       </c>
       <c r="D201" t="str">
         <v>NiftyCE</v>
@@ -9831,7 +9831,7 @@
         <v>0</v>
       </c>
       <c r="K201">
-        <v>-104</v>
+        <v>104</v>
       </c>
       <c r="L201" t="str">
         <v>Yes</v>
@@ -9854,7 +9854,7 @@
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>18-05-2026</v>
+        <v>18-05-2025</v>
       </c>
       <c r="D202" t="str">
         <v>SensexBullPE</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="K202">
-        <v>-98</v>
+        <v>98</v>
       </c>
       <c r="L202" t="str">
         <v>Yes</v>
@@ -9901,7 +9901,7 @@
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>18-05-2026</v>
+        <v>18-05-2025</v>
       </c>
       <c r="D203" t="str">
         <v>NiftyBullPE</v>
@@ -9925,7 +9925,7 @@
         <v>0</v>
       </c>
       <c r="K203">
-        <v>-98</v>
+        <v>98</v>
       </c>
       <c r="L203" t="str">
         <v>Yes</v>
@@ -9948,7 +9948,7 @@
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>18-05-2026</v>
+        <v>18-05-2025</v>
       </c>
       <c r="D204" t="str">
         <v>Sensex PE</v>
@@ -9972,7 +9972,7 @@
         <v>0</v>
       </c>
       <c r="K204">
-        <v>-98</v>
+        <v>98</v>
       </c>
       <c r="L204" t="str">
         <v>Yes</v>
@@ -9995,7 +9995,7 @@
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>18-05-2026</v>
+        <v>18-05-2025</v>
       </c>
       <c r="D205" t="str">
         <v>NiftyPE</v>
@@ -10019,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="K205">
-        <v>-98</v>
+        <v>98</v>
       </c>
       <c r="L205" t="str">
         <v>Yes</v>
@@ -10042,7 +10042,7 @@
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>20-05-2026</v>
+        <v>20-05-2025</v>
       </c>
       <c r="D206" t="str">
         <v>SensexBullPE</v>
@@ -10066,7 +10066,7 @@
         <v>-2000</v>
       </c>
       <c r="K206">
-        <v>-92</v>
+        <v>92</v>
       </c>
       <c r="L206" t="str">
         <v>Yes</v>
@@ -10089,7 +10089,7 @@
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>20-05-2026</v>
+        <v>20-05-2025</v>
       </c>
       <c r="D207" t="str">
         <v>NiftyBullPE</v>
@@ -10113,7 +10113,7 @@
         <v>-1466</v>
       </c>
       <c r="K207">
-        <v>-92</v>
+        <v>92</v>
       </c>
       <c r="L207" t="str">
         <v>Yes</v>
@@ -10136,7 +10136,7 @@
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>20-05-2026</v>
+        <v>20-05-2025</v>
       </c>
       <c r="D208" t="str">
         <v>BankniftyPE</v>
@@ -10160,7 +10160,7 @@
         <v>-3597</v>
       </c>
       <c r="K208">
-        <v>-92</v>
+        <v>92</v>
       </c>
       <c r="L208" t="str">
         <v>Yes</v>
@@ -10183,7 +10183,7 @@
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>20-05-2026</v>
+        <v>20-05-2025</v>
       </c>
       <c r="D209" t="str">
         <v>NiftyPE</v>
@@ -10207,7 +10207,7 @@
         <v>-2496</v>
       </c>
       <c r="K209">
-        <v>-94</v>
+        <v>94</v>
       </c>
       <c r="L209" t="str">
         <v>Yes</v>
@@ -10230,7 +10230,7 @@
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>21-05-2026</v>
+        <v>21-05-2025</v>
       </c>
       <c r="D210" t="str">
         <v>NiftyBullPE</v>
@@ -10254,7 +10254,7 @@
         <v>-2291</v>
       </c>
       <c r="K210">
-        <v>-80</v>
+        <v>80</v>
       </c>
       <c r="L210" t="str">
         <v>Yes</v>
@@ -10277,7 +10277,7 @@
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>22-05-2026</v>
+        <v>22-05-2025</v>
       </c>
       <c r="D211" t="str">
         <v>Sensex CE</v>
@@ -10301,7 +10301,7 @@
         <v>-2648</v>
       </c>
       <c r="K211">
-        <v>-98</v>
+        <v>98</v>
       </c>
       <c r="L211" t="str">
         <v>Yes</v>
@@ -10324,7 +10324,7 @@
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>22-05-2026</v>
+        <v>22-05-2025</v>
       </c>
       <c r="D212" t="str">
         <v>BankniftyCE</v>
@@ -10348,7 +10348,7 @@
         <v>-2769</v>
       </c>
       <c r="K212">
-        <v>-98</v>
+        <v>98</v>
       </c>
       <c r="L212" t="str">
         <v>Yes</v>
@@ -10371,7 +10371,7 @@
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>25-05-2026</v>
+        <v>25-05-2025</v>
       </c>
       <c r="D213" t="str">
         <v>NiftyCE</v>
@@ -10395,7 +10395,7 @@
         <v>-3760</v>
       </c>
       <c r="K213">
-        <v>-160</v>
+        <v>160</v>
       </c>
       <c r="L213" t="str">
         <v>Yes</v>
@@ -10418,7 +10418,7 @@
         <v/>
       </c>
       <c r="C214" t="str">
-        <v>25-05-2026</v>
+        <v>25-05-2025</v>
       </c>
       <c r="D214" t="str">
         <v>Sensex CE</v>
@@ -10442,7 +10442,7 @@
         <v>-2578</v>
       </c>
       <c r="K214">
-        <v>-155</v>
+        <v>155</v>
       </c>
       <c r="L214" t="str">
         <v>Yes</v>
@@ -10465,7 +10465,7 @@
         <v/>
       </c>
       <c r="C215" t="str">
-        <v>25-05-2026</v>
+        <v>25-05-2025</v>
       </c>
       <c r="D215" t="str">
         <v>Sensex CE</v>
@@ -10489,7 +10489,7 @@
         <v>-3473</v>
       </c>
       <c r="K215">
-        <v>-154</v>
+        <v>154</v>
       </c>
       <c r="L215" t="str">
         <v>Yes</v>
@@ -10512,7 +10512,7 @@
         <v/>
       </c>
       <c r="C216" t="str">
-        <v>25-05-2026</v>
+        <v>25-05-2025</v>
       </c>
       <c r="D216" t="str">
         <v>BankniftyCE</v>
@@ -10536,7 +10536,7 @@
         <v>-4649</v>
       </c>
       <c r="K216">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="L216" t="str">
         <v>Yes</v>
@@ -10559,7 +10559,7 @@
         <v/>
       </c>
       <c r="C217" t="str">
-        <v>25-05-2026</v>
+        <v>25-05-2025</v>
       </c>
       <c r="D217" t="str">
         <v>BankniftyCE</v>
@@ -10583,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="K217">
-        <v>-150</v>
+        <v>150</v>
       </c>
       <c r="L217" t="str">
         <v>Yes</v>
@@ -10606,7 +10606,7 @@
         <v/>
       </c>
       <c r="C218" t="str">
-        <v>26-05-2026</v>
+        <v>26-05-2025</v>
       </c>
       <c r="D218" t="str">
         <v>Sensex PE</v>
@@ -10630,7 +10630,7 @@
         <v>-5685</v>
       </c>
       <c r="K218">
-        <v>-146</v>
+        <v>146</v>
       </c>
       <c r="L218" t="str">
         <v>Yes</v>
@@ -10653,7 +10653,7 @@
         <v/>
       </c>
       <c r="C219" t="str">
-        <v>26-05-2026</v>
+        <v>26-05-2025</v>
       </c>
       <c r="D219" t="str">
         <v>NiftyPE</v>
@@ -10677,7 +10677,7 @@
         <v>0</v>
       </c>
       <c r="K219">
-        <v>-146</v>
+        <v>146</v>
       </c>
       <c r="L219" t="str">
         <v>Yes</v>
@@ -10700,7 +10700,7 @@
         <v/>
       </c>
       <c r="C220" t="str">
-        <v>29-05-2026</v>
+        <v>29-05-2025</v>
       </c>
       <c r="D220" t="str">
         <v>Sensex PE</v>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="K220">
-        <v>-61</v>
+        <v>61</v>
       </c>
       <c r="L220" t="str">
         <v>Yes</v>
@@ -10739,56 +10739,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" t="str">
-        <v/>
-      </c>
-      <c r="B221" t="str">
-        <v/>
-      </c>
-      <c r="C221" t="str">
-        <v>01-06-2026</v>
-      </c>
-      <c r="D221" t="str">
-        <v>BankniftyPE</v>
-      </c>
-      <c r="E221">
-        <v>120</v>
-      </c>
-      <c r="F221">
-        <v>522.8</v>
-      </c>
-      <c r="G221">
-        <v>496.85</v>
-      </c>
-      <c r="H221">
-        <v>-25.949999999999932</v>
-      </c>
-      <c r="I221">
-        <v>0</v>
-      </c>
-      <c r="J221">
-        <v>3243.999999999992</v>
-      </c>
-      <c r="K221">
-        <v>130</v>
-      </c>
-      <c r="L221" t="str">
-        <v>YES</v>
-      </c>
-      <c r="M221" t="str">
-        <v/>
-      </c>
-      <c r="N221">
-        <v>-3243.999999999992</v>
-      </c>
-      <c r="O221">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O221"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O220"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/server/trades.xlsx
+++ b/server/trades.xlsx
@@ -32,8 +32,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="D/M/YYYY"/>
+    <numFmt numFmtId="165" formatCode="[$-13809]d\ mmm\ yyyy"/>
+    <numFmt numFmtId="166" formatCode="[$-409]d\-mmm"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -454,7 +458,7 @@
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>14-10-2024</v>
+        <v>14-10-2025</v>
       </c>
       <c r="D2" t="str">
         <v>BankniftyPE</v>
@@ -463,22 +467,22 @@
         <v>35</v>
       </c>
       <c r="F2">
-        <v>413</v>
+        <v>412.65</v>
       </c>
       <c r="G2">
-        <v>449</v>
+        <v>448.8</v>
       </c>
       <c r="H2">
-        <v>36</v>
+        <v>36.15</v>
       </c>
       <c r="I2">
-        <v>1265</v>
+        <v>1265.25</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2">
-        <v>27</v>
+        <v>26.85</v>
       </c>
       <c r="L2" t="str">
         <v>Yes</v>
@@ -487,7 +491,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N2">
-        <v>1238</v>
+        <v>1238.4</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -501,7 +505,7 @@
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>15-10-2024</v>
+        <v>15-10-2025</v>
       </c>
       <c r="D3" t="str">
         <v>NiftyCE</v>
@@ -510,19 +514,19 @@
         <v>75</v>
       </c>
       <c r="F3">
-        <v>193</v>
+        <v>192.55</v>
       </c>
       <c r="G3">
-        <v>163</v>
+        <v>162.5</v>
       </c>
       <c r="H3">
-        <v>-30</v>
+        <v>-30.05</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>-2254</v>
+        <v>-2253.75</v>
       </c>
       <c r="K3">
         <v>27</v>
@@ -534,7 +538,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N3">
-        <v>-2281</v>
+        <v>-2280.75</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -548,7 +552,7 @@
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>15-10-2024</v>
+        <v>15-10-2025</v>
       </c>
       <c r="D4" t="str">
         <v>NiftyCE</v>
@@ -557,16 +561,16 @@
         <v>75</v>
       </c>
       <c r="F4">
-        <v>202</v>
+        <v>201.55</v>
       </c>
       <c r="G4">
-        <v>228</v>
+        <v>228.3</v>
       </c>
       <c r="H4">
-        <v>27</v>
+        <v>26.75</v>
       </c>
       <c r="I4">
-        <v>2006</v>
+        <v>2006.25</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -581,7 +585,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N4">
-        <v>1979</v>
+        <v>1979.25</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -595,7 +599,7 @@
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>15-10-2024</v>
+        <v>15-10-2025</v>
       </c>
       <c r="D5" t="str">
         <v>BankniftyCE</v>
@@ -604,16 +608,16 @@
         <v>35</v>
       </c>
       <c r="F5">
-        <v>394</v>
+        <v>393.5</v>
       </c>
       <c r="G5">
-        <v>426</v>
+        <v>426.35</v>
       </c>
       <c r="H5">
-        <v>33</v>
+        <v>32.85</v>
       </c>
       <c r="I5">
-        <v>1150</v>
+        <v>1149.75</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -628,7 +632,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N5">
-        <v>1123</v>
+        <v>1122.75</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -642,7 +646,7 @@
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>17-10-2024</v>
+        <v>17-10-2025</v>
       </c>
       <c r="D6" t="str">
         <v>Sensex CE</v>
@@ -651,13 +655,13 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <v>528</v>
+        <v>527.85</v>
       </c>
       <c r="G6">
-        <v>603</v>
+        <v>603.4</v>
       </c>
       <c r="H6">
-        <v>76</v>
+        <v>75.55</v>
       </c>
       <c r="I6">
         <v>1511</v>
@@ -689,7 +693,7 @@
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>17-10-2024</v>
+        <v>17-10-2025</v>
       </c>
       <c r="D7" t="str">
         <v>BankniftyCE</v>
@@ -698,16 +702,16 @@
         <v>35</v>
       </c>
       <c r="F7">
-        <v>418</v>
+        <v>418.3</v>
       </c>
       <c r="G7">
-        <v>443</v>
+        <v>442.8</v>
       </c>
       <c r="H7">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="I7">
-        <v>858</v>
+        <v>857.5</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -722,7 +726,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N7">
-        <v>830</v>
+        <v>829.5</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -736,7 +740,7 @@
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>17-10-2024</v>
+        <v>17-10-2025</v>
       </c>
       <c r="D8" t="str">
         <v>NiftyCE</v>
@@ -745,16 +749,16 @@
         <v>75</v>
       </c>
       <c r="F8">
-        <v>185</v>
+        <v>185.4</v>
       </c>
       <c r="G8">
-        <v>195</v>
+        <v>194.55</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>9.15</v>
       </c>
       <c r="I8">
-        <v>686</v>
+        <v>686.25</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -769,7 +773,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N8">
-        <v>658</v>
+        <v>658.25</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -783,7 +787,7 @@
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>17-10-2024</v>
+        <v>17-10-2025</v>
       </c>
       <c r="D9" t="str">
         <v>BankniftyPE</v>
@@ -792,16 +796,16 @@
         <v>35</v>
       </c>
       <c r="F9">
-        <v>423</v>
+        <v>423.2</v>
       </c>
       <c r="G9">
-        <v>474</v>
+        <v>473.65</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>50.45</v>
       </c>
       <c r="I9">
-        <v>1766</v>
+        <v>1765.75</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -816,7 +820,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N9">
-        <v>1738</v>
+        <v>1737.75</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -830,7 +834,7 @@
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>20-10-2024</v>
+        <v>20-10-2025</v>
       </c>
       <c r="D10" t="str">
         <v>BankniftyCE</v>
@@ -839,13 +843,13 @@
         <v>35</v>
       </c>
       <c r="F10">
-        <v>387</v>
+        <v>386.55</v>
       </c>
       <c r="G10">
-        <v>358</v>
+        <v>358.15</v>
       </c>
       <c r="H10">
-        <v>-28</v>
+        <v>-28.4</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -877,7 +881,7 @@
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>23-10-2024</v>
+        <v>23-10-2025</v>
       </c>
       <c r="D11" t="str">
         <v>Sensex PE</v>
@@ -886,13 +890,13 @@
         <v>20</v>
       </c>
       <c r="F11">
-        <v>507</v>
+        <v>507.4</v>
       </c>
       <c r="G11">
-        <v>585</v>
+        <v>585.1</v>
       </c>
       <c r="H11">
-        <v>78</v>
+        <v>77.7</v>
       </c>
       <c r="I11">
         <v>1554</v>
@@ -924,7 +928,7 @@
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>23-10-2024</v>
+        <v>23-10-2025</v>
       </c>
       <c r="D12" t="str">
         <v>Sensex PE</v>
@@ -933,13 +937,13 @@
         <v>20</v>
       </c>
       <c r="F12">
-        <v>535</v>
+        <v>534.6</v>
       </c>
       <c r="G12">
-        <v>537</v>
+        <v>536.75</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="I12">
         <v>43</v>
@@ -971,7 +975,7 @@
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>23-10-2024</v>
+        <v>23-10-2025</v>
       </c>
       <c r="D13" t="str">
         <v>NiftyCE</v>
@@ -980,16 +984,16 @@
         <v>75</v>
       </c>
       <c r="F13">
-        <v>186</v>
+        <v>185.6</v>
       </c>
       <c r="G13">
-        <v>227</v>
+        <v>226.95</v>
       </c>
       <c r="H13">
-        <v>41</v>
+        <v>41.35</v>
       </c>
       <c r="I13">
-        <v>3101</v>
+        <v>3101.25</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1004,7 +1008,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N13">
-        <v>3073</v>
+        <v>3073.25</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1018,7 +1022,7 @@
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>24-10-2024</v>
+        <v>24-10-2025</v>
       </c>
       <c r="D14" t="str">
         <v>BankniftyPE</v>
@@ -1027,16 +1031,16 @@
         <v>35</v>
       </c>
       <c r="F14">
-        <v>380</v>
+        <v>379.9</v>
       </c>
       <c r="G14">
-        <v>438</v>
+        <v>438.15</v>
       </c>
       <c r="H14">
-        <v>58</v>
+        <v>58.25</v>
       </c>
       <c r="I14">
-        <v>2039</v>
+        <v>2038.75</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1051,7 +1055,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N14">
-        <v>2011</v>
+        <v>2010.75</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1065,7 +1069,7 @@
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>27-10-2024</v>
+        <v>27-10-2025</v>
       </c>
       <c r="D15" t="str">
         <v>BankniftyCE</v>
@@ -1074,13 +1078,13 @@
         <v>35</v>
       </c>
       <c r="F15">
-        <v>405</v>
+        <v>404.5</v>
       </c>
       <c r="G15">
-        <v>344</v>
+        <v>344.3</v>
       </c>
       <c r="H15">
-        <v>-60</v>
+        <v>-60.2</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -1112,7 +1116,7 @@
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>27-10-2024</v>
+        <v>27-10-2025</v>
       </c>
       <c r="D16" t="str">
         <v>Sensex CE</v>
@@ -1121,13 +1125,13 @@
         <v>20</v>
       </c>
       <c r="F16">
-        <v>480</v>
+        <v>479.85</v>
       </c>
       <c r="G16">
-        <v>405</v>
+        <v>404.8</v>
       </c>
       <c r="H16">
-        <v>-75</v>
+        <v>-75.05</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -1159,7 +1163,7 @@
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>29-10-2024</v>
+        <v>29-10-2025</v>
       </c>
       <c r="D17" t="str">
         <v>NiftyCE</v>
@@ -1168,19 +1172,19 @@
         <v>75</v>
       </c>
       <c r="F17">
-        <v>209</v>
+        <v>209.25</v>
       </c>
       <c r="G17">
-        <v>185</v>
+        <v>184.6</v>
       </c>
       <c r="H17">
-        <v>-25</v>
+        <v>-24.65</v>
       </c>
       <c r="I17">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>-1849</v>
+        <v>-1848.75</v>
       </c>
       <c r="K17">
         <v>28</v>
@@ -1192,7 +1196,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N17">
-        <v>-1877</v>
+        <v>-1876.75</v>
       </c>
       <c r="O17">
         <v>0</v>
@@ -1206,7 +1210,7 @@
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>29-10-2024</v>
+        <v>29-10-2025</v>
       </c>
       <c r="D18" t="str">
         <v>BankniftyCE</v>
@@ -1215,13 +1219,13 @@
         <v>35</v>
       </c>
       <c r="F18">
-        <v>414</v>
+        <v>414.15</v>
       </c>
       <c r="G18">
-        <v>394</v>
+        <v>394.35</v>
       </c>
       <c r="H18">
-        <v>-20</v>
+        <v>-19.8</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1253,7 +1257,7 @@
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>30-10-2024</v>
+        <v>30-10-2025</v>
       </c>
       <c r="D19" t="str">
         <v>Sensex PE</v>
@@ -1262,13 +1266,13 @@
         <v>20</v>
       </c>
       <c r="F19">
-        <v>474</v>
+        <v>474.25</v>
       </c>
       <c r="G19">
-        <v>575</v>
+        <v>575.05</v>
       </c>
       <c r="H19">
-        <v>101</v>
+        <v>100.8</v>
       </c>
       <c r="I19">
         <v>2016</v>
@@ -1300,7 +1304,7 @@
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>04-11-2024</v>
+        <v>04-11-2025</v>
       </c>
       <c r="D20" t="str">
         <v>NiftyPE</v>
@@ -1312,19 +1316,19 @@
         <v>187</v>
       </c>
       <c r="G20">
-        <v>218</v>
+        <v>217.75</v>
       </c>
       <c r="H20">
-        <v>31</v>
+        <v>30.75</v>
       </c>
       <c r="I20">
-        <v>4613</v>
+        <v>4612.5</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>54</v>
+        <v>54.05</v>
       </c>
       <c r="L20" t="str">
         <v>Yes</v>
@@ -1333,7 +1337,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N20">
-        <v>4558</v>
+        <v>4558.45</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -1347,7 +1351,7 @@
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>06-11-2024</v>
+        <v>06-11-2025</v>
       </c>
       <c r="D21" t="str">
         <v>BankniftyPE</v>
@@ -1356,13 +1360,13 @@
         <v>35</v>
       </c>
       <c r="F21">
-        <v>391</v>
+        <v>390.7</v>
       </c>
       <c r="G21">
         <v>350</v>
       </c>
       <c r="H21">
-        <v>-41</v>
+        <v>-40.69999999999999</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -1394,7 +1398,7 @@
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>07-11-2024</v>
+        <v>07-11-2025</v>
       </c>
       <c r="D22" t="str">
         <v>NiftyPE</v>
@@ -1403,19 +1407,19 @@
         <v>75</v>
       </c>
       <c r="F22">
-        <v>185</v>
+        <v>184.8</v>
       </c>
       <c r="G22">
-        <v>159</v>
+        <v>158.75</v>
       </c>
       <c r="H22">
-        <v>-26</v>
+        <v>-26.05000000000001</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>-3908</v>
+        <v>-3907.5</v>
       </c>
       <c r="K22">
         <v>54</v>
@@ -1427,7 +1431,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N22">
-        <v>-3962</v>
+        <v>-3961.5</v>
       </c>
       <c r="O22">
         <v>0</v>
@@ -1441,7 +1445,7 @@
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>07-11-2024</v>
+        <v>07-11-2025</v>
       </c>
       <c r="D23" t="str">
         <v>Sensex PE</v>
@@ -1450,13 +1454,13 @@
         <v>20</v>
       </c>
       <c r="F23">
-        <v>479</v>
+        <v>478.95</v>
       </c>
       <c r="G23">
-        <v>383</v>
+        <v>383.1</v>
       </c>
       <c r="H23">
-        <v>-96</v>
+        <v>-95.84999999999997</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -1488,7 +1492,7 @@
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>07-11-2024</v>
+        <v>07-11-2025</v>
       </c>
       <c r="D24" t="str">
         <v>BankniftyCE</v>
@@ -1497,19 +1501,19 @@
         <v>35</v>
       </c>
       <c r="F24">
-        <v>402</v>
+        <v>402.37</v>
       </c>
       <c r="G24">
-        <v>377</v>
+        <v>377.35</v>
       </c>
       <c r="H24">
-        <v>-25</v>
+        <v>-25.019999999999982</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>-1751</v>
+        <v>-1751.4</v>
       </c>
       <c r="K24">
         <v>54</v>
@@ -1521,7 +1525,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N24">
-        <v>-1805</v>
+        <v>-1805.4</v>
       </c>
       <c r="O24">
         <v>0</v>
@@ -1535,7 +1539,7 @@
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>10-11-2024</v>
+        <v>10-11-2025</v>
       </c>
       <c r="D25" t="str">
         <v>NiftyCE</v>
@@ -1544,19 +1548,19 @@
         <v>75</v>
       </c>
       <c r="F25">
-        <v>180</v>
+        <v>180.4</v>
       </c>
       <c r="G25">
-        <v>155</v>
+        <v>155.15</v>
       </c>
       <c r="H25">
-        <v>-25</v>
+        <v>-25.25</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>-3788</v>
+        <v>-3787.5</v>
       </c>
       <c r="K25">
         <v>54</v>
@@ -1568,7 +1572,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N25">
-        <v>-3842</v>
+        <v>-3841.5</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -1582,7 +1586,7 @@
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>11-11-2024</v>
+        <v>11-11-2025</v>
       </c>
       <c r="D26" t="str">
         <v>Sensex PE</v>
@@ -1591,16 +1595,16 @@
         <v>20</v>
       </c>
       <c r="F26">
-        <v>498</v>
+        <v>498.25</v>
       </c>
       <c r="G26">
-        <v>597</v>
+        <v>597.02</v>
       </c>
       <c r="H26">
-        <v>99</v>
+        <v>98.76999999999998</v>
       </c>
       <c r="I26">
-        <v>3951</v>
+        <v>3950.8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1615,7 +1619,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N26">
-        <v>3911</v>
+        <v>3910.8</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -1629,7 +1633,7 @@
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>12-11-2024</v>
+        <v>12-11-2025</v>
       </c>
       <c r="D27" t="str">
         <v>NiftyCE</v>
@@ -1638,13 +1642,13 @@
         <v>75</v>
       </c>
       <c r="F27">
-        <v>196</v>
+        <v>195.8</v>
       </c>
       <c r="G27">
-        <v>176</v>
+        <v>176.2</v>
       </c>
       <c r="H27">
-        <v>-20</v>
+        <v>-19.600000000000023</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -1676,7 +1680,7 @@
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>12-11-2024</v>
+        <v>12-11-2025</v>
       </c>
       <c r="D28" t="str">
         <v>NiftyCE</v>
@@ -1685,19 +1689,19 @@
         <v>75</v>
       </c>
       <c r="F28">
-        <v>210</v>
+        <v>209.6</v>
       </c>
       <c r="G28">
-        <v>187</v>
+        <v>187.05</v>
       </c>
       <c r="H28">
-        <v>-23</v>
+        <v>-22.549999999999983</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>-3383</v>
+        <v>-3382.5</v>
       </c>
       <c r="K28">
         <v>54</v>
@@ -1709,7 +1713,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N28">
-        <v>-3437</v>
+        <v>-3436.5</v>
       </c>
       <c r="O28">
         <v>0</v>
@@ -1723,7 +1727,7 @@
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>13-11-2024</v>
+        <v>13-11-2025</v>
       </c>
       <c r="D29" t="str">
         <v>NiftyCE</v>
@@ -1732,10 +1736,10 @@
         <v>75</v>
       </c>
       <c r="F29">
-        <v>206</v>
+        <v>206.45</v>
       </c>
       <c r="G29">
-        <v>240</v>
+        <v>240.45</v>
       </c>
       <c r="H29">
         <v>34</v>
@@ -1770,7 +1774,7 @@
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>14-11-2024</v>
+        <v>14-11-2025</v>
       </c>
       <c r="D30" t="str">
         <v>Sensex PE</v>
@@ -1779,13 +1783,13 @@
         <v>20</v>
       </c>
       <c r="F30">
-        <v>518</v>
+        <v>517.9</v>
       </c>
       <c r="G30">
-        <v>414</v>
+        <v>414.3</v>
       </c>
       <c r="H30">
-        <v>-104</v>
+        <v>-103.59999999999997</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1794,7 +1798,7 @@
         <v>-4144</v>
       </c>
       <c r="K30">
-        <v>40</v>
+        <v>40.09</v>
       </c>
       <c r="L30" t="str">
         <v>Yes</v>
@@ -1803,7 +1807,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N30">
-        <v>-4184</v>
+        <v>-4184.09</v>
       </c>
       <c r="O30">
         <v>0</v>
@@ -1817,7 +1821,7 @@
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>17-11-2024</v>
+        <v>17-11-2025</v>
       </c>
       <c r="D31" t="str">
         <v>BankniftyCE</v>
@@ -1826,16 +1830,16 @@
         <v>35</v>
       </c>
       <c r="F31">
-        <v>410</v>
+        <v>410.4</v>
       </c>
       <c r="G31">
-        <v>439</v>
+        <v>439.05</v>
       </c>
       <c r="H31">
-        <v>29</v>
+        <v>28.650000000000034</v>
       </c>
       <c r="I31">
-        <v>2006</v>
+        <v>2005.5</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -1850,7 +1854,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N31">
-        <v>1952</v>
+        <v>1951.5</v>
       </c>
       <c r="O31">
         <v>0</v>
@@ -1864,7 +1868,7 @@
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>19-11-2024</v>
+        <v>19-11-2025</v>
       </c>
       <c r="D32" t="str">
         <v>BankniftyCE</v>
@@ -1876,16 +1880,16 @@
         <v>420</v>
       </c>
       <c r="G32">
-        <v>409</v>
+        <v>409.45</v>
       </c>
       <c r="H32">
-        <v>-11</v>
+        <v>-10.550000000000011</v>
       </c>
       <c r="I32">
         <v>0</v>
       </c>
       <c r="J32">
-        <v>-739</v>
+        <v>-738.5</v>
       </c>
       <c r="K32">
         <v>54</v>
@@ -1897,7 +1901,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N32">
-        <v>-793</v>
+        <v>-792.5</v>
       </c>
       <c r="O32">
         <v>0</v>
@@ -1911,7 +1915,7 @@
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>20-11-2024</v>
+        <v>20-11-2025</v>
       </c>
       <c r="D33" t="str">
         <v>Sensex CE</v>
@@ -1920,13 +1924,13 @@
         <v>20</v>
       </c>
       <c r="F33">
-        <v>499</v>
+        <v>499.1</v>
       </c>
       <c r="G33">
-        <v>424</v>
+        <v>424.05</v>
       </c>
       <c r="H33">
-        <v>-75</v>
+        <v>-75.05000000000001</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -1935,7 +1939,7 @@
         <v>-3002</v>
       </c>
       <c r="K33">
-        <v>40</v>
+        <v>40.46</v>
       </c>
       <c r="L33" t="str">
         <v>Yes</v>
@@ -1944,7 +1948,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N33">
-        <v>-3042</v>
+        <v>-3042.46</v>
       </c>
       <c r="O33">
         <v>0</v>
@@ -1958,7 +1962,7 @@
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>21-11-2024</v>
+        <v>21-11-2025</v>
       </c>
       <c r="D34" t="str">
         <v>BankniftyPE</v>
@@ -1967,16 +1971,16 @@
         <v>35</v>
       </c>
       <c r="F34">
-        <v>479</v>
+        <v>478.67</v>
       </c>
       <c r="G34">
-        <v>518</v>
+        <v>518.05</v>
       </c>
       <c r="H34">
-        <v>39</v>
+        <v>39.37999999999994</v>
       </c>
       <c r="I34">
-        <v>2757</v>
+        <v>2756.6</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -1991,7 +1995,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N34">
-        <v>2703</v>
+        <v>2702.6</v>
       </c>
       <c r="O34">
         <v>0</v>
@@ -2005,7 +2009,7 @@
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>24-11-2024</v>
+        <v>24-11-2025</v>
       </c>
       <c r="D35" t="str">
         <v>BankniftyCE</v>
@@ -2014,10 +2018,10 @@
         <v>35</v>
       </c>
       <c r="F35">
-        <v>405</v>
+        <v>405.1</v>
       </c>
       <c r="G35">
-        <v>448</v>
+        <v>448.1</v>
       </c>
       <c r="H35">
         <v>43</v>
@@ -2052,7 +2056,7 @@
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>24-11-2024</v>
+        <v>24-11-2025</v>
       </c>
       <c r="D36" t="str">
         <v>BankniftyPE</v>
@@ -2061,16 +2065,16 @@
         <v>35</v>
       </c>
       <c r="F36">
-        <v>434</v>
+        <v>433.5</v>
       </c>
       <c r="G36">
-        <v>473</v>
+        <v>472.55</v>
       </c>
       <c r="H36">
-        <v>39</v>
+        <v>39.05000000000001</v>
       </c>
       <c r="I36">
-        <v>2734</v>
+        <v>2733.5</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2085,7 +2089,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N36">
-        <v>2680</v>
+        <v>2679.5</v>
       </c>
       <c r="O36">
         <v>0</v>
@@ -2099,7 +2103,7 @@
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>26-11-2024</v>
+        <v>26-11-2025</v>
       </c>
       <c r="D37" t="str">
         <v>NiftyCE</v>
@@ -2111,10 +2115,10 @@
         <v>214</v>
       </c>
       <c r="G37">
-        <v>243</v>
+        <v>243.3983</v>
       </c>
       <c r="H37">
-        <v>29</v>
+        <v>29.398300000000006</v>
       </c>
       <c r="I37">
         <v>4409</v>
@@ -2146,7 +2150,7 @@
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>03-12-2024</v>
+        <v>03-12-2025</v>
       </c>
       <c r="D38" t="str">
         <v>NiftyPE</v>
@@ -2155,16 +2159,16 @@
         <v>75</v>
       </c>
       <c r="F38">
-        <v>185</v>
+        <v>184.7</v>
       </c>
       <c r="G38">
-        <v>204</v>
+        <v>204.15</v>
       </c>
       <c r="H38">
-        <v>19</v>
+        <v>19.45</v>
       </c>
       <c r="I38">
-        <v>1459</v>
+        <v>1458.75</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2179,7 +2183,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N38">
-        <v>1435</v>
+        <v>1434.75</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -2193,7 +2197,7 @@
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>03-12-2024</v>
+        <v>03-12-2025</v>
       </c>
       <c r="D39" t="str">
         <v>BankniftyPE</v>
@@ -2202,16 +2206,16 @@
         <v>35</v>
       </c>
       <c r="F39">
-        <v>463</v>
+        <v>463.15</v>
       </c>
       <c r="G39">
-        <v>482</v>
+        <v>482.05</v>
       </c>
       <c r="H39">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="I39">
-        <v>662</v>
+        <v>661.5</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2226,7 +2230,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N39">
-        <v>642</v>
+        <v>641.5</v>
       </c>
       <c r="O39">
         <v>0</v>
@@ -2240,7 +2244,7 @@
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>05-12-2024</v>
+        <v>05-12-2025</v>
       </c>
       <c r="D40" t="str">
         <v>NiftyCE</v>
@@ -2249,19 +2253,19 @@
         <v>75</v>
       </c>
       <c r="F40">
-        <v>196</v>
+        <v>196.05</v>
       </c>
       <c r="G40">
         <v>156</v>
       </c>
       <c r="H40">
-        <v>-40</v>
+        <v>-40.05</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40">
-        <v>-3004</v>
+        <v>-3003.75</v>
       </c>
       <c r="K40">
         <v>24</v>
@@ -2273,7 +2277,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N40">
-        <v>-3028</v>
+        <v>-3027.75</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -2287,7 +2291,7 @@
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>05-12-2024</v>
+        <v>05-12-2025</v>
       </c>
       <c r="D41" t="str">
         <v>BankniftyCE</v>
@@ -2296,13 +2300,13 @@
         <v>35</v>
       </c>
       <c r="F41">
-        <v>406</v>
+        <v>406.2</v>
       </c>
       <c r="G41">
-        <v>345</v>
+        <v>344.6</v>
       </c>
       <c r="H41">
-        <v>-62</v>
+        <v>-61.6</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2334,7 +2338,7 @@
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>10-12-2024</v>
+        <v>10-12-2025</v>
       </c>
       <c r="D42" t="str">
         <v>NiftyCE</v>
@@ -2343,19 +2347,19 @@
         <v>75</v>
       </c>
       <c r="F42">
-        <v>192</v>
+        <v>191.65</v>
       </c>
       <c r="G42">
-        <v>177</v>
+        <v>177.4</v>
       </c>
       <c r="H42">
-        <v>-14</v>
+        <v>-14.25</v>
       </c>
       <c r="I42">
         <v>0</v>
       </c>
       <c r="J42">
-        <v>-1069</v>
+        <v>-1068.75</v>
       </c>
       <c r="K42">
         <v>24</v>
@@ -2367,7 +2371,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N42">
-        <v>-1093</v>
+        <v>-1092.75</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -2381,7 +2385,7 @@
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>11-12-2024</v>
+        <v>11-12-2025</v>
       </c>
       <c r="D43" t="str">
         <v>BankniftyCE</v>
@@ -2390,19 +2394,19 @@
         <v>35</v>
       </c>
       <c r="F43">
-        <v>406</v>
+        <v>405.8</v>
       </c>
       <c r="G43">
-        <v>351</v>
+        <v>350.5</v>
       </c>
       <c r="H43">
-        <v>-55</v>
+        <v>-55.3</v>
       </c>
       <c r="I43">
         <v>0</v>
       </c>
       <c r="J43">
-        <v>-1936</v>
+        <v>-1935.5000000000005</v>
       </c>
       <c r="K43">
         <v>20</v>
@@ -2414,7 +2418,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N43">
-        <v>-1956</v>
+        <v>-1955.5</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -2428,7 +2432,7 @@
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>12-12-2024</v>
+        <v>12-12-2025</v>
       </c>
       <c r="D44" t="str">
         <v>Sensex CE</v>
@@ -2437,19 +2441,19 @@
         <v>20</v>
       </c>
       <c r="F44">
-        <v>528</v>
+        <v>527.5</v>
       </c>
       <c r="G44">
-        <v>432</v>
+        <v>432.45</v>
       </c>
       <c r="H44">
-        <v>-95</v>
+        <v>-95.05</v>
       </c>
       <c r="I44">
         <v>0</v>
       </c>
       <c r="J44">
-        <v>-1901</v>
+        <v>-1901.0000000000002</v>
       </c>
       <c r="K44">
         <v>24</v>
@@ -2475,7 +2479,7 @@
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>15-12-2024</v>
+        <v>15-12-2025</v>
       </c>
       <c r="D45" t="str">
         <v>NiftyPE</v>
@@ -2484,16 +2488,16 @@
         <v>75</v>
       </c>
       <c r="F45">
-        <v>224</v>
+        <v>223.9</v>
       </c>
       <c r="G45">
-        <v>233</v>
+        <v>233.35</v>
       </c>
       <c r="H45">
-        <v>9</v>
+        <v>9.45</v>
       </c>
       <c r="I45">
-        <v>709</v>
+        <v>708.75</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -2508,7 +2512,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N45">
-        <v>685</v>
+        <v>684.75</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -2522,7 +2526,7 @@
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>16-12-2024</v>
+        <v>16-12-2025</v>
       </c>
       <c r="D46" t="str">
         <v>Sensex PE</v>
@@ -2531,13 +2535,13 @@
         <v>20</v>
       </c>
       <c r="F46">
-        <v>514</v>
+        <v>513.75</v>
       </c>
       <c r="G46">
-        <v>625</v>
+        <v>625.1</v>
       </c>
       <c r="H46">
-        <v>111</v>
+        <v>111.35</v>
       </c>
       <c r="I46">
         <v>2227</v>
@@ -2569,7 +2573,7 @@
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>16-12-2024</v>
+        <v>16-12-2025</v>
       </c>
       <c r="D47" t="str">
         <v>NiftyPE</v>
@@ -2578,19 +2582,19 @@
         <v>75</v>
       </c>
       <c r="F47">
-        <v>178</v>
+        <v>177.9</v>
       </c>
       <c r="G47">
-        <v>164</v>
+        <v>164.2</v>
       </c>
       <c r="H47">
-        <v>-14</v>
+        <v>-13.7</v>
       </c>
       <c r="I47">
         <v>0</v>
       </c>
       <c r="J47">
-        <v>-1028</v>
+        <v>-1027.5000000000014</v>
       </c>
       <c r="K47">
         <v>24</v>
@@ -2602,7 +2606,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N47">
-        <v>-1052</v>
+        <v>-1051.5</v>
       </c>
       <c r="O47">
         <v>0</v>
@@ -2616,7 +2620,7 @@
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>18-12-2024</v>
+        <v>18-12-2025</v>
       </c>
       <c r="D48" t="str">
         <v>NiftyPE</v>
@@ -2625,16 +2629,16 @@
         <v>75</v>
       </c>
       <c r="F48">
-        <v>199</v>
+        <v>198.75</v>
       </c>
       <c r="G48">
-        <v>215</v>
+        <v>215.3</v>
       </c>
       <c r="H48">
-        <v>17</v>
+        <v>16.55</v>
       </c>
       <c r="I48">
-        <v>1241</v>
+        <v>1241.25</v>
       </c>
       <c r="J48">
         <v>0</v>
@@ -2649,7 +2653,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N48">
-        <v>1217</v>
+        <v>1217.25</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -2663,7 +2667,7 @@
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>19-12-2024</v>
+        <v>19-12-2025</v>
       </c>
       <c r="D49" t="str">
         <v>NiftyCE</v>
@@ -2672,19 +2676,19 @@
         <v>75</v>
       </c>
       <c r="F49">
-        <v>188</v>
+        <v>188.4</v>
       </c>
       <c r="G49">
-        <v>175</v>
+        <v>175.2</v>
       </c>
       <c r="H49">
-        <v>-13</v>
+        <v>-13.2</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49">
-        <v>-990</v>
+        <v>-990.0000000000013</v>
       </c>
       <c r="K49">
         <v>24</v>
@@ -2710,7 +2714,7 @@
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>19-12-2024</v>
+        <v>19-12-2025</v>
       </c>
       <c r="D50" t="str">
         <v>Sensex CE</v>
@@ -2719,19 +2723,19 @@
         <v>20</v>
       </c>
       <c r="F50">
-        <v>475</v>
+        <v>475.3</v>
       </c>
       <c r="G50">
-        <v>439</v>
+        <v>439.1</v>
       </c>
       <c r="H50">
-        <v>-36</v>
+        <v>-36.2</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50">
-        <v>-724</v>
+        <v>-723.9999999999998</v>
       </c>
       <c r="K50">
         <v>24</v>
@@ -2757,7 +2761,7 @@
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>22-12-2024</v>
+        <v>22-12-2025</v>
       </c>
       <c r="D51" t="str">
         <v>BankniftyCE</v>
@@ -2766,16 +2770,16 @@
         <v>35</v>
       </c>
       <c r="F51">
-        <v>420</v>
+        <v>419.85</v>
       </c>
       <c r="G51">
         <v>442</v>
       </c>
       <c r="H51">
-        <v>22</v>
+        <v>22.15</v>
       </c>
       <c r="I51">
-        <v>775</v>
+        <v>775.25</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -2790,7 +2794,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N51">
-        <v>755</v>
+        <v>755.25</v>
       </c>
       <c r="O51">
         <v>0</v>
@@ -2804,7 +2808,7 @@
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>22-12-2024</v>
+        <v>22-12-2025</v>
       </c>
       <c r="D52" t="str">
         <v>NiftyCE</v>
@@ -2813,19 +2817,19 @@
         <v>75</v>
       </c>
       <c r="F52">
-        <v>195</v>
+        <v>195.35</v>
       </c>
       <c r="G52">
-        <v>192</v>
+        <v>191.75</v>
       </c>
       <c r="H52">
-        <v>-4</v>
+        <v>-3.6</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52">
-        <v>-270</v>
+        <v>-269.99999999999955</v>
       </c>
       <c r="K52">
         <v>24</v>
@@ -2851,7 +2855,7 @@
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>22-12-2024</v>
+        <v>22-12-2025</v>
       </c>
       <c r="D53" t="str">
         <v>Sensex CE</v>
@@ -2860,13 +2864,13 @@
         <v>20</v>
       </c>
       <c r="F53">
-        <v>521</v>
+        <v>520.75</v>
       </c>
       <c r="G53">
         <v>473</v>
       </c>
       <c r="H53">
-        <v>-48</v>
+        <v>-47.75</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2898,7 +2902,7 @@
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>24-12-2024</v>
+        <v>24-12-2025</v>
       </c>
       <c r="D54" t="str">
         <v>BankniftyCE</v>
@@ -2910,16 +2914,16 @@
         <v>384</v>
       </c>
       <c r="G54">
-        <v>369</v>
+        <v>369.2</v>
       </c>
       <c r="H54">
-        <v>-15</v>
+        <v>-14.8</v>
       </c>
       <c r="I54">
         <v>0</v>
       </c>
       <c r="J54">
-        <v>-518</v>
+        <v>-518.0000000000005</v>
       </c>
       <c r="K54">
         <v>20</v>
@@ -2945,7 +2949,7 @@
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>24-12-2024</v>
+        <v>24-12-2025</v>
       </c>
       <c r="D55" t="str">
         <v>BankniftyPE</v>
@@ -2954,16 +2958,16 @@
         <v>35</v>
       </c>
       <c r="F55">
-        <v>426</v>
+        <v>425.55</v>
       </c>
       <c r="G55">
-        <v>469</v>
+        <v>468.7</v>
       </c>
       <c r="H55">
-        <v>43</v>
+        <v>43.15</v>
       </c>
       <c r="I55">
-        <v>1510</v>
+        <v>1510.25</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -2978,7 +2982,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N55">
-        <v>1490</v>
+        <v>1490.25</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -2992,7 +2996,7 @@
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>24-12-2024</v>
+        <v>24-12-2025</v>
       </c>
       <c r="D56" t="str">
         <v>NiftyPE</v>
@@ -3004,16 +3008,16 @@
         <v>198</v>
       </c>
       <c r="G56">
-        <v>182</v>
+        <v>182.1</v>
       </c>
       <c r="H56">
-        <v>-16</v>
+        <v>-15.9</v>
       </c>
       <c r="I56">
         <v>0</v>
       </c>
       <c r="J56">
-        <v>-1193</v>
+        <v>-1192.5000000000005</v>
       </c>
       <c r="K56">
         <v>24</v>
@@ -3025,7 +3029,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N56">
-        <v>-1217</v>
+        <v>-1216.5</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -3039,7 +3043,7 @@
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>26-12-2024</v>
+        <v>26-12-2025</v>
       </c>
       <c r="D57" t="str">
         <v>BankniftyPE</v>
@@ -3048,19 +3052,19 @@
         <v>35</v>
       </c>
       <c r="F57">
-        <v>497</v>
+        <v>497.4</v>
       </c>
       <c r="G57">
-        <v>486</v>
+        <v>485.8</v>
       </c>
       <c r="H57">
-        <v>-12</v>
+        <v>-11.6</v>
       </c>
       <c r="I57">
         <v>0</v>
       </c>
       <c r="J57">
-        <v>-406</v>
+        <v>-405.9999999999988</v>
       </c>
       <c r="K57">
         <v>20</v>
@@ -3086,7 +3090,7 @@
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>29-12-2024</v>
+        <v>29-12-2025</v>
       </c>
       <c r="D58" t="str">
         <v>BankniftyPE</v>
@@ -3095,16 +3099,16 @@
         <v>35</v>
       </c>
       <c r="F58">
-        <v>473</v>
+        <v>472.5</v>
       </c>
       <c r="G58">
-        <v>486</v>
+        <v>485.75</v>
       </c>
       <c r="H58">
-        <v>13</v>
+        <v>13.25</v>
       </c>
       <c r="I58">
-        <v>464</v>
+        <v>463.75</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -3119,7 +3123,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N58">
-        <v>444</v>
+        <v>443.75</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -3133,7 +3137,7 @@
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>29-12-2024</v>
+        <v>29-12-2025</v>
       </c>
       <c r="D59" t="str">
         <v>NiftyPE</v>
@@ -3142,16 +3146,16 @@
         <v>75</v>
       </c>
       <c r="F59">
-        <v>206</v>
+        <v>206.1</v>
       </c>
       <c r="G59">
-        <v>217</v>
+        <v>217.15</v>
       </c>
       <c r="H59">
-        <v>11</v>
+        <v>11.05</v>
       </c>
       <c r="I59">
-        <v>829</v>
+        <v>828.75</v>
       </c>
       <c r="J59">
         <v>0</v>
@@ -3166,7 +3170,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N59">
-        <v>805</v>
+        <v>804.75</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -3180,7 +3184,7 @@
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>30-12-2024</v>
+        <v>30-12-2025</v>
       </c>
       <c r="D60" t="str">
         <v>BankniftyPE</v>
@@ -3189,16 +3193,16 @@
         <v>35</v>
       </c>
       <c r="F60">
-        <v>482</v>
+        <v>482.3</v>
       </c>
       <c r="G60">
-        <v>536</v>
+        <v>535.85</v>
       </c>
       <c r="H60">
-        <v>54</v>
+        <v>53.55</v>
       </c>
       <c r="I60">
-        <v>1874</v>
+        <v>1874.25</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3213,7 +3217,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N60">
-        <v>1854</v>
+        <v>1854.25</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -3227,7 +3231,7 @@
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>30-12-2024</v>
+        <v>30-12-2025</v>
       </c>
       <c r="D61" t="str">
         <v>NiftyPE</v>
@@ -3236,19 +3240,19 @@
         <v>75</v>
       </c>
       <c r="F61">
-        <v>217</v>
+        <v>216.75</v>
       </c>
       <c r="G61">
-        <v>191</v>
+        <v>190.65</v>
       </c>
       <c r="H61">
-        <v>-26</v>
+        <v>-26.1</v>
       </c>
       <c r="I61">
         <v>0</v>
       </c>
       <c r="J61">
-        <v>-1958</v>
+        <v>-1957.4999999999995</v>
       </c>
       <c r="K61">
         <v>24</v>
@@ -3260,7 +3264,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N61">
-        <v>-1982</v>
+        <v>-1981.5</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -3274,7 +3278,7 @@
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>30-12-2024</v>
+        <v>30-12-2025</v>
       </c>
       <c r="D62" t="str">
         <v>Sensex PE</v>
@@ -3283,19 +3287,19 @@
         <v>20</v>
       </c>
       <c r="F62">
-        <v>501</v>
+        <v>500.6</v>
       </c>
       <c r="G62">
-        <v>413</v>
+        <v>413.25</v>
       </c>
       <c r="H62">
-        <v>-87</v>
+        <v>-87.35</v>
       </c>
       <c r="I62">
         <v>0</v>
       </c>
       <c r="J62">
-        <v>-1747</v>
+        <v>-1747.0000000000005</v>
       </c>
       <c r="K62">
         <v>24</v>
@@ -3321,7 +3325,7 @@
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>31-12-2024</v>
+        <v>31-12-2025</v>
       </c>
       <c r="D63" t="str">
         <v>BankniftyCE</v>
@@ -3330,19 +3334,19 @@
         <v>30</v>
       </c>
       <c r="F63">
-        <v>406</v>
+        <v>406.45</v>
       </c>
       <c r="G63">
-        <v>391</v>
+        <v>391.2</v>
       </c>
       <c r="H63">
-        <v>-15</v>
+        <v>-15.25</v>
       </c>
       <c r="I63">
         <v>0</v>
       </c>
       <c r="J63">
-        <v>-458</v>
+        <v>-457.5</v>
       </c>
       <c r="K63">
         <v>20</v>
@@ -3354,7 +3358,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N63">
-        <v>-478</v>
+        <v>-477.5</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -3368,7 +3372,7 @@
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>31-12-2024</v>
+        <v>31-12-2025</v>
       </c>
       <c r="D64" t="str">
         <v>NiftyCE</v>
@@ -3377,16 +3381,16 @@
         <v>65</v>
       </c>
       <c r="F64">
-        <v>206</v>
+        <v>206.4</v>
       </c>
       <c r="G64">
-        <v>230</v>
+        <v>230.05</v>
       </c>
       <c r="H64">
-        <v>24</v>
+        <v>23.65</v>
       </c>
       <c r="I64">
-        <v>1537</v>
+        <v>1537.25</v>
       </c>
       <c r="J64">
         <v>0</v>
@@ -3401,7 +3405,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N64">
-        <v>1513</v>
+        <v>1513.25</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -3415,7 +3419,7 @@
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>31-12-2024</v>
+        <v>31-12-2025</v>
       </c>
       <c r="D65" t="str">
         <v>BankniftyCE</v>
@@ -3424,13 +3428,13 @@
         <v>30</v>
       </c>
       <c r="F65">
-        <v>418</v>
+        <v>417.5</v>
       </c>
       <c r="G65">
-        <v>437</v>
+        <v>436.7</v>
       </c>
       <c r="H65">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="I65">
         <v>576</v>
@@ -3462,7 +3466,7 @@
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>31-12-2024</v>
+        <v>31-12-2025</v>
       </c>
       <c r="D66" t="str">
         <v>Sensex CE</v>
@@ -3471,13 +3475,13 @@
         <v>20</v>
       </c>
       <c r="F66">
-        <v>541</v>
+        <v>541.1</v>
       </c>
       <c r="G66">
-        <v>592</v>
+        <v>592.35</v>
       </c>
       <c r="H66">
-        <v>51</v>
+        <v>51.25</v>
       </c>
       <c r="I66">
         <v>1025</v>
@@ -3509,7 +3513,7 @@
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>31-12-2024</v>
+        <v>31-12-2025</v>
       </c>
       <c r="D67" t="str">
         <v>Sensex CE</v>
@@ -3518,13 +3522,13 @@
         <v>20</v>
       </c>
       <c r="F67">
-        <v>509</v>
+        <v>509.35</v>
       </c>
       <c r="G67">
         <v>569</v>
       </c>
       <c r="H67">
-        <v>60</v>
+        <v>59.65</v>
       </c>
       <c r="I67">
         <v>1193</v>
@@ -3556,7 +3560,7 @@
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>31-12-2024</v>
+        <v>31-12-2025</v>
       </c>
       <c r="D68" t="str">
         <v>Sensex CE</v>
@@ -3565,19 +3569,19 @@
         <v>20</v>
       </c>
       <c r="F68">
-        <v>493</v>
+        <v>493.4</v>
       </c>
       <c r="G68">
-        <v>487</v>
+        <v>486.6</v>
       </c>
       <c r="H68">
-        <v>-7</v>
+        <v>-6.8</v>
       </c>
       <c r="I68">
         <v>0</v>
       </c>
       <c r="J68">
-        <v>-136</v>
+        <v>-135.9999999999991</v>
       </c>
       <c r="K68">
         <v>24</v>
@@ -3603,7 +3607,7 @@
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>02-01-2025</v>
+        <v>02-01-2026</v>
       </c>
       <c r="D69" t="str">
         <v>NiftyCE</v>
@@ -3615,13 +3619,13 @@
         <v>200</v>
       </c>
       <c r="G69">
-        <v>236</v>
+        <v>236.15</v>
       </c>
       <c r="H69">
-        <v>36</v>
+        <v>36.15</v>
       </c>
       <c r="I69">
-        <v>2350</v>
+        <v>2349.75</v>
       </c>
       <c r="J69">
         <v>0</v>
@@ -3636,7 +3640,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N69">
-        <v>2326</v>
+        <v>2325.75</v>
       </c>
       <c r="O69">
         <v>0</v>
@@ -3650,7 +3654,7 @@
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>02-01-2025</v>
+        <v>02-01-2026</v>
       </c>
       <c r="D70" t="str">
         <v>Sensex CE</v>
@@ -3659,19 +3663,19 @@
         <v>20</v>
       </c>
       <c r="F70">
-        <v>532</v>
+        <v>532.2</v>
       </c>
       <c r="G70">
-        <v>527</v>
+        <v>527.25</v>
       </c>
       <c r="H70">
-        <v>-5</v>
+        <v>-4.95</v>
       </c>
       <c r="I70">
         <v>0</v>
       </c>
       <c r="J70">
-        <v>-99</v>
+        <v>-99.00000000000091</v>
       </c>
       <c r="K70">
         <v>24</v>
@@ -3697,7 +3701,7 @@
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>02-01-2025</v>
+        <v>02-01-2026</v>
       </c>
       <c r="D71" t="str">
         <v>Sensex CE</v>
@@ -3706,19 +3710,19 @@
         <v>20</v>
       </c>
       <c r="F71">
-        <v>471</v>
+        <v>470.95</v>
       </c>
       <c r="G71">
-        <v>439</v>
+        <v>438.9</v>
       </c>
       <c r="H71">
-        <v>-32</v>
+        <v>-32.05</v>
       </c>
       <c r="I71">
         <v>0</v>
       </c>
       <c r="J71">
-        <v>-641</v>
+        <v>-641.0000000000002</v>
       </c>
       <c r="K71">
         <v>24</v>
@@ -3744,7 +3748,7 @@
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>05-01-2025</v>
+        <v>05-01-2026</v>
       </c>
       <c r="D72" t="str">
         <v>NiftyPE</v>
@@ -3753,19 +3757,19 @@
         <v>65</v>
       </c>
       <c r="F72">
-        <v>188</v>
+        <v>188.05</v>
       </c>
       <c r="G72">
-        <v>181</v>
+        <v>180.55</v>
       </c>
       <c r="H72">
-        <v>-8</v>
+        <v>-7.5</v>
       </c>
       <c r="I72">
         <v>0</v>
       </c>
       <c r="J72">
-        <v>-488</v>
+        <v>-487.5</v>
       </c>
       <c r="K72">
         <v>24</v>
@@ -3777,7 +3781,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N72">
-        <v>-512</v>
+        <v>-511.5</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -3791,7 +3795,7 @@
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>06-01-2025</v>
+        <v>06-01-2026</v>
       </c>
       <c r="D73" t="str">
         <v>Sensex PE</v>
@@ -3800,13 +3804,13 @@
         <v>20</v>
       </c>
       <c r="F73">
-        <v>473</v>
+        <v>473.35</v>
       </c>
       <c r="G73">
-        <v>376</v>
+        <v>376.1</v>
       </c>
       <c r="H73">
-        <v>-97</v>
+        <v>-97.25</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3838,7 +3842,7 @@
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>07-01-2025</v>
+        <v>07-01-2026</v>
       </c>
       <c r="D74" t="str">
         <v>BankniftyPE</v>
@@ -3847,19 +3851,19 @@
         <v>30</v>
       </c>
       <c r="F74">
-        <v>500</v>
+        <v>499.95</v>
       </c>
       <c r="G74">
-        <v>472</v>
+        <v>471.9</v>
       </c>
       <c r="H74">
-        <v>-28</v>
+        <v>-28.05</v>
       </c>
       <c r="I74">
         <v>0</v>
       </c>
       <c r="J74">
-        <v>-842</v>
+        <v>-841.5000000000003</v>
       </c>
       <c r="K74">
         <v>20</v>
@@ -3871,7 +3875,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N74">
-        <v>-862</v>
+        <v>-861.5</v>
       </c>
       <c r="O74">
         <v>0</v>
@@ -3885,7 +3889,7 @@
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>08-01-2025</v>
+        <v>08-01-2026</v>
       </c>
       <c r="D75" t="str">
         <v>NiftyPE</v>
@@ -3897,16 +3901,16 @@
         <v>192</v>
       </c>
       <c r="G75">
-        <v>181</v>
+        <v>180.55</v>
       </c>
       <c r="H75">
-        <v>-11</v>
+        <v>-11.45</v>
       </c>
       <c r="I75">
         <v>0</v>
       </c>
       <c r="J75">
-        <v>-744</v>
+        <v>-744.2499999999993</v>
       </c>
       <c r="K75">
         <v>24</v>
@@ -3918,7 +3922,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N75">
-        <v>-768</v>
+        <v>-768.25</v>
       </c>
       <c r="O75">
         <v>0</v>
@@ -3932,7 +3936,7 @@
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>08-01-2025</v>
+        <v>08-01-2026</v>
       </c>
       <c r="D76" t="str">
         <v>BankniftyPE</v>
@@ -3979,7 +3983,7 @@
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>09-01-2025</v>
+        <v>09-01-2026</v>
       </c>
       <c r="D77" t="str">
         <v>NiftyPE</v>
@@ -3988,16 +3992,16 @@
         <v>65</v>
       </c>
       <c r="F77">
-        <v>190</v>
+        <v>189.8</v>
       </c>
       <c r="G77">
-        <v>212</v>
+        <v>212.45</v>
       </c>
       <c r="H77">
-        <v>23</v>
+        <v>22.65</v>
       </c>
       <c r="I77">
-        <v>1472</v>
+        <v>1472.25</v>
       </c>
       <c r="J77">
         <v>0</v>
@@ -4012,7 +4016,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N77">
-        <v>1448</v>
+        <v>1448.25</v>
       </c>
       <c r="O77">
         <v>0</v>
@@ -4026,7 +4030,7 @@
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>09-01-2025</v>
+        <v>09-01-2026</v>
       </c>
       <c r="D78" t="str">
         <v>BankniftyPE</v>
@@ -4035,13 +4039,13 @@
         <v>30</v>
       </c>
       <c r="F78">
-        <v>512</v>
+        <v>512.4</v>
       </c>
       <c r="G78">
-        <v>529</v>
+        <v>529.1</v>
       </c>
       <c r="H78">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="I78">
         <v>501</v>
@@ -4073,7 +4077,7 @@
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>12-01-2025</v>
+        <v>12-01-2026</v>
       </c>
       <c r="D79" t="str">
         <v>NiftyPE</v>
@@ -4082,19 +4086,19 @@
         <v>65</v>
       </c>
       <c r="F79">
-        <v>202</v>
+        <v>202.4</v>
       </c>
       <c r="G79">
-        <v>176</v>
+        <v>175.9</v>
       </c>
       <c r="H79">
-        <v>-27</v>
+        <v>-26.5</v>
       </c>
       <c r="I79">
         <v>0</v>
       </c>
       <c r="J79">
-        <v>-1723</v>
+        <v>-1722.5</v>
       </c>
       <c r="K79">
         <v>24</v>
@@ -4106,7 +4110,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N79">
-        <v>-1747</v>
+        <v>-1746.5</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -4120,7 +4124,7 @@
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>13-01-2025</v>
+        <v>13-01-2026</v>
       </c>
       <c r="D80" t="str">
         <v>NiftyPE</v>
@@ -4129,16 +4133,16 @@
         <v>65</v>
       </c>
       <c r="F80">
-        <v>190</v>
+        <v>189.8</v>
       </c>
       <c r="G80">
-        <v>220</v>
+        <v>219.9</v>
       </c>
       <c r="H80">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="I80">
-        <v>1957</v>
+        <v>1956.5</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4153,7 +4157,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N80">
-        <v>1933</v>
+        <v>1932.5</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -4167,7 +4171,7 @@
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>13-01-2025</v>
+        <v>13-01-2026</v>
       </c>
       <c r="D81" t="str">
         <v>BankniftyPE</v>
@@ -4176,10 +4180,10 @@
         <v>30</v>
       </c>
       <c r="F81">
-        <v>519</v>
+        <v>519.35</v>
       </c>
       <c r="G81">
-        <v>554</v>
+        <v>554.35</v>
       </c>
       <c r="H81">
         <v>35</v>
@@ -4214,7 +4218,7 @@
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>14-01-2025</v>
+        <v>14-01-2026</v>
       </c>
       <c r="D82" t="str">
         <v>Sensex PE</v>
@@ -4223,13 +4227,13 @@
         <v>20</v>
       </c>
       <c r="F82">
-        <v>756</v>
+        <v>756.05</v>
       </c>
       <c r="G82">
-        <v>848</v>
+        <v>848.15</v>
       </c>
       <c r="H82">
-        <v>92</v>
+        <v>92.1</v>
       </c>
       <c r="I82">
         <v>1842</v>
@@ -4261,7 +4265,7 @@
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>16-01-2025</v>
+        <v>16-01-2026</v>
       </c>
       <c r="D83" t="str">
         <v>BankniftyCE</v>
@@ -4270,13 +4274,13 @@
         <v>30</v>
       </c>
       <c r="F83">
-        <v>402</v>
+        <v>402.4</v>
       </c>
       <c r="G83">
-        <v>465</v>
+        <v>464.7</v>
       </c>
       <c r="H83">
-        <v>62</v>
+        <v>62.3</v>
       </c>
       <c r="I83">
         <v>1869</v>
@@ -4308,7 +4312,7 @@
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>16-01-2025</v>
+        <v>16-01-2026</v>
       </c>
       <c r="D84" t="str">
         <v>Sensex CE</v>
@@ -4317,13 +4321,13 @@
         <v>20</v>
       </c>
       <c r="F84">
-        <v>609</v>
+        <v>608.9</v>
       </c>
       <c r="G84">
-        <v>705</v>
+        <v>705.25</v>
       </c>
       <c r="H84">
-        <v>96</v>
+        <v>96.35</v>
       </c>
       <c r="I84">
         <v>1927</v>
@@ -4355,7 +4359,7 @@
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>19-01-2025</v>
+        <v>19-01-2026</v>
       </c>
       <c r="D85" t="str">
         <v>Sensex PE</v>
@@ -4364,13 +4368,13 @@
         <v>20</v>
       </c>
       <c r="F85">
-        <v>782</v>
+        <v>781.95</v>
       </c>
       <c r="G85">
-        <v>890</v>
+        <v>890.2</v>
       </c>
       <c r="H85">
-        <v>108</v>
+        <v>108.25</v>
       </c>
       <c r="I85">
         <v>2165</v>
@@ -4402,7 +4406,7 @@
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>19-01-2025</v>
+        <v>19-01-2026</v>
       </c>
       <c r="D86" t="str">
         <v>BankniftyPE</v>
@@ -4411,13 +4415,13 @@
         <v>30</v>
       </c>
       <c r="F86">
-        <v>503</v>
+        <v>502.6</v>
       </c>
       <c r="G86">
-        <v>541</v>
+        <v>541.2</v>
       </c>
       <c r="H86">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="I86">
         <v>1158</v>
@@ -4449,7 +4453,7 @@
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>20-01-2025</v>
+        <v>20-01-2026</v>
       </c>
       <c r="D87" t="str">
         <v>Sensex PE</v>
@@ -4458,13 +4462,13 @@
         <v>20</v>
       </c>
       <c r="F87">
-        <v>844</v>
+        <v>844.35</v>
       </c>
       <c r="G87">
-        <v>899</v>
+        <v>898.5</v>
       </c>
       <c r="H87">
-        <v>54</v>
+        <v>54.15</v>
       </c>
       <c r="I87">
         <v>1083</v>
@@ -4496,7 +4500,7 @@
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>21-01-2025</v>
+        <v>21-01-2026</v>
       </c>
       <c r="D88" t="str">
         <v>BankniftyPE</v>
@@ -4505,16 +4509,16 @@
         <v>30</v>
       </c>
       <c r="F88">
-        <v>498</v>
+        <v>498.15</v>
       </c>
       <c r="G88">
-        <v>605</v>
+        <v>605.4</v>
       </c>
       <c r="H88">
-        <v>107</v>
+        <v>107.25</v>
       </c>
       <c r="I88">
-        <v>3218</v>
+        <v>3217.5</v>
       </c>
       <c r="J88">
         <v>0</v>
@@ -4529,7 +4533,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N88">
-        <v>3198</v>
+        <v>3197.5</v>
       </c>
       <c r="O88">
         <v>0</v>
@@ -4543,7 +4547,7 @@
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>22-01-2025</v>
+        <v>22-01-2026</v>
       </c>
       <c r="D89" t="str">
         <v>BankniftyCE</v>
@@ -4552,16 +4556,16 @@
         <v>30</v>
       </c>
       <c r="F89">
-        <v>387</v>
+        <v>387.1</v>
       </c>
       <c r="G89">
-        <v>474</v>
+        <v>474.05</v>
       </c>
       <c r="H89">
-        <v>87</v>
+        <v>86.95</v>
       </c>
       <c r="I89">
-        <v>2609</v>
+        <v>2608.5</v>
       </c>
       <c r="J89">
         <v>0</v>
@@ -4576,7 +4580,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N89">
-        <v>2585</v>
+        <v>2584.5</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -4590,7 +4594,7 @@
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>22-01-2025</v>
+        <v>22-01-2026</v>
       </c>
       <c r="D90" t="str">
         <v>NiftyCE</v>
@@ -4599,10 +4603,10 @@
         <v>65</v>
       </c>
       <c r="F90">
-        <v>211</v>
+        <v>211.25</v>
       </c>
       <c r="G90">
-        <v>271</v>
+        <v>271.25</v>
       </c>
       <c r="H90">
         <v>60</v>
@@ -4637,7 +4641,7 @@
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>22-01-2025</v>
+        <v>22-01-2026</v>
       </c>
       <c r="D91" t="str">
         <v>Sensex CE</v>
@@ -4646,13 +4650,13 @@
         <v>20</v>
       </c>
       <c r="F91">
-        <v>615</v>
+        <v>614.85</v>
       </c>
       <c r="G91">
-        <v>734</v>
+        <v>733.5</v>
       </c>
       <c r="H91">
-        <v>119</v>
+        <v>118.65</v>
       </c>
       <c r="I91">
         <v>2373</v>
@@ -4684,7 +4688,7 @@
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>23-01-2025</v>
+        <v>23-01-2026</v>
       </c>
       <c r="D92" t="str">
         <v>Sensex PE</v>
@@ -4693,19 +4697,19 @@
         <v>20</v>
       </c>
       <c r="F92">
-        <v>782</v>
+        <v>781.6</v>
       </c>
       <c r="G92">
-        <v>764</v>
+        <v>763.95</v>
       </c>
       <c r="H92">
-        <v>-18</v>
+        <v>-17.65</v>
       </c>
       <c r="I92">
         <v>0</v>
       </c>
       <c r="J92">
-        <v>-353</v>
+        <v>-352.99999999999955</v>
       </c>
       <c r="K92">
         <v>98</v>
@@ -4731,7 +4735,7 @@
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>23-01-2025</v>
+        <v>23-01-2026</v>
       </c>
       <c r="D93" t="str">
         <v>NiftyPE</v>
@@ -4740,16 +4744,16 @@
         <v>65</v>
       </c>
       <c r="F93">
-        <v>191</v>
+        <v>190.6</v>
       </c>
       <c r="G93">
-        <v>223</v>
+        <v>223.25</v>
       </c>
       <c r="H93">
-        <v>33</v>
+        <v>32.65</v>
       </c>
       <c r="I93">
-        <v>2122</v>
+        <v>2122.25</v>
       </c>
       <c r="J93">
         <v>0</v>
@@ -4764,7 +4768,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N93">
-        <v>2017</v>
+        <v>2017.25</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -4778,7 +4782,7 @@
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>23-01-2025</v>
+        <v>23-01-2026</v>
       </c>
       <c r="D94" t="str">
         <v>BankniftyPE</v>
@@ -4787,13 +4791,13 @@
         <v>30</v>
       </c>
       <c r="F94">
-        <v>471</v>
+        <v>471.45</v>
       </c>
       <c r="G94">
-        <v>500</v>
+        <v>500.15</v>
       </c>
       <c r="H94">
-        <v>29</v>
+        <v>28.7</v>
       </c>
       <c r="I94">
         <v>861</v>
@@ -4825,7 +4829,7 @@
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>29-01-2025</v>
+        <v>29-01-2026</v>
       </c>
       <c r="D95" t="str">
         <v>Sensex PE</v>
@@ -4834,13 +4838,13 @@
         <v>20</v>
       </c>
       <c r="F95">
-        <v>784</v>
+        <v>784.3</v>
       </c>
       <c r="G95">
         <v>690</v>
       </c>
       <c r="H95">
-        <v>-94</v>
+        <v>-94.3</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -4872,7 +4876,7 @@
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>30-01-2025</v>
+        <v>30-01-2026</v>
       </c>
       <c r="D96" t="str">
         <v>BankniftyPE</v>
@@ -4884,16 +4888,16 @@
         <v>509</v>
       </c>
       <c r="G96">
-        <v>494</v>
+        <v>493.85</v>
       </c>
       <c r="H96">
-        <v>-15</v>
+        <v>-15.15</v>
       </c>
       <c r="I96">
         <v>0</v>
       </c>
       <c r="J96">
-        <v>-454</v>
+        <v>-454.5</v>
       </c>
       <c r="K96">
         <v>25</v>
@@ -4905,7 +4909,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N96">
-        <v>-479</v>
+        <v>-479.5</v>
       </c>
       <c r="O96">
         <v>0</v>
@@ -4919,7 +4923,7 @@
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>05-02-2025</v>
+        <v>05-02-2026</v>
       </c>
       <c r="D97" t="str">
         <v>NiftyPE</v>
@@ -4928,16 +4932,16 @@
         <v>65</v>
       </c>
       <c r="F97">
-        <v>202</v>
+        <v>202.35</v>
       </c>
       <c r="G97">
-        <v>242</v>
+        <v>241.6</v>
       </c>
       <c r="H97">
-        <v>39</v>
+        <v>39.25</v>
       </c>
       <c r="I97">
-        <v>2551</v>
+        <v>2551.25</v>
       </c>
       <c r="J97">
         <v>0</v>
@@ -4952,7 +4956,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N97">
-        <v>2526</v>
+        <v>2526.25</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -4966,7 +4970,7 @@
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>05-02-2025</v>
+        <v>05-02-2026</v>
       </c>
       <c r="D98" t="str">
         <v>Sensex PE</v>
@@ -4975,13 +4979,13 @@
         <v>20</v>
       </c>
       <c r="F98">
-        <v>808</v>
+        <v>807.9</v>
       </c>
       <c r="G98">
-        <v>879</v>
+        <v>879.3</v>
       </c>
       <c r="H98">
-        <v>71</v>
+        <v>71.4</v>
       </c>
       <c r="I98">
         <v>1428</v>
@@ -5013,7 +5017,7 @@
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>06-02-2025</v>
+        <v>06-02-2026</v>
       </c>
       <c r="D99" t="str">
         <v>Sensex PE</v>
@@ -5022,13 +5026,13 @@
         <v>20</v>
       </c>
       <c r="F99">
-        <v>825</v>
+        <v>825.4</v>
       </c>
       <c r="G99">
-        <v>773</v>
+        <v>773.25</v>
       </c>
       <c r="H99">
-        <v>-52</v>
+        <v>-52.15</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -5060,7 +5064,7 @@
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>09-02-2025</v>
+        <v>09-02-2026</v>
       </c>
       <c r="D100" t="str">
         <v>NiftyCE</v>
@@ -5069,16 +5073,16 @@
         <v>65</v>
       </c>
       <c r="F100">
-        <v>205</v>
+        <v>204.85</v>
       </c>
       <c r="G100">
-        <v>241</v>
+        <v>241.15</v>
       </c>
       <c r="H100">
-        <v>36</v>
+        <v>36.3</v>
       </c>
       <c r="I100">
-        <v>2360</v>
+        <v>2359.5</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -5093,7 +5097,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N100">
-        <v>2335</v>
+        <v>2334.5</v>
       </c>
       <c r="O100">
         <v>0</v>
@@ -5107,7 +5111,7 @@
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>09-02-2025</v>
+        <v>09-02-2026</v>
       </c>
       <c r="D101" t="str">
         <v>BankniftyCE</v>
@@ -5116,19 +5120,19 @@
         <v>30</v>
       </c>
       <c r="F101">
-        <v>408</v>
+        <v>407.5</v>
       </c>
       <c r="G101">
-        <v>393</v>
+        <v>393.15</v>
       </c>
       <c r="H101">
-        <v>-14</v>
+        <v>-14.35</v>
       </c>
       <c r="I101">
         <v>0</v>
       </c>
       <c r="J101">
-        <v>-431</v>
+        <v>-430.5</v>
       </c>
       <c r="K101">
         <v>25</v>
@@ -5140,7 +5144,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N101">
-        <v>-456</v>
+        <v>-455.5</v>
       </c>
       <c r="O101">
         <v>0</v>
@@ -5154,7 +5158,7 @@
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>10-02-2025</v>
+        <v>10-02-2026</v>
       </c>
       <c r="D102" t="str">
         <v>NiftyCE</v>
@@ -5163,16 +5167,16 @@
         <v>65</v>
       </c>
       <c r="F102">
-        <v>203</v>
+        <v>203.3</v>
       </c>
       <c r="G102">
-        <v>205</v>
+        <v>204.95</v>
       </c>
       <c r="H102">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="I102">
-        <v>107</v>
+        <v>107.25</v>
       </c>
       <c r="J102">
         <v>0</v>
@@ -5187,7 +5191,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N102">
-        <v>82</v>
+        <v>82.25</v>
       </c>
       <c r="O102">
         <v>0</v>
@@ -5201,7 +5205,7 @@
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>10-02-2025</v>
+        <v>10-02-2026</v>
       </c>
       <c r="D103" t="str">
         <v>Sensex CE</v>
@@ -5210,13 +5214,13 @@
         <v>20</v>
       </c>
       <c r="F103">
-        <v>599</v>
+        <v>599.2</v>
       </c>
       <c r="G103">
-        <v>626</v>
+        <v>626.1</v>
       </c>
       <c r="H103">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="I103">
         <v>538</v>
@@ -5248,7 +5252,7 @@
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>10-02-2025</v>
+        <v>10-02-2026</v>
       </c>
       <c r="D104" t="str">
         <v>BankniftyPE</v>
@@ -5257,16 +5261,16 @@
         <v>30</v>
       </c>
       <c r="F104">
-        <v>516</v>
+        <v>516.2</v>
       </c>
       <c r="G104">
-        <v>543</v>
+        <v>543.05</v>
       </c>
       <c r="H104">
-        <v>27</v>
+        <v>26.85</v>
       </c>
       <c r="I104">
-        <v>805</v>
+        <v>805.5</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -5281,7 +5285,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N104">
-        <v>780</v>
+        <v>780.5</v>
       </c>
       <c r="O104">
         <v>0</v>
@@ -5295,7 +5299,7 @@
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>11-02-2025</v>
+        <v>11-02-2026</v>
       </c>
       <c r="D105" t="str">
         <v>BankniftyCE</v>
@@ -5304,13 +5308,13 @@
         <v>30</v>
       </c>
       <c r="F105">
-        <v>415</v>
+        <v>415.3</v>
       </c>
       <c r="G105">
-        <v>364</v>
+        <v>363.6</v>
       </c>
       <c r="H105">
-        <v>-52</v>
+        <v>-51.7</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -5342,7 +5346,7 @@
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>12-02-2025</v>
+        <v>12-02-2026</v>
       </c>
       <c r="D106" t="str">
         <v>Sensex PE</v>
@@ -5351,13 +5355,13 @@
         <v>20</v>
       </c>
       <c r="F106">
-        <v>780</v>
+        <v>780.45</v>
       </c>
       <c r="G106">
-        <v>819</v>
+        <v>819.4</v>
       </c>
       <c r="H106">
-        <v>39</v>
+        <v>38.95</v>
       </c>
       <c r="I106">
         <v>779</v>
@@ -5389,7 +5393,7 @@
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>12-02-2025</v>
+        <v>12-02-2026</v>
       </c>
       <c r="D107" t="str">
         <v>BankniftyPE</v>
@@ -5401,13 +5405,13 @@
         <v>486</v>
       </c>
       <c r="G107">
-        <v>497</v>
+        <v>497.15</v>
       </c>
       <c r="H107">
-        <v>11</v>
+        <v>11.15</v>
       </c>
       <c r="I107">
-        <v>334</v>
+        <v>334.5</v>
       </c>
       <c r="J107">
         <v>0</v>
@@ -5422,7 +5426,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N107">
-        <v>309</v>
+        <v>309.5</v>
       </c>
       <c r="O107">
         <v>0</v>
@@ -5436,7 +5440,7 @@
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>13-02-2025</v>
+        <v>13-02-2026</v>
       </c>
       <c r="D108" t="str">
         <v>Sensex PE</v>
@@ -5445,13 +5449,13 @@
         <v>20</v>
       </c>
       <c r="F108">
-        <v>818</v>
+        <v>817.85</v>
       </c>
       <c r="G108">
-        <v>925</v>
+        <v>924.9</v>
       </c>
       <c r="H108">
-        <v>107</v>
+        <v>107.05</v>
       </c>
       <c r="I108">
         <v>2141</v>
@@ -5483,7 +5487,7 @@
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>18-02-2025</v>
+        <v>18-02-2026</v>
       </c>
       <c r="D109" t="str">
         <v>Sensex PE</v>
@@ -5492,13 +5496,13 @@
         <v>20</v>
       </c>
       <c r="F109">
-        <v>681</v>
+        <v>681.1</v>
       </c>
       <c r="G109">
-        <v>581</v>
+        <v>580.75</v>
       </c>
       <c r="H109">
-        <v>-100</v>
+        <v>-100.35</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -5530,7 +5534,7 @@
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>18-02-2025</v>
+        <v>18-02-2026</v>
       </c>
       <c r="D110" t="str">
         <v>BankniftyCE</v>
@@ -5539,16 +5543,16 @@
         <v>30</v>
       </c>
       <c r="F110">
-        <v>375</v>
+        <v>375.25</v>
       </c>
       <c r="G110">
-        <v>418</v>
+        <v>418.08</v>
       </c>
       <c r="H110">
-        <v>43</v>
+        <v>42.83</v>
       </c>
       <c r="I110">
-        <v>1285</v>
+        <v>1284.9</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -5563,7 +5567,7 @@
         <v/>
       </c>
       <c r="N110">
-        <v>1257</v>
+        <v>1256.9</v>
       </c>
       <c r="O110">
         <v>0</v>
@@ -5577,7 +5581,7 @@
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>19-02-2025</v>
+        <v>19-02-2026</v>
       </c>
       <c r="D111" t="str">
         <v>Sensex PE</v>
@@ -5586,13 +5590,13 @@
         <v>20</v>
       </c>
       <c r="F111">
-        <v>717</v>
+        <v>717.05</v>
       </c>
       <c r="G111">
-        <v>958</v>
+        <v>958.45</v>
       </c>
       <c r="H111">
-        <v>241</v>
+        <v>241.4</v>
       </c>
       <c r="I111">
         <v>4828</v>
@@ -5624,7 +5628,7 @@
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>20-02-2025</v>
+        <v>20-02-2026</v>
       </c>
       <c r="D112" t="str">
         <v>BankniftyCE</v>
@@ -5633,19 +5637,19 @@
         <v>30</v>
       </c>
       <c r="F112">
-        <v>398</v>
+        <v>397.95</v>
       </c>
       <c r="G112">
         <v>343</v>
       </c>
       <c r="H112">
-        <v>-55</v>
+        <v>-54.95</v>
       </c>
       <c r="I112">
         <v>0</v>
       </c>
       <c r="J112">
-        <v>-1649</v>
+        <v>-1648.5</v>
       </c>
       <c r="K112">
         <v>28</v>
@@ -5657,7 +5661,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N112">
-        <v>-1677</v>
+        <v>-1676.5</v>
       </c>
       <c r="O112">
         <v>0</v>
@@ -5671,7 +5675,7 @@
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>24-02-2025</v>
+        <v>24-02-2026</v>
       </c>
       <c r="D113" t="str">
         <v>Sensex PE</v>
@@ -5680,13 +5684,13 @@
         <v>20</v>
       </c>
       <c r="F113">
-        <v>683</v>
+        <v>683.1</v>
       </c>
       <c r="G113">
         <v>828</v>
       </c>
       <c r="H113">
-        <v>145</v>
+        <v>144.9</v>
       </c>
       <c r="I113">
         <v>2898</v>
@@ -5695,7 +5699,7 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>27</v>
+        <v>26.54</v>
       </c>
       <c r="L113" t="str">
         <v>Yes</v>
@@ -5704,7 +5708,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N113">
-        <v>2871</v>
+        <v>2871.46</v>
       </c>
       <c r="O113">
         <v>0</v>
@@ -5718,7 +5722,7 @@
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>24-02-2025</v>
+        <v>24-02-2026</v>
       </c>
       <c r="D114" t="str">
         <v>NiftyPE</v>
@@ -5727,22 +5731,22 @@
         <v>65</v>
       </c>
       <c r="F114">
-        <v>208</v>
+        <v>207.6</v>
       </c>
       <c r="G114">
-        <v>244</v>
+        <v>244.3</v>
       </c>
       <c r="H114">
-        <v>37</v>
+        <v>36.7</v>
       </c>
       <c r="I114">
-        <v>2386</v>
+        <v>2385.5</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114">
-        <v>27</v>
+        <v>26.54</v>
       </c>
       <c r="L114" t="str">
         <v>Yes</v>
@@ -5751,7 +5755,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N114">
-        <v>2359</v>
+        <v>2358.96</v>
       </c>
       <c r="O114">
         <v>0</v>
@@ -5765,7 +5769,7 @@
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>25-02-2025</v>
+        <v>25-02-2026</v>
       </c>
       <c r="D115" t="str">
         <v>NiftyCE</v>
@@ -5774,13 +5778,13 @@
         <v>65</v>
       </c>
       <c r="F115">
-        <v>207</v>
+        <v>207.45</v>
       </c>
       <c r="G115">
-        <v>237</v>
+        <v>236.65</v>
       </c>
       <c r="H115">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="I115">
         <v>1898</v>
@@ -5789,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="K115">
-        <v>27</v>
+        <v>26.54</v>
       </c>
       <c r="L115" t="str">
         <v>Yes</v>
@@ -5798,7 +5802,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N115">
-        <v>1871</v>
+        <v>1871.46</v>
       </c>
       <c r="O115">
         <v>0</v>
@@ -5812,7 +5816,7 @@
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>25-02-2025</v>
+        <v>25-02-2026</v>
       </c>
       <c r="D116" t="str">
         <v>NiftyCE</v>
@@ -5821,22 +5825,22 @@
         <v>65</v>
       </c>
       <c r="F116">
-        <v>194</v>
+        <v>194.25</v>
       </c>
       <c r="G116">
-        <v>174</v>
+        <v>173.6</v>
       </c>
       <c r="H116">
-        <v>-21</v>
+        <v>-20.65</v>
       </c>
       <c r="I116">
         <v>0</v>
       </c>
       <c r="J116">
-        <v>-1342</v>
+        <v>-1342.25</v>
       </c>
       <c r="K116">
-        <v>27</v>
+        <v>26.54</v>
       </c>
       <c r="L116" t="str">
         <v>Yes</v>
@@ -5845,7 +5849,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N116">
-        <v>-1369</v>
+        <v>-1368.79</v>
       </c>
       <c r="O116">
         <v>0</v>
@@ -5859,7 +5863,7 @@
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>25-02-2025</v>
+        <v>25-02-2026</v>
       </c>
       <c r="D117" t="str">
         <v>NiftyPE</v>
@@ -5868,22 +5872,22 @@
         <v>65</v>
       </c>
       <c r="F117">
-        <v>199</v>
+        <v>198.9</v>
       </c>
       <c r="G117">
-        <v>240</v>
+        <v>240.2</v>
       </c>
       <c r="H117">
-        <v>41</v>
+        <v>41.3</v>
       </c>
       <c r="I117">
-        <v>2685</v>
+        <v>2684.5</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117">
-        <v>27</v>
+        <v>26.54</v>
       </c>
       <c r="L117" t="str">
         <v>Yes</v>
@@ -5892,7 +5896,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N117">
-        <v>2658</v>
+        <v>2657.96</v>
       </c>
       <c r="O117">
         <v>0</v>
@@ -5906,7 +5910,7 @@
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>27-02-2025</v>
+        <v>27-02-2026</v>
       </c>
       <c r="D118" t="str">
         <v>NiftyPE</v>
@@ -5915,13 +5919,13 @@
         <v>65</v>
       </c>
       <c r="F118">
-        <v>191</v>
+        <v>191.15</v>
       </c>
       <c r="G118">
-        <v>214</v>
+        <v>213.55</v>
       </c>
       <c r="H118">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="I118">
         <v>1456</v>
@@ -5930,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>27</v>
+        <v>26.54</v>
       </c>
       <c r="L118" t="str">
         <v>Yes</v>
@@ -5939,7 +5943,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N118">
-        <v>1429</v>
+        <v>1429.46</v>
       </c>
       <c r="O118">
         <v>0</v>
@@ -5953,7 +5957,7 @@
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>02-03-2025</v>
+        <v>02-03-2026</v>
       </c>
       <c r="D119" t="str">
         <v>NiftyPE</v>
@@ -5962,16 +5966,16 @@
         <v>65</v>
       </c>
       <c r="F119">
-        <v>202</v>
+        <v>201.8</v>
       </c>
       <c r="G119">
-        <v>240</v>
+        <v>240.15</v>
       </c>
       <c r="H119">
-        <v>38</v>
+        <v>38.35</v>
       </c>
       <c r="I119">
-        <v>4986</v>
+        <v>4985.5</v>
       </c>
       <c r="J119">
         <v>0</v>
@@ -5986,7 +5990,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N119">
-        <v>4959</v>
+        <v>4958.5</v>
       </c>
       <c r="O119">
         <v>0</v>
@@ -6000,7 +6004,7 @@
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>05-03-2025</v>
+        <v>05-03-2026</v>
       </c>
       <c r="D120" t="str">
         <v>NiftyCE</v>
@@ -6009,16 +6013,16 @@
         <v>65</v>
       </c>
       <c r="F120">
-        <v>188</v>
+        <v>187.65</v>
       </c>
       <c r="G120">
         <v>216</v>
       </c>
       <c r="H120">
-        <v>28</v>
+        <v>28.35</v>
       </c>
       <c r="I120">
-        <v>1843</v>
+        <v>1842.75</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -6033,7 +6037,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N120">
-        <v>1816</v>
+        <v>1815.75</v>
       </c>
       <c r="O120">
         <v>0</v>
@@ -6047,7 +6051,7 @@
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>11-03-2025</v>
+        <v>11-03-2026</v>
       </c>
       <c r="D121" t="str">
         <v>BankniftyPE</v>
@@ -6056,13 +6060,13 @@
         <v>30</v>
       </c>
       <c r="F121">
-        <v>495</v>
+        <v>494.5</v>
       </c>
       <c r="G121">
-        <v>598</v>
+        <v>597.7</v>
       </c>
       <c r="H121">
-        <v>103</v>
+        <v>103.2</v>
       </c>
       <c r="I121">
         <v>3096</v>
@@ -6071,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>32</v>
+        <v>32.34</v>
       </c>
       <c r="L121" t="str">
         <v>Yes</v>
@@ -6080,7 +6084,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N121">
-        <v>3064</v>
+        <v>3063.66</v>
       </c>
       <c r="O121">
         <v>0</v>
@@ -6094,7 +6098,7 @@
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>11-03-2025</v>
+        <v>11-03-2026</v>
       </c>
       <c r="D122" t="str">
         <v>Sensex PE</v>
@@ -6103,13 +6107,13 @@
         <v>20</v>
       </c>
       <c r="F122">
-        <v>705</v>
+        <v>704.5</v>
       </c>
       <c r="G122">
-        <v>817</v>
+        <v>816.95</v>
       </c>
       <c r="H122">
-        <v>112</v>
+        <v>112.45</v>
       </c>
       <c r="I122">
         <v>2249</v>
@@ -6118,7 +6122,7 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>30</v>
+        <v>29.73</v>
       </c>
       <c r="L122" t="str">
         <v>Yes</v>
@@ -6127,7 +6131,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N122">
-        <v>2219</v>
+        <v>2219.27</v>
       </c>
       <c r="O122">
         <v>0</v>
@@ -6141,7 +6145,7 @@
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>13-03-2025</v>
+        <v>13-03-2026</v>
       </c>
       <c r="D123" t="str">
         <v>BankniftyPE</v>
@@ -6150,13 +6154,13 @@
         <v>30</v>
       </c>
       <c r="F123">
-        <v>543</v>
+        <v>543.05</v>
       </c>
       <c r="G123">
-        <v>474</v>
+        <v>473.85</v>
       </c>
       <c r="H123">
-        <v>-69</v>
+        <v>-69.2</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -6188,7 +6192,7 @@
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>13-03-2025</v>
+        <v>13-03-2026</v>
       </c>
       <c r="D124" t="str">
         <v>Sensex PE</v>
@@ -6197,13 +6201,13 @@
         <v>20</v>
       </c>
       <c r="F124">
-        <v>711</v>
+        <v>710.55</v>
       </c>
       <c r="G124">
-        <v>712</v>
+        <v>711.8</v>
       </c>
       <c r="H124">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I124">
         <v>25</v>
@@ -6235,7 +6239,7 @@
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>18-03-2025</v>
+        <v>18-03-2026</v>
       </c>
       <c r="D125" t="str">
         <v>Sensex CE</v>
@@ -6244,13 +6248,13 @@
         <v>20</v>
       </c>
       <c r="F125">
-        <v>695</v>
+        <v>695.2</v>
       </c>
       <c r="G125">
-        <v>622</v>
+        <v>621.65</v>
       </c>
       <c r="H125">
-        <v>-74</v>
+        <v>-73.55</v>
       </c>
       <c r="I125">
         <v>0</v>
@@ -6282,7 +6286,7 @@
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>18-03-2025</v>
+        <v>18-03-2026</v>
       </c>
       <c r="D126" t="str">
         <v>BankniftyCE</v>
@@ -6291,19 +6295,19 @@
         <v>30</v>
       </c>
       <c r="F126">
-        <v>492</v>
+        <v>492.1</v>
       </c>
       <c r="G126">
-        <v>433</v>
+        <v>433.25</v>
       </c>
       <c r="H126">
-        <v>-59</v>
+        <v>-58.85</v>
       </c>
       <c r="I126">
         <v>0</v>
       </c>
       <c r="J126">
-        <v>-1766</v>
+        <v>-1765.5</v>
       </c>
       <c r="K126">
         <v>18</v>
@@ -6315,7 +6319,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N126">
-        <v>-1784</v>
+        <v>-1783.5</v>
       </c>
       <c r="O126">
         <v>0</v>
@@ -6329,7 +6333,7 @@
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>18-03-2025</v>
+        <v>18-03-2026</v>
       </c>
       <c r="D127" t="str">
         <v>NiftyCE</v>
@@ -6338,19 +6342,19 @@
         <v>65</v>
       </c>
       <c r="F127">
-        <v>213</v>
+        <v>212.5</v>
       </c>
       <c r="G127">
-        <v>183</v>
+        <v>183.4</v>
       </c>
       <c r="H127">
-        <v>-29</v>
+        <v>-29.1</v>
       </c>
       <c r="I127">
         <v>0</v>
       </c>
       <c r="J127">
-        <v>-1892</v>
+        <v>-1891.5</v>
       </c>
       <c r="K127">
         <v>20</v>
@@ -6362,7 +6366,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N127">
-        <v>-1912</v>
+        <v>-1911.5</v>
       </c>
       <c r="O127">
         <v>0</v>
@@ -6376,7 +6380,7 @@
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>19-03-2025</v>
+        <v>19-03-2026</v>
       </c>
       <c r="D128" t="str">
         <v>NiftyPE</v>
@@ -6385,16 +6389,16 @@
         <v>65</v>
       </c>
       <c r="F128">
-        <v>200</v>
+        <v>199.65</v>
       </c>
       <c r="G128">
-        <v>222</v>
+        <v>222.3</v>
       </c>
       <c r="H128">
-        <v>23</v>
+        <v>22.65</v>
       </c>
       <c r="I128">
-        <v>1472</v>
+        <v>1472.25</v>
       </c>
       <c r="J128">
         <v>0</v>
@@ -6409,7 +6413,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N128">
-        <v>1452</v>
+        <v>1452.25</v>
       </c>
       <c r="O128">
         <v>0</v>
@@ -6423,7 +6427,7 @@
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>23-03-2025</v>
+        <v>23-03-2026</v>
       </c>
       <c r="D129" t="str">
         <v>BankniftyPE</v>
@@ -6432,19 +6436,19 @@
         <v>30</v>
       </c>
       <c r="F129">
-        <v>526</v>
+        <v>526.2</v>
       </c>
       <c r="G129">
-        <v>457</v>
+        <v>456.85</v>
       </c>
       <c r="H129">
-        <v>-69</v>
+        <v>-69.35</v>
       </c>
       <c r="I129">
         <v>0</v>
       </c>
       <c r="J129">
-        <v>-2081</v>
+        <v>-2080.5</v>
       </c>
       <c r="K129">
         <v>20</v>
@@ -6456,7 +6460,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N129">
-        <v>-2101</v>
+        <v>-2100.5</v>
       </c>
       <c r="O129">
         <v>0</v>
@@ -6470,7 +6474,7 @@
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>25-03-2025</v>
+        <v>25-03-2026</v>
       </c>
       <c r="D130" t="str">
         <v>BankniftyCE</v>
@@ -6479,13 +6483,13 @@
         <v>30</v>
       </c>
       <c r="F130">
-        <v>504</v>
+        <v>504.1</v>
       </c>
       <c r="G130">
-        <v>534</v>
+        <v>534.4</v>
       </c>
       <c r="H130">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="I130">
         <v>909</v>
@@ -6517,7 +6521,7 @@
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>25-03-2025</v>
+        <v>25-03-2026</v>
       </c>
       <c r="D131" t="str">
         <v>NiftyCE</v>
@@ -6526,16 +6530,16 @@
         <v>65</v>
       </c>
       <c r="F131">
-        <v>193</v>
+        <v>192.5</v>
       </c>
       <c r="G131">
-        <v>223</v>
+        <v>222.6</v>
       </c>
       <c r="H131">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="I131">
-        <v>1957</v>
+        <v>1956.5</v>
       </c>
       <c r="J131">
         <v>0</v>
@@ -6550,7 +6554,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N131">
-        <v>1930</v>
+        <v>1929.5</v>
       </c>
       <c r="O131">
         <v>0</v>
@@ -6564,7 +6568,7 @@
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>25-03-2025</v>
+        <v>25-03-2026</v>
       </c>
       <c r="D132" t="str">
         <v>Sensex CE</v>
@@ -6576,10 +6580,10 @@
         <v>664</v>
       </c>
       <c r="G132">
-        <v>821</v>
+        <v>820.95</v>
       </c>
       <c r="H132">
-        <v>157</v>
+        <v>156.95</v>
       </c>
       <c r="I132">
         <v>3139</v>
@@ -6611,7 +6615,7 @@
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>27-03-2025</v>
+        <v>27-03-2026</v>
       </c>
       <c r="D133" t="str">
         <v>BankniftyPE</v>
@@ -6620,13 +6624,13 @@
         <v>30</v>
       </c>
       <c r="F133">
-        <v>528</v>
+        <v>528.2</v>
       </c>
       <c r="G133">
-        <v>459</v>
+        <v>458.8</v>
       </c>
       <c r="H133">
-        <v>-69</v>
+        <v>-69.4</v>
       </c>
       <c r="I133">
         <v>0</v>
@@ -6658,7 +6662,7 @@
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>08-04-2025</v>
+        <v>08-04-2026</v>
       </c>
       <c r="D134" t="str">
         <v>BankniftyCE</v>
@@ -6667,19 +6671,19 @@
         <v>60</v>
       </c>
       <c r="F134">
-        <v>484</v>
+        <v>484.27</v>
       </c>
       <c r="G134">
-        <v>430</v>
+        <v>430.15</v>
       </c>
       <c r="H134">
-        <v>-54</v>
+        <v>-54.12</v>
       </c>
       <c r="I134">
         <v>0</v>
       </c>
       <c r="J134">
-        <v>-3247</v>
+        <v>-3247.2</v>
       </c>
       <c r="K134">
         <v>105</v>
@@ -6691,7 +6695,7 @@
         <v>2 Lot 1L invested</v>
       </c>
       <c r="N134">
-        <v>-3352</v>
+        <v>-3352.2</v>
       </c>
       <c r="O134">
         <v>0</v>
@@ -6705,7 +6709,7 @@
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>10-04-2025</v>
+        <v>10-04-2026</v>
       </c>
       <c r="D135" t="str">
         <v>NiftyCE</v>
@@ -6714,19 +6718,19 @@
         <v>130</v>
       </c>
       <c r="F135">
-        <v>188</v>
+        <v>188.25</v>
       </c>
       <c r="G135">
-        <v>159</v>
+        <v>159.1</v>
       </c>
       <c r="H135">
-        <v>-29</v>
+        <v>-29.15</v>
       </c>
       <c r="I135">
         <v>0</v>
       </c>
       <c r="J135">
-        <v>-3790</v>
+        <v>-3789.5</v>
       </c>
       <c r="K135">
         <v>102</v>
@@ -6738,7 +6742,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N135">
-        <v>-3892</v>
+        <v>-3891.5</v>
       </c>
       <c r="O135">
         <v>0</v>
@@ -6752,7 +6756,7 @@
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>16-04-2025</v>
+        <v>16-04-2026</v>
       </c>
       <c r="D136" t="str">
         <v>NiftyCE</v>
@@ -6761,19 +6765,19 @@
         <v>130</v>
       </c>
       <c r="F136">
-        <v>206</v>
+        <v>205.85</v>
       </c>
       <c r="G136">
-        <v>169</v>
+        <v>168.8</v>
       </c>
       <c r="H136">
-        <v>-37</v>
+        <v>-37.05</v>
       </c>
       <c r="I136">
         <v>0</v>
       </c>
       <c r="J136">
-        <v>-4817</v>
+        <v>-4816.5</v>
       </c>
       <c r="K136">
         <v>100</v>
@@ -6785,7 +6789,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N136">
-        <v>-4917</v>
+        <v>-4916.5</v>
       </c>
       <c r="O136">
         <v>0</v>
@@ -6799,7 +6803,7 @@
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>16-04-2025</v>
+        <v>16-04-2026</v>
       </c>
       <c r="D137" t="str">
         <v>NiftyPE</v>
@@ -6808,16 +6812,16 @@
         <v>130</v>
       </c>
       <c r="F137">
-        <v>203</v>
+        <v>203.15</v>
       </c>
       <c r="G137">
-        <v>218</v>
+        <v>217.6</v>
       </c>
       <c r="H137">
-        <v>14</v>
+        <v>14.45</v>
       </c>
       <c r="I137">
-        <v>1879</v>
+        <v>1878.5</v>
       </c>
       <c r="J137">
         <v>0</v>
@@ -6832,7 +6836,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N137">
-        <v>1799</v>
+        <v>1798.5</v>
       </c>
       <c r="O137">
         <v>0</v>
@@ -6846,7 +6850,7 @@
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>16-04-2025</v>
+        <v>16-04-2026</v>
       </c>
       <c r="D138" t="str">
         <v>Sensex CE</v>
@@ -6855,13 +6859,13 @@
         <v>40</v>
       </c>
       <c r="F138">
-        <v>597</v>
+        <v>597.1</v>
       </c>
       <c r="G138">
         <v>480</v>
       </c>
       <c r="H138">
-        <v>-117</v>
+        <v>-117.1</v>
       </c>
       <c r="I138">
         <v>0</v>
@@ -6893,7 +6897,7 @@
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>16-04-2025</v>
+        <v>16-04-2026</v>
       </c>
       <c r="D139" t="str">
         <v>Sensex PE</v>
@@ -6902,13 +6906,13 @@
         <v>40</v>
       </c>
       <c r="F139">
-        <v>716</v>
+        <v>716.2</v>
       </c>
       <c r="G139">
-        <v>813</v>
+        <v>813.35</v>
       </c>
       <c r="H139">
-        <v>97</v>
+        <v>97.15</v>
       </c>
       <c r="I139">
         <v>3886</v>
@@ -6940,7 +6944,7 @@
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>16-04-2025</v>
+        <v>16-04-2026</v>
       </c>
       <c r="D140" t="str">
         <v>NiftyBullCE</v>
@@ -6949,19 +6953,19 @@
         <v>65</v>
       </c>
       <c r="F140">
-        <v>264</v>
+        <v>263.75</v>
       </c>
       <c r="G140">
-        <v>224</v>
+        <v>223.6</v>
       </c>
       <c r="H140">
-        <v>-40</v>
+        <v>-40.15</v>
       </c>
       <c r="I140">
         <v>0</v>
       </c>
       <c r="J140">
-        <v>-2610</v>
+        <v>-2609.75</v>
       </c>
       <c r="K140">
         <v>100</v>
@@ -6973,7 +6977,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N140">
-        <v>-2710</v>
+        <v>-2709.75</v>
       </c>
       <c r="O140">
         <v>0</v>
@@ -6987,7 +6991,7 @@
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>16-04-2025</v>
+        <v>16-04-2026</v>
       </c>
       <c r="D141" t="str">
         <v>NiftyBullPE</v>
@@ -6996,16 +7000,16 @@
         <v>65</v>
       </c>
       <c r="F141">
-        <v>256</v>
+        <v>255.5</v>
       </c>
       <c r="G141">
-        <v>286</v>
+        <v>285.55</v>
       </c>
       <c r="H141">
-        <v>30</v>
+        <v>30.05</v>
       </c>
       <c r="I141">
-        <v>1953</v>
+        <v>1953.25</v>
       </c>
       <c r="J141">
         <v>0</v>
@@ -7020,7 +7024,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N141">
-        <v>1853</v>
+        <v>1853.25</v>
       </c>
       <c r="O141">
         <v>0</v>
@@ -7034,7 +7038,7 @@
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>17-04-2025</v>
+        <v>17-04-2026</v>
       </c>
       <c r="D142" t="str">
         <v>NiftyCE</v>
@@ -7046,10 +7050,10 @@
         <v>190</v>
       </c>
       <c r="G142">
-        <v>178</v>
+        <v>177.9</v>
       </c>
       <c r="H142">
-        <v>-12</v>
+        <v>-12.1</v>
       </c>
       <c r="I142">
         <v>0</v>
@@ -7081,7 +7085,7 @@
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>17-04-2025</v>
+        <v>17-04-2026</v>
       </c>
       <c r="D143" t="str">
         <v>NiftyBullCE</v>
@@ -7090,19 +7094,19 @@
         <v>65</v>
       </c>
       <c r="F143">
-        <v>252</v>
+        <v>252.15</v>
       </c>
       <c r="G143">
-        <v>238</v>
+        <v>237.9</v>
       </c>
       <c r="H143">
-        <v>-14</v>
+        <v>-14.25</v>
       </c>
       <c r="I143">
         <v>0</v>
       </c>
       <c r="J143">
-        <v>-926</v>
+        <v>-926.25</v>
       </c>
       <c r="K143">
         <v>100</v>
@@ -7114,7 +7118,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N143">
-        <v>-1026</v>
+        <v>-1026.25</v>
       </c>
       <c r="O143">
         <v>0</v>
@@ -7128,7 +7132,7 @@
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>20-04-2025</v>
+        <v>20-04-2026</v>
       </c>
       <c r="D144" t="str">
         <v>SensexBullCE</v>
@@ -7140,10 +7144,10 @@
         <v>684</v>
       </c>
       <c r="G144">
-        <v>676</v>
+        <v>675.6</v>
       </c>
       <c r="H144">
-        <v>-8</v>
+        <v>-8.4</v>
       </c>
       <c r="I144">
         <v>0</v>
@@ -7175,7 +7179,7 @@
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>20-04-2025</v>
+        <v>20-04-2026</v>
       </c>
       <c r="D145" t="str">
         <v>NiftyBullPE</v>
@@ -7184,19 +7188,19 @@
         <v>65</v>
       </c>
       <c r="F145">
-        <v>254</v>
+        <v>254.2</v>
       </c>
       <c r="G145">
-        <v>219</v>
+        <v>219.05</v>
       </c>
       <c r="H145">
-        <v>-35</v>
+        <v>-35.15</v>
       </c>
       <c r="I145">
         <v>0</v>
       </c>
       <c r="J145">
-        <v>-2285</v>
+        <v>-2284.75</v>
       </c>
       <c r="K145">
         <v>100</v>
@@ -7208,7 +7212,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N145">
-        <v>-2385</v>
+        <v>-2384.75</v>
       </c>
       <c r="O145">
         <v>0</v>
@@ -7222,7 +7226,7 @@
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>20-04-2025</v>
+        <v>20-04-2026</v>
       </c>
       <c r="D146" t="str">
         <v>BankniftyPE</v>
@@ -7234,10 +7238,10 @@
         <v>830</v>
       </c>
       <c r="G146">
-        <v>932</v>
+        <v>931.9</v>
       </c>
       <c r="H146">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="I146">
         <v>6114</v>
@@ -7269,7 +7273,7 @@
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>20-04-2025</v>
+        <v>20-04-2026</v>
       </c>
       <c r="D147" t="str">
         <v>BankniftyCE</v>
@@ -7278,13 +7282,13 @@
         <v>60</v>
       </c>
       <c r="F147">
-        <v>780</v>
+        <v>779.8</v>
       </c>
       <c r="G147">
-        <v>724</v>
+        <v>724.05</v>
       </c>
       <c r="H147">
-        <v>-56</v>
+        <v>-55.75</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -7316,7 +7320,7 @@
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>21-04-2025</v>
+        <v>21-04-2026</v>
       </c>
       <c r="D148" t="str">
         <v>Sensex CE</v>
@@ -7325,13 +7329,13 @@
         <v>40</v>
       </c>
       <c r="F148">
-        <v>584</v>
+        <v>584.25</v>
       </c>
       <c r="G148">
-        <v>628</v>
+        <v>627.75</v>
       </c>
       <c r="H148">
-        <v>44</v>
+        <v>43.5</v>
       </c>
       <c r="I148">
         <v>1740</v>
@@ -7363,7 +7367,7 @@
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>21-04-2025</v>
+        <v>21-04-2026</v>
       </c>
       <c r="D149" t="str">
         <v>SensexBullCE</v>
@@ -7372,13 +7376,13 @@
         <v>20</v>
       </c>
       <c r="F149">
-        <v>703</v>
+        <v>702.5</v>
       </c>
       <c r="G149">
-        <v>683</v>
+        <v>682.9</v>
       </c>
       <c r="H149">
-        <v>-20</v>
+        <v>-19.6</v>
       </c>
       <c r="I149">
         <v>0</v>
@@ -7410,7 +7414,7 @@
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>22-04-2025</v>
+        <v>22-04-2026</v>
       </c>
       <c r="D150" t="str">
         <v>NiftyBullPE</v>
@@ -7419,16 +7423,16 @@
         <v>65</v>
       </c>
       <c r="F150">
-        <v>249</v>
+        <v>249.35</v>
       </c>
       <c r="G150">
         <v>296</v>
       </c>
       <c r="H150">
-        <v>47</v>
+        <v>46.65</v>
       </c>
       <c r="I150">
-        <v>3032</v>
+        <v>3032.25</v>
       </c>
       <c r="J150">
         <v>0</v>
@@ -7443,7 +7447,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N150">
-        <v>2932</v>
+        <v>2932.25</v>
       </c>
       <c r="O150">
         <v>0</v>
@@ -7457,7 +7461,7 @@
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>22-04-2025</v>
+        <v>22-04-2026</v>
       </c>
       <c r="D151" t="str">
         <v>NiftyPE</v>
@@ -7466,13 +7470,13 @@
         <v>130</v>
       </c>
       <c r="F151">
-        <v>201</v>
+        <v>200.75</v>
       </c>
       <c r="G151">
-        <v>237</v>
+        <v>237.15</v>
       </c>
       <c r="H151">
-        <v>36</v>
+        <v>36.4</v>
       </c>
       <c r="I151">
         <v>4732</v>
@@ -7504,7 +7508,7 @@
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>23-04-2025</v>
+        <v>23-04-2026</v>
       </c>
       <c r="D152" t="str">
         <v>NiftyPE</v>
@@ -7513,13 +7517,13 @@
         <v>130</v>
       </c>
       <c r="F152">
-        <v>192</v>
+        <v>191.5</v>
       </c>
       <c r="G152">
-        <v>161</v>
+        <v>160.7</v>
       </c>
       <c r="H152">
-        <v>-31</v>
+        <v>-30.8</v>
       </c>
       <c r="I152">
         <v>0</v>
@@ -7551,7 +7555,7 @@
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>23-04-2025</v>
+        <v>23-04-2026</v>
       </c>
       <c r="D153" t="str">
         <v>NiftyBullPE</v>
@@ -7560,19 +7564,19 @@
         <v>65</v>
       </c>
       <c r="F153">
-        <v>239</v>
+        <v>238.5</v>
       </c>
       <c r="G153">
-        <v>203</v>
+        <v>203.45</v>
       </c>
       <c r="H153">
-        <v>-35</v>
+        <v>-35.05</v>
       </c>
       <c r="I153">
         <v>0</v>
       </c>
       <c r="J153">
-        <v>-2278</v>
+        <v>-2278.25</v>
       </c>
       <c r="K153">
         <v>90</v>
@@ -7584,7 +7588,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N153">
-        <v>-2368</v>
+        <v>-2368.25</v>
       </c>
       <c r="O153">
         <v>0</v>
@@ -7598,7 +7602,7 @@
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>28-04-2025</v>
+        <v>28-04-2026</v>
       </c>
       <c r="D154" t="str">
         <v>NiftyPE</v>
@@ -7607,19 +7611,19 @@
         <v>130</v>
       </c>
       <c r="F154">
-        <v>208</v>
+        <v>207.95</v>
       </c>
       <c r="G154">
         <v>171</v>
       </c>
       <c r="H154">
-        <v>-37</v>
+        <v>-36.95</v>
       </c>
       <c r="I154">
         <v>0</v>
       </c>
       <c r="J154">
-        <v>-4804</v>
+        <v>-4803.5</v>
       </c>
       <c r="K154">
         <v>90</v>
@@ -7631,7 +7635,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N154">
-        <v>-4894</v>
+        <v>-4893.5</v>
       </c>
       <c r="O154">
         <v>0</v>
@@ -7645,7 +7649,7 @@
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>28-04-2025</v>
+        <v>28-04-2026</v>
       </c>
       <c r="D155" t="str">
         <v>BankniftyPE</v>
@@ -7654,19 +7658,19 @@
         <v>60</v>
       </c>
       <c r="F155">
-        <v>522</v>
+        <v>521.87</v>
       </c>
       <c r="G155">
-        <v>452</v>
+        <v>452.05</v>
       </c>
       <c r="H155">
-        <v>-70</v>
+        <v>-69.82</v>
       </c>
       <c r="I155">
         <v>0</v>
       </c>
       <c r="J155">
-        <v>-4189</v>
+        <v>-4189.2</v>
       </c>
       <c r="K155">
         <v>90</v>
@@ -7678,7 +7682,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N155">
-        <v>-4279</v>
+        <v>-4279.2</v>
       </c>
       <c r="O155">
         <v>0</v>
@@ -7692,7 +7696,7 @@
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>28-04-2025</v>
+        <v>28-04-2026</v>
       </c>
       <c r="D156" t="str">
         <v>NiftyBullPE</v>
@@ -7701,13 +7705,13 @@
         <v>65</v>
       </c>
       <c r="F156">
-        <v>256</v>
+        <v>256.4</v>
       </c>
       <c r="G156">
         <v>221</v>
       </c>
       <c r="H156">
-        <v>-35</v>
+        <v>-35.4</v>
       </c>
       <c r="I156">
         <v>0</v>
@@ -7739,7 +7743,7 @@
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>28-04-2025</v>
+        <v>28-04-2026</v>
       </c>
       <c r="D157" t="str">
         <v>SensexBullPE</v>
@@ -7748,13 +7752,13 @@
         <v>20</v>
       </c>
       <c r="F157">
-        <v>722</v>
+        <v>722.25</v>
       </c>
       <c r="G157">
         <v>622</v>
       </c>
       <c r="H157">
-        <v>-100</v>
+        <v>-100.25</v>
       </c>
       <c r="I157">
         <v>0</v>
@@ -7786,7 +7790,7 @@
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>29-04-2025</v>
+        <v>29-04-2026</v>
       </c>
       <c r="D158" t="str">
         <v>NiftyCE</v>
@@ -7795,13 +7799,13 @@
         <v>130</v>
       </c>
       <c r="F158">
-        <v>199</v>
+        <v>198.6</v>
       </c>
       <c r="G158">
         <v>273</v>
       </c>
       <c r="H158">
-        <v>74</v>
+        <v>74.4</v>
       </c>
       <c r="I158">
         <v>9672</v>
@@ -7833,7 +7837,7 @@
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>29-04-2025</v>
+        <v>29-04-2026</v>
       </c>
       <c r="D159" t="str">
         <v>Sensex CE</v>
@@ -7845,10 +7849,10 @@
         <v>600</v>
       </c>
       <c r="G159">
-        <v>699</v>
+        <v>699.35</v>
       </c>
       <c r="H159">
-        <v>99</v>
+        <v>99.35</v>
       </c>
       <c r="I159">
         <v>3974</v>
@@ -7880,7 +7884,7 @@
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>29-04-2025</v>
+        <v>29-04-2026</v>
       </c>
       <c r="D160" t="str">
         <v>NiftyBullCE</v>
@@ -7889,16 +7893,16 @@
         <v>65</v>
       </c>
       <c r="F160">
-        <v>257</v>
+        <v>256.5</v>
       </c>
       <c r="G160">
-        <v>367</v>
+        <v>366.85</v>
       </c>
       <c r="H160">
-        <v>110</v>
+        <v>110.35</v>
       </c>
       <c r="I160">
-        <v>7173</v>
+        <v>7172.75</v>
       </c>
       <c r="J160">
         <v>0</v>
@@ -7913,7 +7917,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N160">
-        <v>7073</v>
+        <v>7072.75</v>
       </c>
       <c r="O160">
         <v>0</v>
@@ -7927,7 +7931,7 @@
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>29-04-2025</v>
+        <v>29-04-2026</v>
       </c>
       <c r="D161" t="str">
         <v>SensexBullCE</v>
@@ -7936,13 +7940,13 @@
         <v>20</v>
       </c>
       <c r="F161">
-        <v>675</v>
+        <v>675.2</v>
       </c>
       <c r="G161">
         <v>960</v>
       </c>
       <c r="H161">
-        <v>285</v>
+        <v>284.8</v>
       </c>
       <c r="I161">
         <v>5696</v>
@@ -7974,7 +7978,7 @@
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>30-04-2025</v>
+        <v>30-04-2026</v>
       </c>
       <c r="D162" t="str">
         <v>SensexBullPE</v>
@@ -7983,13 +7987,13 @@
         <v>20</v>
       </c>
       <c r="F162">
-        <v>746</v>
+        <v>745.85</v>
       </c>
       <c r="G162">
-        <v>639</v>
+        <v>639.3</v>
       </c>
       <c r="H162">
-        <v>-107</v>
+        <v>-106.55</v>
       </c>
       <c r="I162">
         <v>0</v>
@@ -8021,7 +8025,7 @@
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>30-04-2025</v>
+        <v>30-04-2026</v>
       </c>
       <c r="D163" t="str">
         <v>NiftyBullPE</v>
@@ -8030,19 +8034,19 @@
         <v>65</v>
       </c>
       <c r="F163">
-        <v>251</v>
+        <v>250.7</v>
       </c>
       <c r="G163">
-        <v>216</v>
+        <v>215.8</v>
       </c>
       <c r="H163">
-        <v>-35</v>
+        <v>-34.9</v>
       </c>
       <c r="I163">
         <v>0</v>
       </c>
       <c r="J163">
-        <v>-2269</v>
+        <v>-2268.5</v>
       </c>
       <c r="K163">
         <v>100</v>
@@ -8054,7 +8058,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N163">
-        <v>-2369</v>
+        <v>-2368.5</v>
       </c>
       <c r="O163">
         <v>0</v>
@@ -8068,7 +8072,7 @@
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>30-04-2025</v>
+        <v>30-04-2026</v>
       </c>
       <c r="D164" t="str">
         <v>Sensex PE</v>
@@ -8077,13 +8081,13 @@
         <v>40</v>
       </c>
       <c r="F164">
-        <v>750</v>
+        <v>749.95</v>
       </c>
       <c r="G164">
-        <v>655</v>
+        <v>655.05</v>
       </c>
       <c r="H164">
-        <v>-95</v>
+        <v>-94.9</v>
       </c>
       <c r="I164">
         <v>0</v>
@@ -8115,7 +8119,7 @@
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>30-04-2025</v>
+        <v>30-04-2026</v>
       </c>
       <c r="D165" t="str">
         <v>Sensex PE</v>
@@ -8124,13 +8128,13 @@
         <v>40</v>
       </c>
       <c r="F165">
-        <v>734</v>
+        <v>734.2</v>
       </c>
       <c r="G165">
-        <v>796</v>
+        <v>795.75</v>
       </c>
       <c r="H165">
-        <v>62</v>
+        <v>61.55</v>
       </c>
       <c r="I165">
         <v>2462</v>
@@ -8162,7 +8166,7 @@
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>30-04-2025</v>
+        <v>30-04-2026</v>
       </c>
       <c r="D166" t="str">
         <v>NiftyPE</v>
@@ -8171,19 +8175,19 @@
         <v>130</v>
       </c>
       <c r="F166">
-        <v>198</v>
+        <v>197.7</v>
       </c>
       <c r="G166">
-        <v>186</v>
+        <v>186.35</v>
       </c>
       <c r="H166">
-        <v>-11</v>
+        <v>-11.35</v>
       </c>
       <c r="I166">
         <v>0</v>
       </c>
       <c r="J166">
-        <v>-1476</v>
+        <v>-1475.5</v>
       </c>
       <c r="K166">
         <v>100</v>
@@ -8195,7 +8199,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N166">
-        <v>-1576</v>
+        <v>-1575.5</v>
       </c>
       <c r="O166">
         <v>0</v>
@@ -8209,7 +8213,7 @@
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>04-05-2025</v>
+        <v>04-05-2026</v>
       </c>
       <c r="D167" t="str">
         <v>SensexBullCE</v>
@@ -8218,13 +8222,13 @@
         <v>20</v>
       </c>
       <c r="F167">
-        <v>695</v>
+        <v>694.5</v>
       </c>
       <c r="G167">
         <v>594</v>
       </c>
       <c r="H167">
-        <v>-101</v>
+        <v>-100.5</v>
       </c>
       <c r="I167">
         <v>0</v>
@@ -8256,7 +8260,7 @@
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>04-05-2025</v>
+        <v>04-05-2026</v>
       </c>
       <c r="D168" t="str">
         <v>NiftyBullCE</v>
@@ -8265,19 +8269,19 @@
         <v>65</v>
       </c>
       <c r="F168">
-        <v>258</v>
+        <v>258.4</v>
       </c>
       <c r="G168">
-        <v>217</v>
+        <v>216.55</v>
       </c>
       <c r="H168">
-        <v>-42</v>
+        <v>-41.85</v>
       </c>
       <c r="I168">
         <v>0</v>
       </c>
       <c r="J168">
-        <v>-2720</v>
+        <v>-2720.25</v>
       </c>
       <c r="K168">
         <v>100</v>
@@ -8289,7 +8293,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N168">
-        <v>-2820</v>
+        <v>-2820.25</v>
       </c>
       <c r="O168">
         <v>0</v>
@@ -8303,7 +8307,7 @@
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>04-05-2025</v>
+        <v>04-05-2026</v>
       </c>
       <c r="D169" t="str">
         <v>BankniftyPE</v>
@@ -8312,13 +8316,13 @@
         <v>60</v>
       </c>
       <c r="F169">
-        <v>508</v>
+        <v>507.95</v>
       </c>
       <c r="G169">
-        <v>604</v>
+        <v>604.25</v>
       </c>
       <c r="H169">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="I169">
         <v>5778</v>
@@ -8350,7 +8354,7 @@
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>04-05-2025</v>
+        <v>04-05-2026</v>
       </c>
       <c r="D170" t="str">
         <v>BankniftyCE</v>
@@ -8359,13 +8363,13 @@
         <v>60</v>
       </c>
       <c r="F170">
-        <v>510</v>
+        <v>509.95</v>
       </c>
       <c r="G170">
-        <v>493</v>
+        <v>492.9</v>
       </c>
       <c r="H170">
-        <v>-17</v>
+        <v>-17.05</v>
       </c>
       <c r="I170">
         <v>0</v>
@@ -8397,7 +8401,7 @@
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>05-05-2025</v>
+        <v>05-05-2026</v>
       </c>
       <c r="D171" t="str">
         <v>SensexBullPE</v>
@@ -8406,13 +8410,13 @@
         <v>20</v>
       </c>
       <c r="F171">
-        <v>719</v>
+        <v>718.7</v>
       </c>
       <c r="G171">
-        <v>615</v>
+        <v>615.1</v>
       </c>
       <c r="H171">
-        <v>-104</v>
+        <v>-103.6</v>
       </c>
       <c r="I171">
         <v>0</v>
@@ -8444,7 +8448,7 @@
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>05-05-2025</v>
+        <v>05-05-2026</v>
       </c>
       <c r="D172" t="str">
         <v>NiftyBullPE</v>
@@ -8453,13 +8457,13 @@
         <v>65</v>
       </c>
       <c r="F172">
-        <v>271</v>
+        <v>270.8</v>
       </c>
       <c r="G172">
         <v>235</v>
       </c>
       <c r="H172">
-        <v>-36</v>
+        <v>-35.8</v>
       </c>
       <c r="I172">
         <v>0</v>
@@ -8491,7 +8495,7 @@
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>05-05-2025</v>
+        <v>05-05-2026</v>
       </c>
       <c r="D173" t="str">
         <v>Sensex PE</v>
@@ -8500,13 +8504,13 @@
         <v>40</v>
       </c>
       <c r="F173">
-        <v>717</v>
+        <v>717.25</v>
       </c>
       <c r="G173">
-        <v>622</v>
+        <v>621.6</v>
       </c>
       <c r="H173">
-        <v>-96</v>
+        <v>-95.65</v>
       </c>
       <c r="I173">
         <v>0</v>
@@ -8538,7 +8542,7 @@
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>05-05-2025</v>
+        <v>05-05-2026</v>
       </c>
       <c r="D174" t="str">
         <v>NiftyPE</v>
@@ -8547,19 +8551,19 @@
         <v>130</v>
       </c>
       <c r="F174">
-        <v>183</v>
+        <v>182.6</v>
       </c>
       <c r="G174">
-        <v>147</v>
+        <v>147.35</v>
       </c>
       <c r="H174">
-        <v>-35</v>
+        <v>-35.25</v>
       </c>
       <c r="I174">
         <v>0</v>
       </c>
       <c r="J174">
-        <v>-4583</v>
+        <v>-4582.5</v>
       </c>
       <c r="K174">
         <v>100</v>
@@ -8571,7 +8575,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N174">
-        <v>-4683</v>
+        <v>-4682.5</v>
       </c>
       <c r="O174">
         <v>0</v>
@@ -8585,7 +8589,7 @@
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>06-05-2025</v>
+        <v>06-05-2026</v>
       </c>
       <c r="D175" t="str">
         <v>SensexBullCE</v>
@@ -8594,13 +8598,13 @@
         <v>20</v>
       </c>
       <c r="F175">
-        <v>738</v>
+        <v>738.35</v>
       </c>
       <c r="G175">
-        <v>637</v>
+        <v>637.45</v>
       </c>
       <c r="H175">
-        <v>-101</v>
+        <v>-100.9</v>
       </c>
       <c r="I175">
         <v>0</v>
@@ -8632,7 +8636,7 @@
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>06-05-2025</v>
+        <v>06-05-2026</v>
       </c>
       <c r="D176" t="str">
         <v>SensexBullPE</v>
@@ -8641,13 +8645,13 @@
         <v>20</v>
       </c>
       <c r="F176">
-        <v>589</v>
+        <v>589.25</v>
       </c>
       <c r="G176">
-        <v>489</v>
+        <v>488.5</v>
       </c>
       <c r="H176">
-        <v>-101</v>
+        <v>-100.75</v>
       </c>
       <c r="I176">
         <v>0</v>
@@ -8679,7 +8683,7 @@
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>06-05-2025</v>
+        <v>06-05-2026</v>
       </c>
       <c r="D177" t="str">
         <v>NiftyBullCE</v>
@@ -8688,13 +8692,13 @@
         <v>65</v>
       </c>
       <c r="F177">
-        <v>239</v>
+        <v>238.5</v>
       </c>
       <c r="G177">
-        <v>222</v>
+        <v>222.3</v>
       </c>
       <c r="H177">
-        <v>-16</v>
+        <v>-16.2</v>
       </c>
       <c r="I177">
         <v>0</v>
@@ -8726,7 +8730,7 @@
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>06-05-2025</v>
+        <v>06-05-2026</v>
       </c>
       <c r="D178" t="str">
         <v>NiftyBullCE</v>
@@ -8735,16 +8739,16 @@
         <v>65</v>
       </c>
       <c r="F178">
-        <v>254</v>
+        <v>253.5</v>
       </c>
       <c r="G178">
-        <v>399</v>
+        <v>399.15</v>
       </c>
       <c r="H178">
-        <v>146</v>
+        <v>145.65</v>
       </c>
       <c r="I178">
-        <v>9467</v>
+        <v>9467.25</v>
       </c>
       <c r="J178">
         <v>0</v>
@@ -8759,7 +8763,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N178">
-        <v>9367</v>
+        <v>9367.25</v>
       </c>
       <c r="O178">
         <v>0</v>
@@ -8773,7 +8777,7 @@
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>06-05-2025</v>
+        <v>06-05-2026</v>
       </c>
       <c r="D179" t="str">
         <v>BankniftyCE</v>
@@ -8782,19 +8786,19 @@
         <v>60</v>
       </c>
       <c r="F179">
-        <v>527</v>
+        <v>527.05</v>
       </c>
       <c r="G179">
-        <v>480</v>
+        <v>480.12</v>
       </c>
       <c r="H179">
-        <v>-47</v>
+        <v>-46.93</v>
       </c>
       <c r="I179">
         <v>0</v>
       </c>
       <c r="J179">
-        <v>-2816</v>
+        <v>-2815.8</v>
       </c>
       <c r="K179">
         <v>100</v>
@@ -8806,7 +8810,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N179">
-        <v>-2916</v>
+        <v>-2915.8</v>
       </c>
       <c r="O179">
         <v>0</v>
@@ -8820,7 +8824,7 @@
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>06-05-2025</v>
+        <v>06-05-2026</v>
       </c>
       <c r="D180" t="str">
         <v>NiftyCE</v>
@@ -8829,19 +8833,19 @@
         <v>130</v>
       </c>
       <c r="F180">
-        <v>211</v>
+        <v>210.95</v>
       </c>
       <c r="G180">
         <v>195</v>
       </c>
       <c r="H180">
-        <v>-16</v>
+        <v>-15.95</v>
       </c>
       <c r="I180">
         <v>0</v>
       </c>
       <c r="J180">
-        <v>-2074</v>
+        <v>-2073.5</v>
       </c>
       <c r="K180">
         <v>100</v>
@@ -8853,7 +8857,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N180">
-        <v>-2174</v>
+        <v>-2173.5</v>
       </c>
       <c r="O180">
         <v>0</v>
@@ -8867,7 +8871,7 @@
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>06-05-2025</v>
+        <v>06-05-2026</v>
       </c>
       <c r="D181" t="str">
         <v>NiftyCE</v>
@@ -8876,22 +8880,22 @@
         <v>130</v>
       </c>
       <c r="F181">
-        <v>197</v>
+        <v>196.55</v>
       </c>
       <c r="G181">
-        <v>267</v>
+        <v>266.5</v>
       </c>
       <c r="H181">
-        <v>70</v>
+        <v>69.95</v>
       </c>
       <c r="I181">
-        <v>9094</v>
+        <v>9093.5</v>
       </c>
       <c r="J181">
         <v>0</v>
       </c>
       <c r="K181">
-        <v>71</v>
+        <v>70.69</v>
       </c>
       <c r="L181" t="str">
         <v>Yes</v>
@@ -8900,7 +8904,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N181">
-        <v>9023</v>
+        <v>9022.81</v>
       </c>
       <c r="O181">
         <v>0</v>
@@ -8914,7 +8918,7 @@
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>08-05-2025</v>
+        <v>08-05-2026</v>
       </c>
       <c r="D182" t="str">
         <v>SensexBullPE</v>
@@ -8923,13 +8927,13 @@
         <v>20</v>
       </c>
       <c r="F182">
-        <v>607</v>
+        <v>606.95</v>
       </c>
       <c r="G182">
-        <v>634</v>
+        <v>633.75</v>
       </c>
       <c r="H182">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="I182">
         <v>536</v>
@@ -8961,7 +8965,7 @@
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>08-05-2025</v>
+        <v>08-05-2026</v>
       </c>
       <c r="D183" t="str">
         <v>NiftyBullPE</v>
@@ -8970,16 +8974,16 @@
         <v>65</v>
       </c>
       <c r="F183">
-        <v>266</v>
+        <v>266.15</v>
       </c>
       <c r="G183">
-        <v>282</v>
+        <v>281.7</v>
       </c>
       <c r="H183">
-        <v>16</v>
+        <v>15.55</v>
       </c>
       <c r="I183">
-        <v>1011</v>
+        <v>1010.75</v>
       </c>
       <c r="J183">
         <v>0</v>
@@ -8994,7 +8998,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N183">
-        <v>911</v>
+        <v>910.75</v>
       </c>
       <c r="O183">
         <v>0</v>
@@ -9008,7 +9012,7 @@
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>08-05-2025</v>
+        <v>08-05-2026</v>
       </c>
       <c r="D184" t="str">
         <v>BankniftyPE</v>
@@ -9017,13 +9021,13 @@
         <v>60</v>
       </c>
       <c r="F184">
-        <v>496</v>
+        <v>496.35</v>
       </c>
       <c r="G184">
-        <v>534</v>
+        <v>534.1</v>
       </c>
       <c r="H184">
-        <v>38</v>
+        <v>37.75</v>
       </c>
       <c r="I184">
         <v>2265</v>
@@ -9055,7 +9059,7 @@
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>08-05-2025</v>
+        <v>08-05-2026</v>
       </c>
       <c r="D185" t="str">
         <v>Sensex PE</v>
@@ -9064,16 +9068,16 @@
         <v>40</v>
       </c>
       <c r="F185">
-        <v>481</v>
+        <v>480.92</v>
       </c>
       <c r="G185">
-        <v>532</v>
+        <v>531.85</v>
       </c>
       <c r="H185">
-        <v>51</v>
+        <v>50.93</v>
       </c>
       <c r="I185">
-        <v>2037</v>
+        <v>2037.2</v>
       </c>
       <c r="J185">
         <v>0</v>
@@ -9088,7 +9092,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N185">
-        <v>1937</v>
+        <v>1937.2</v>
       </c>
       <c r="O185">
         <v>0</v>
@@ -9102,7 +9106,7 @@
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>08-05-2025</v>
+        <v>08-05-2026</v>
       </c>
       <c r="D186" t="str">
         <v>NiftyPE</v>
@@ -9111,13 +9115,13 @@
         <v>130</v>
       </c>
       <c r="F186">
-        <v>204</v>
+        <v>203.55</v>
       </c>
       <c r="G186">
-        <v>243</v>
+        <v>243.05</v>
       </c>
       <c r="H186">
-        <v>40</v>
+        <v>39.5</v>
       </c>
       <c r="I186">
         <v>5135</v>
@@ -9149,7 +9153,7 @@
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>11-05-2025</v>
+        <v>11-05-2026</v>
       </c>
       <c r="D187" t="str">
         <v>NiftyBullPE</v>
@@ -9158,10 +9162,10 @@
         <v>65</v>
       </c>
       <c r="F187">
-        <v>242</v>
+        <v>241.85</v>
       </c>
       <c r="G187">
-        <v>207</v>
+        <v>206.85</v>
       </c>
       <c r="H187">
         <v>-35</v>
@@ -9196,7 +9200,7 @@
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>11-05-2025</v>
+        <v>11-05-2026</v>
       </c>
       <c r="D188" t="str">
         <v>BankniftyPE</v>
@@ -9205,19 +9209,19 @@
         <v>60</v>
       </c>
       <c r="F188">
-        <v>498</v>
+        <v>497.95</v>
       </c>
       <c r="G188">
-        <v>428</v>
+        <v>428.37</v>
       </c>
       <c r="H188">
-        <v>-70</v>
+        <v>-69.58</v>
       </c>
       <c r="I188">
         <v>0</v>
       </c>
       <c r="J188">
-        <v>-4175</v>
+        <v>-4174.8</v>
       </c>
       <c r="K188">
         <v>100</v>
@@ -9229,7 +9233,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N188">
-        <v>-4275</v>
+        <v>-4274.8</v>
       </c>
       <c r="O188">
         <v>0</v>
@@ -9243,7 +9247,7 @@
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>11-05-2025</v>
+        <v>11-05-2026</v>
       </c>
       <c r="D189" t="str">
         <v>Sensex PE</v>
@@ -9252,13 +9256,13 @@
         <v>40</v>
       </c>
       <c r="F189">
-        <v>518</v>
+        <v>518.3</v>
       </c>
       <c r="G189">
-        <v>546</v>
+        <v>545.6</v>
       </c>
       <c r="H189">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="I189">
         <v>1092</v>
@@ -9290,7 +9294,7 @@
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>11-05-2025</v>
+        <v>11-05-2026</v>
       </c>
       <c r="D190" t="str">
         <v>NiftyPE</v>
@@ -9299,16 +9303,16 @@
         <v>130</v>
       </c>
       <c r="F190">
-        <v>196</v>
+        <v>195.9</v>
       </c>
       <c r="G190">
-        <v>206</v>
+        <v>205.65</v>
       </c>
       <c r="H190">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="I190">
-        <v>1268</v>
+        <v>1267.5</v>
       </c>
       <c r="J190">
         <v>0</v>
@@ -9323,7 +9327,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N190">
-        <v>1166</v>
+        <v>1165.5</v>
       </c>
       <c r="O190">
         <v>0</v>
@@ -9337,7 +9341,7 @@
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>12-05-2025</v>
+        <v>12-05-2026</v>
       </c>
       <c r="D191" t="str">
         <v>SensexBullPE</v>
@@ -9346,13 +9350,13 @@
         <v>20</v>
       </c>
       <c r="F191">
-        <v>574</v>
+        <v>573.7</v>
       </c>
       <c r="G191">
-        <v>704</v>
+        <v>703.75</v>
       </c>
       <c r="H191">
-        <v>130</v>
+        <v>130.05</v>
       </c>
       <c r="I191">
         <v>2601</v>
@@ -9384,7 +9388,7 @@
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>12-05-2025</v>
+        <v>12-05-2026</v>
       </c>
       <c r="D192" t="str">
         <v>NiftyBullPE</v>
@@ -9393,16 +9397,16 @@
         <v>65</v>
       </c>
       <c r="F192">
-        <v>258</v>
+        <v>258.35</v>
       </c>
       <c r="G192">
-        <v>294</v>
+        <v>293.7</v>
       </c>
       <c r="H192">
-        <v>35</v>
+        <v>35.35</v>
       </c>
       <c r="I192">
-        <v>2298</v>
+        <v>2297.75</v>
       </c>
       <c r="J192">
         <v>0</v>
@@ -9417,7 +9421,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N192">
-        <v>2198</v>
+        <v>2197.75</v>
       </c>
       <c r="O192">
         <v>0</v>
@@ -9431,7 +9435,7 @@
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>12-05-2025</v>
+        <v>12-05-2026</v>
       </c>
       <c r="D193" t="str">
         <v>NiftyPE</v>
@@ -9440,16 +9444,16 @@
         <v>130</v>
       </c>
       <c r="F193">
-        <v>212</v>
+        <v>212.4</v>
       </c>
       <c r="G193">
-        <v>258</v>
+        <v>258.17</v>
       </c>
       <c r="H193">
-        <v>46</v>
+        <v>45.77</v>
       </c>
       <c r="I193">
-        <v>5950</v>
+        <v>5950.1</v>
       </c>
       <c r="J193">
         <v>0</v>
@@ -9464,7 +9468,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N193">
-        <v>5850</v>
+        <v>5850.1</v>
       </c>
       <c r="O193">
         <v>0</v>
@@ -9478,7 +9482,7 @@
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>13-05-2025</v>
+        <v>13-05-2026</v>
       </c>
       <c r="D194" t="str">
         <v>SensexBullPE</v>
@@ -9487,13 +9491,13 @@
         <v>20</v>
       </c>
       <c r="F194">
-        <v>616</v>
+        <v>615.8</v>
       </c>
       <c r="G194">
-        <v>512</v>
+        <v>512.05</v>
       </c>
       <c r="H194">
-        <v>-104</v>
+        <v>-103.75</v>
       </c>
       <c r="I194">
         <v>0</v>
@@ -9525,7 +9529,7 @@
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>13-05-2025</v>
+        <v>13-05-2026</v>
       </c>
       <c r="D195" t="str">
         <v>NiftyBullPE</v>
@@ -9534,13 +9538,13 @@
         <v>65</v>
       </c>
       <c r="F195">
-        <v>247</v>
+        <v>247.15</v>
       </c>
       <c r="G195">
-        <v>215</v>
+        <v>214.75</v>
       </c>
       <c r="H195">
-        <v>-32</v>
+        <v>-32.4</v>
       </c>
       <c r="I195">
         <v>0</v>
@@ -9572,7 +9576,7 @@
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>13-05-2025</v>
+        <v>13-05-2026</v>
       </c>
       <c r="D196" t="str">
         <v>BankniftyPE</v>
@@ -9581,13 +9585,13 @@
         <v>60</v>
       </c>
       <c r="F196">
-        <v>504</v>
+        <v>504.35</v>
       </c>
       <c r="G196">
-        <v>437</v>
+        <v>436.9</v>
       </c>
       <c r="H196">
-        <v>-67</v>
+        <v>-67.45</v>
       </c>
       <c r="I196">
         <v>0</v>
@@ -9596,7 +9600,7 @@
         <v>-4047</v>
       </c>
       <c r="K196">
-        <v>86</v>
+        <v>85.5</v>
       </c>
       <c r="L196" t="str">
         <v>Yes</v>
@@ -9605,7 +9609,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N196">
-        <v>-4133</v>
+        <v>-4132.5</v>
       </c>
       <c r="O196">
         <v>0</v>
@@ -9619,7 +9623,7 @@
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>14-05-2025</v>
+        <v>14-05-2026</v>
       </c>
       <c r="D197" t="str">
         <v>SensexBullCE</v>
@@ -9628,13 +9632,13 @@
         <v>20</v>
       </c>
       <c r="F197">
-        <v>673</v>
+        <v>672.65</v>
       </c>
       <c r="G197">
-        <v>771</v>
+        <v>771.15</v>
       </c>
       <c r="H197">
-        <v>99</v>
+        <v>98.5</v>
       </c>
       <c r="I197">
         <v>1970</v>
@@ -9643,7 +9647,7 @@
         <v>0</v>
       </c>
       <c r="K197">
-        <v>104</v>
+        <v>104.1</v>
       </c>
       <c r="L197" t="str">
         <v>Yes</v>
@@ -9652,7 +9656,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N197">
-        <v>1866</v>
+        <v>1865.9</v>
       </c>
       <c r="O197">
         <v>0</v>
@@ -9666,7 +9670,7 @@
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>14-05-2025</v>
+        <v>14-05-2026</v>
       </c>
       <c r="D198" t="str">
         <v>NiftyBullCE</v>
@@ -9675,22 +9679,22 @@
         <v>65</v>
       </c>
       <c r="F198">
-        <v>254</v>
+        <v>253.8</v>
       </c>
       <c r="G198">
-        <v>258</v>
+        <v>258.45</v>
       </c>
       <c r="H198">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="I198">
-        <v>302</v>
+        <v>302.25</v>
       </c>
       <c r="J198">
         <v>0</v>
       </c>
       <c r="K198">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="L198" t="str">
         <v>Yes</v>
@@ -9699,7 +9703,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N198">
-        <v>201</v>
+        <v>200.75</v>
       </c>
       <c r="O198">
         <v>0</v>
@@ -9713,7 +9717,7 @@
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>14-05-2025</v>
+        <v>14-05-2026</v>
       </c>
       <c r="D199" t="str">
         <v>BankniftyCE</v>
@@ -9722,16 +9726,16 @@
         <v>60</v>
       </c>
       <c r="F199">
-        <v>499</v>
+        <v>499.25</v>
       </c>
       <c r="G199">
-        <v>546</v>
+        <v>545.87</v>
       </c>
       <c r="H199">
-        <v>47</v>
+        <v>46.62</v>
       </c>
       <c r="I199">
-        <v>2797</v>
+        <v>2797.2</v>
       </c>
       <c r="J199">
         <v>0</v>
@@ -9746,7 +9750,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N199">
-        <v>2693</v>
+        <v>2693.2</v>
       </c>
       <c r="O199">
         <v>0</v>
@@ -9760,7 +9764,7 @@
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>14-05-2025</v>
+        <v>14-05-2026</v>
       </c>
       <c r="D200" t="str">
         <v>Sensex CE</v>
@@ -9769,16 +9773,16 @@
         <v>40</v>
       </c>
       <c r="F200">
-        <v>582</v>
+        <v>582.05</v>
       </c>
       <c r="G200">
-        <v>776</v>
+        <v>776.02</v>
       </c>
       <c r="H200">
-        <v>194</v>
+        <v>193.97</v>
       </c>
       <c r="I200">
-        <v>7759</v>
+        <v>7758.8</v>
       </c>
       <c r="J200">
         <v>0</v>
@@ -9793,7 +9797,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N200">
-        <v>7655</v>
+        <v>7654.8</v>
       </c>
       <c r="O200">
         <v>0</v>
@@ -9807,7 +9811,7 @@
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>14-05-2025</v>
+        <v>14-05-2026</v>
       </c>
       <c r="D201" t="str">
         <v>NiftyCE</v>
@@ -9816,16 +9820,16 @@
         <v>130</v>
       </c>
       <c r="F201">
-        <v>195</v>
+        <v>194.8</v>
       </c>
       <c r="G201">
-        <v>211</v>
+        <v>210.75</v>
       </c>
       <c r="H201">
-        <v>16</v>
+        <v>15.95</v>
       </c>
       <c r="I201">
-        <v>2074</v>
+        <v>2073.5</v>
       </c>
       <c r="J201">
         <v>0</v>
@@ -9840,7 +9844,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N201">
-        <v>1970</v>
+        <v>1969.5</v>
       </c>
       <c r="O201">
         <v>0</v>
@@ -9854,7 +9858,7 @@
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>18-05-2025</v>
+        <v>18-05-2026</v>
       </c>
       <c r="D202" t="str">
         <v>SensexBullPE</v>
@@ -9863,10 +9867,10 @@
         <v>20</v>
       </c>
       <c r="F202">
-        <v>609</v>
+        <v>608.7</v>
       </c>
       <c r="G202">
-        <v>672</v>
+        <v>671.7</v>
       </c>
       <c r="H202">
         <v>63</v>
@@ -9901,7 +9905,7 @@
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>18-05-2025</v>
+        <v>18-05-2026</v>
       </c>
       <c r="D203" t="str">
         <v>NiftyBullPE</v>
@@ -9910,10 +9914,10 @@
         <v>65</v>
       </c>
       <c r="F203">
-        <v>249</v>
+        <v>249.3</v>
       </c>
       <c r="G203">
-        <v>300</v>
+        <v>300.3</v>
       </c>
       <c r="H203">
         <v>51</v>
@@ -9948,7 +9952,7 @@
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>18-05-2025</v>
+        <v>18-05-2026</v>
       </c>
       <c r="D204" t="str">
         <v>Sensex PE</v>
@@ -9957,10 +9961,10 @@
         <v>40</v>
       </c>
       <c r="F204">
-        <v>530</v>
+        <v>529.8</v>
       </c>
       <c r="G204">
-        <v>587</v>
+        <v>586.8</v>
       </c>
       <c r="H204">
         <v>57</v>
@@ -9995,7 +9999,7 @@
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>18-05-2025</v>
+        <v>18-05-2026</v>
       </c>
       <c r="D205" t="str">
         <v>NiftyPE</v>
@@ -10004,13 +10008,13 @@
         <v>130</v>
       </c>
       <c r="F205">
-        <v>215</v>
+        <v>215.47</v>
       </c>
       <c r="G205">
-        <v>250</v>
+        <v>249.87</v>
       </c>
       <c r="H205">
-        <v>34</v>
+        <v>34.4</v>
       </c>
       <c r="I205">
         <v>4439</v>
@@ -10042,7 +10046,7 @@
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>20-05-2025</v>
+        <v>20-05-2026</v>
       </c>
       <c r="D206" t="str">
         <v>SensexBullPE</v>
@@ -10066,7 +10070,7 @@
         <v>-2000</v>
       </c>
       <c r="K206">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="L206" t="str">
         <v>Yes</v>
@@ -10075,7 +10079,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N206">
-        <v>-2092</v>
+        <v>-2091.5</v>
       </c>
       <c r="O206">
         <v>0</v>
@@ -10089,7 +10093,7 @@
         <v/>
       </c>
       <c r="C207" t="str">
-        <v>20-05-2025</v>
+        <v>20-05-2026</v>
       </c>
       <c r="D207" t="str">
         <v>NiftyBullPE</v>
@@ -10098,22 +10102,22 @@
         <v>65</v>
       </c>
       <c r="F207">
-        <v>252</v>
+        <v>252.4</v>
       </c>
       <c r="G207">
-        <v>230</v>
+        <v>229.85</v>
       </c>
       <c r="H207">
-        <v>-23</v>
+        <v>-22.55</v>
       </c>
       <c r="I207">
         <v>0</v>
       </c>
       <c r="J207">
-        <v>-1466</v>
+        <v>-1465.75</v>
       </c>
       <c r="K207">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="L207" t="str">
         <v>Yes</v>
@@ -10122,7 +10126,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N207">
-        <v>-1558</v>
+        <v>-1557.55</v>
       </c>
       <c r="O207">
         <v>0</v>
@@ -10136,7 +10140,7 @@
         <v/>
       </c>
       <c r="C208" t="str">
-        <v>20-05-2025</v>
+        <v>20-05-2026</v>
       </c>
       <c r="D208" t="str">
         <v>BankniftyPE</v>
@@ -10145,13 +10149,13 @@
         <v>60</v>
       </c>
       <c r="F208">
-        <v>493</v>
+        <v>492.6</v>
       </c>
       <c r="G208">
-        <v>433</v>
+        <v>432.65</v>
       </c>
       <c r="H208">
-        <v>-60</v>
+        <v>-59.95</v>
       </c>
       <c r="I208">
         <v>0</v>
@@ -10160,7 +10164,7 @@
         <v>-3597</v>
       </c>
       <c r="K208">
-        <v>92</v>
+        <v>91.8</v>
       </c>
       <c r="L208" t="str">
         <v>Yes</v>
@@ -10169,7 +10173,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N208">
-        <v>-3689</v>
+        <v>-3688.8</v>
       </c>
       <c r="O208">
         <v>0</v>
@@ -10183,7 +10187,7 @@
         <v/>
       </c>
       <c r="C209" t="str">
-        <v>20-05-2025</v>
+        <v>20-05-2026</v>
       </c>
       <c r="D209" t="str">
         <v>NiftyPE</v>
@@ -10192,13 +10196,13 @@
         <v>130</v>
       </c>
       <c r="F209">
-        <v>205</v>
+        <v>204.65</v>
       </c>
       <c r="G209">
-        <v>185</v>
+        <v>185.45</v>
       </c>
       <c r="H209">
-        <v>-19</v>
+        <v>-19.2</v>
       </c>
       <c r="I209">
         <v>0</v>
@@ -10207,7 +10211,7 @@
         <v>-2496</v>
       </c>
       <c r="K209">
-        <v>94</v>
+        <v>93.5</v>
       </c>
       <c r="L209" t="str">
         <v>Yes</v>
@@ -10216,7 +10220,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N209">
-        <v>-2590</v>
+        <v>-2589.5</v>
       </c>
       <c r="O209">
         <v>0</v>
@@ -10230,7 +10234,7 @@
         <v/>
       </c>
       <c r="C210" t="str">
-        <v>21-05-2025</v>
+        <v>21-05-2026</v>
       </c>
       <c r="D210" t="str">
         <v>NiftyBullPE</v>
@@ -10239,19 +10243,19 @@
         <v>65</v>
       </c>
       <c r="F210">
-        <v>242</v>
+        <v>242.35</v>
       </c>
       <c r="G210">
-        <v>207</v>
+        <v>207.1</v>
       </c>
       <c r="H210">
-        <v>-35</v>
+        <v>-35.25</v>
       </c>
       <c r="I210">
         <v>0</v>
       </c>
       <c r="J210">
-        <v>-2291</v>
+        <v>-2291.25</v>
       </c>
       <c r="K210">
         <v>80</v>
@@ -10263,7 +10267,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N210">
-        <v>-2371</v>
+        <v>-2371.25</v>
       </c>
       <c r="O210">
         <v>0</v>
@@ -10277,7 +10281,7 @@
         <v/>
       </c>
       <c r="C211" t="str">
-        <v>22-05-2025</v>
+        <v>22-05-2026</v>
       </c>
       <c r="D211" t="str">
         <v>Sensex CE</v>
@@ -10286,19 +10290,19 @@
         <v>60</v>
       </c>
       <c r="F211">
-        <v>616</v>
+        <v>615.73</v>
       </c>
       <c r="G211">
-        <v>572</v>
+        <v>571.6</v>
       </c>
       <c r="H211">
-        <v>-44</v>
+        <v>-44.13</v>
       </c>
       <c r="I211">
         <v>0</v>
       </c>
       <c r="J211">
-        <v>-2648</v>
+        <v>-2647.8</v>
       </c>
       <c r="K211">
         <v>98</v>
@@ -10310,7 +10314,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N211">
-        <v>-2746</v>
+        <v>-2745.8</v>
       </c>
       <c r="O211">
         <v>0</v>
@@ -10324,7 +10328,7 @@
         <v/>
       </c>
       <c r="C212" t="str">
-        <v>22-05-2025</v>
+        <v>22-05-2026</v>
       </c>
       <c r="D212" t="str">
         <v>BankniftyCE</v>
@@ -10333,19 +10337,19 @@
         <v>90</v>
       </c>
       <c r="F212">
-        <v>500</v>
+        <v>499.8</v>
       </c>
       <c r="G212">
-        <v>469</v>
+        <v>469.03</v>
       </c>
       <c r="H212">
-        <v>-31</v>
+        <v>-30.77</v>
       </c>
       <c r="I212">
         <v>0</v>
       </c>
       <c r="J212">
-        <v>-2769</v>
+        <v>-2769.3</v>
       </c>
       <c r="K212">
         <v>98</v>
@@ -10357,7 +10361,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N212">
-        <v>-2867</v>
+        <v>-2867.3</v>
       </c>
       <c r="O212">
         <v>0</v>
@@ -10371,7 +10375,7 @@
         <v/>
       </c>
       <c r="C213" t="str">
-        <v>25-05-2025</v>
+        <v>25-05-2026</v>
       </c>
       <c r="D213" t="str">
         <v>NiftyCE</v>
@@ -10380,19 +10384,19 @@
         <v>195</v>
       </c>
       <c r="F213">
-        <v>190</v>
+        <v>189.73333</v>
       </c>
       <c r="G213">
-        <v>170</v>
+        <v>170.45</v>
       </c>
       <c r="H213">
-        <v>-19</v>
+        <v>-19.28333</v>
       </c>
       <c r="I213">
         <v>0</v>
       </c>
       <c r="J213">
-        <v>-3760</v>
+        <v>-3760.24935</v>
       </c>
       <c r="K213">
         <v>160</v>
@@ -10404,7 +10408,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N213">
-        <v>-3920</v>
+        <v>-3920.24935</v>
       </c>
       <c r="O213">
         <v>0</v>
@@ -10418,7 +10422,7 @@
         <v/>
       </c>
       <c r="C214" t="str">
-        <v>25-05-2025</v>
+        <v>25-05-2026</v>
       </c>
       <c r="D214" t="str">
         <v>Sensex CE</v>
@@ -10427,22 +10431,22 @@
         <v>60</v>
       </c>
       <c r="F214">
-        <v>613</v>
+        <v>613.2667</v>
       </c>
       <c r="G214">
-        <v>570</v>
+        <v>570.3</v>
       </c>
       <c r="H214">
-        <v>-43</v>
+        <v>-42.9667</v>
       </c>
       <c r="I214">
         <v>0</v>
       </c>
       <c r="J214">
-        <v>-2578</v>
+        <v>-2578.002</v>
       </c>
       <c r="K214">
-        <v>155</v>
+        <v>154.65</v>
       </c>
       <c r="L214" t="str">
         <v>Yes</v>
@@ -10451,7 +10455,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N214">
-        <v>-2733</v>
+        <v>-2732.652</v>
       </c>
       <c r="O214">
         <v>0</v>
@@ -10465,7 +10469,7 @@
         <v/>
       </c>
       <c r="C215" t="str">
-        <v>25-05-2025</v>
+        <v>25-05-2026</v>
       </c>
       <c r="D215" t="str">
         <v>Sensex CE</v>
@@ -10474,19 +10478,19 @@
         <v>60</v>
       </c>
       <c r="F215">
-        <v>606</v>
+        <v>605.6</v>
       </c>
       <c r="G215">
-        <v>548</v>
+        <v>547.7167</v>
       </c>
       <c r="H215">
-        <v>-58</v>
+        <v>-57.8833</v>
       </c>
       <c r="I215">
         <v>0</v>
       </c>
       <c r="J215">
-        <v>-3473</v>
+        <v>-3472.998</v>
       </c>
       <c r="K215">
         <v>154</v>
@@ -10498,7 +10502,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N215">
-        <v>-3627</v>
+        <v>-3626.998</v>
       </c>
       <c r="O215">
         <v>0</v>
@@ -10512,7 +10516,7 @@
         <v/>
       </c>
       <c r="C216" t="str">
-        <v>25-05-2025</v>
+        <v>25-05-2026</v>
       </c>
       <c r="D216" t="str">
         <v>BankniftyCE</v>
@@ -10521,19 +10525,19 @@
         <v>90</v>
       </c>
       <c r="F216">
-        <v>482</v>
+        <v>481.65</v>
       </c>
       <c r="G216">
         <v>430</v>
       </c>
       <c r="H216">
-        <v>-52</v>
+        <v>-51.65</v>
       </c>
       <c r="I216">
         <v>0</v>
       </c>
       <c r="J216">
-        <v>-4649</v>
+        <v>-4648.5</v>
       </c>
       <c r="K216">
         <v>150</v>
@@ -10545,7 +10549,7 @@
         <v>Stop Loss Hit</v>
       </c>
       <c r="N216">
-        <v>-4799</v>
+        <v>-4798.5</v>
       </c>
       <c r="O216">
         <v>0</v>
@@ -10559,7 +10563,7 @@
         <v/>
       </c>
       <c r="C217" t="str">
-        <v>25-05-2025</v>
+        <v>25-05-2026</v>
       </c>
       <c r="D217" t="str">
         <v>BankniftyCE</v>
@@ -10568,13 +10572,13 @@
         <v>90</v>
       </c>
       <c r="F217">
-        <v>497</v>
+        <v>497.3</v>
       </c>
       <c r="G217">
-        <v>611</v>
+        <v>610.6</v>
       </c>
       <c r="H217">
-        <v>113</v>
+        <v>113.3</v>
       </c>
       <c r="I217">
         <v>10197</v>
@@ -10606,7 +10610,7 @@
         <v/>
       </c>
       <c r="C218" t="str">
-        <v>26-05-2025</v>
+        <v>26-05-2026</v>
       </c>
       <c r="D218" t="str">
         <v>Sensex PE</v>
@@ -10615,13 +10619,13 @@
         <v>60</v>
       </c>
       <c r="F218">
-        <v>539</v>
+        <v>538.75</v>
       </c>
       <c r="G218">
         <v>444</v>
       </c>
       <c r="H218">
-        <v>-95</v>
+        <v>-94.75</v>
       </c>
       <c r="I218">
         <v>0</v>
@@ -10653,7 +10657,7 @@
         <v/>
       </c>
       <c r="C219" t="str">
-        <v>26-05-2025</v>
+        <v>26-05-2026</v>
       </c>
       <c r="D219" t="str">
         <v>NiftyPE</v>
@@ -10665,10 +10669,10 @@
         <v>179</v>
       </c>
       <c r="G219">
-        <v>223</v>
+        <v>223.4</v>
       </c>
       <c r="H219">
-        <v>44</v>
+        <v>44.4</v>
       </c>
       <c r="I219">
         <v>8658</v>
@@ -10700,7 +10704,7 @@
         <v/>
       </c>
       <c r="C220" t="str">
-        <v>29-05-2025</v>
+        <v>29-05-2026</v>
       </c>
       <c r="D220" t="str">
         <v>Sensex PE</v>
@@ -10709,16 +10713,16 @@
         <v>60</v>
       </c>
       <c r="F220">
-        <v>396</v>
+        <v>396.33</v>
       </c>
       <c r="G220">
-        <v>493</v>
+        <v>492.7</v>
       </c>
       <c r="H220">
-        <v>96</v>
+        <v>96.37</v>
       </c>
       <c r="I220">
-        <v>5782</v>
+        <v>5782.2</v>
       </c>
       <c r="J220">
         <v>0</v>
@@ -10733,7 +10737,7 @@
         <v>Target Hit</v>
       </c>
       <c r="N220">
-        <v>5721</v>
+        <v>5721.2</v>
       </c>
       <c r="O220">
         <v>0</v>
